--- a/data/amma_ji_recipes.xlsx
+++ b/data/amma_ji_recipes.xlsx
@@ -1506,12 +1506,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Meetha daliya</t>
+          <t>मीठा दलिया</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Meetha daliya</t>
+          <t>ਮਿੱਠਾ ਦਲੀਆ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1597,17 +1597,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oatmeal Porridge</t>
+          <t>Oats porridge</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Oatmeal Porridge</t>
+          <t>ओट्स दलिया</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oatmeal Porridge</t>
+          <t>ਓਟਸ ਦਲੀਆ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -3229,17 +3229,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mixed vegetable pulao</t>
+          <t>Veg pulao</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mixed vegetable pulao</t>
+          <t>वेज पुलाव</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mixed vegetable pulao</t>
+          <t>ਵੈਜ ਪੁਲਾਓ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sprouted moong pulao</t>
+          <t>Moong sprouts pulao</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sprouted moong pulao</t>
+          <t>अंकुरित मूंग पुलाव</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sprouted moong pulao</t>
+          <t>ਪੁੰਗਰੀ ਮੂੰਗੀ ਪੁਲਾਓ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Paneer pulao</t>
+          <t>पनीर पुलाव</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Paneer pulao</t>
+          <t>ਪਨੀਰ ਪੁਲਾਓ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3605,17 +3605,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Vegetable biryani/biriyani</t>
+          <t>Veg biryani</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Vegetable biryani/biriyani</t>
+          <t>वेज बिरयानी</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vegetable biryani/biriyani</t>
+          <t>ਵੈਜ ਬਿਰਯਾਨੀ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Idli</t>
+          <t>इडली</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Idli</t>
+          <t>ਇਡਲੀ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Masala dosa</t>
+          <t>मसाला डोसा</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Masala dosa</t>
+          <t>ਮਸਾਲਾ ਡੋਸਾ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4177,17 +4177,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Suji/Rava dosa</t>
+          <t>Rava dosa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Suji/Rava dosa</t>
+          <t>रवा डोसा</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Suji/Rava dosa</t>
+          <t>ਰਵਾ ਡੋਸਾ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mixed dal</t>
+          <t>Mili-juli dal</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mixed dal</t>
+          <t>मिली-जुली दाल</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mixed dal</t>
+          <t>ਮਿਲੀ-ਜੁਲੀ ਦਾਲ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Aloo methi</t>
+          <t>आलू मेथी</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aloo methi</t>
+          <t>ਆਲੂ ਮੇਥੀ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Matar mushroom</t>
+          <t>मटर मशरूम</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Matar mushroom</t>
+          <t>ਮਟਰ ਮਸ਼ਰੂਮ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Matar ki sabzi</t>
+          <t>मटर की सब्ज़ी</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Matar ki sabzi</t>
+          <t>ਮਟਰਾਂ ਦੀ ਸਬਜ਼ੀ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Dum aloo</t>
+          <t>दम आलू</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dum aloo</t>
+          <t>ਦਮ ਆਲੂ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -10833,17 +10833,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Potato with curd</t>
+          <t>Dahi aloo</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Potato with curd</t>
+          <t>दही आलू</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Potato with curd</t>
+          <t>ਦਹੀਂ ਆਲੂ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -11213,17 +11213,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Semiya/Seviyan upma</t>
+          <t>Semiya upma</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Semiya/Seviyan upma</t>
+          <t>सेवइयाँ उपमा</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Semiya/Seviyan upma</t>
+          <t>ਸੇਵੀਆਂ ਦਾ ਉਪਮਾ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -11314,12 +11314,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Rice upma</t>
+          <t>चावल उपमा</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Rice upma</t>
+          <t>ਚੌਲਾਂ ਦਾ ਉਪਮਾ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
@@ -11506,12 +11506,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Vegetable upma</t>
+          <t>वेजिटेबल उपमा</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Vegetable upma</t>
+          <t>ਸਬਜ਼ੀ ਵਾਲਾ ਉਪਮਾ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
@@ -12361,17 +12361,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>with semolina</t>
+          <t>Instant rava idli</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>with semolina</t>
+          <t>झटपट रवा इडली</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>with semolina</t>
+          <t>ਝਟਪਟ ਰਵਾ ਇਡਲੀ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
@@ -12649,17 +12649,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Dal moong</t>
+          <t>Moong dal</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Dal moong</t>
+          <t>मूंग दाल</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dal moong</t>
+          <t>ਮੂੰਗੀ ਦੀ ਦਾਲ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
@@ -13418,12 +13418,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Aloo ki sabzi</t>
+          <t>आलू की सब्ज़ी</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aloo ki sabzi</t>
+          <t>ਆਲੂਆਂ ਦੀ ਸਬਜ਼ੀ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
@@ -15409,17 +15409,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Palak khichri/khichdi</t>
+          <t>Palak khichdi</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Palak khichri/khichdi</t>
+          <t>पालक खिचड़ी</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Palak khichri/khichdi</t>
+          <t>ਪਾਲਕ ਖਿਚੜੀ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -15479,7 +15479,7 @@
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V158" t="inlineStr">
@@ -15501,17 +15501,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Suji/Rava idli</t>
+          <t>Palak rava idli</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Suji/Rava idli</t>
+          <t>पालक रवा इडली</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Suji/Rava idli</t>
+          <t>ਪਾਲਕ ਰਵਾ ਇਡਲੀ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -15575,7 +15575,7 @@
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V159" t="inlineStr">
@@ -17774,12 +17774,12 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Dal makhani</t>
+          <t>दाल मखनी</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Dal makhani</t>
+          <t>ਦਾਲ ਮੱਖਣੀ</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V183" t="inlineStr">
@@ -17966,12 +17966,12 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Panchmel dal</t>
+          <t>पंचमेल दाल</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Panchmel dal</t>
+          <t>ਪੰਚਮੇਲ ਦਾਲ</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -18035,7 +18035,7 @@
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="V185" t="inlineStr">
@@ -20022,7 +20022,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>jaggery, honey</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -20177,7 +20181,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>honey, jaggery</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -24277,7 +24285,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -24339,7 +24351,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -24680,7 +24696,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>peas, skip</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -25176,7 +25196,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>tofu</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -26013,7 +26037,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>potato</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -26540,7 +26568,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr"/>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -27966,7 +27998,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr"/>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -28307,7 +28343,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G327" t="inlineStr"/>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>rice_flour</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -29454,7 +29494,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G364" t="inlineStr"/>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>spinach</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -31349,7 +31393,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G425" t="inlineStr"/>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>paneer, potato</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -35255,7 +35303,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G551" t="inlineStr"/>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>cashews, skip</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -35317,7 +35369,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G553" t="inlineStr"/>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -51852,7 +51908,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G1086" t="inlineStr"/>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>chana_dal, skip</t>
+        </is>
+      </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
@@ -52317,7 +52377,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G1101" t="inlineStr"/>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>chana_dal, skip</t>
+        </is>
+      </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
@@ -53247,7 +53311,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G1131" t="inlineStr"/>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>chana_dal, skip</t>
+        </is>
+      </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
@@ -53309,7 +53377,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G1133" t="inlineStr"/>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
@@ -53526,7 +53598,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G1140" t="inlineStr"/>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
@@ -57688,7 +57764,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G1274" t="inlineStr"/>
+      <c r="G1274" t="inlineStr">
+        <is>
+          <t>baking_powder</t>
+        </is>
+      </c>
     </row>
     <row r="1275">
       <c r="A1275" t="inlineStr">
@@ -58618,7 +58698,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G1304" t="inlineStr"/>
+      <c r="G1304" t="inlineStr">
+        <is>
+          <t>oil</t>
+        </is>
+      </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
@@ -68538,7 +68622,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G1624" t="inlineStr"/>
+      <c r="G1624" t="inlineStr">
+        <is>
+          <t>ghee</t>
+        </is>
+      </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
@@ -68693,7 +68781,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G1629" t="inlineStr"/>
+      <c r="G1629" t="inlineStr">
+        <is>
+          <t>carrot</t>
+        </is>
+      </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
@@ -68724,7 +68816,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G1630" t="inlineStr"/>
+      <c r="G1630" t="inlineStr">
+        <is>
+          <t>skip</t>
+        </is>
+      </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
@@ -77187,7 +77283,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G1903" t="inlineStr"/>
+      <c r="G1903" t="inlineStr">
+        <is>
+          <t>ghee</t>
+        </is>
+      </c>
     </row>
     <row r="1904">
       <c r="A1904" t="inlineStr">
@@ -78675,7 +78775,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G1951" t="inlineStr"/>
+      <c r="G1951" t="inlineStr">
+        <is>
+          <t>oil</t>
+        </is>
+      </c>
     </row>
     <row r="1952">
       <c r="A1952" t="inlineStr">
@@ -79277,7 +79381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79459,7 +79563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASC059</t>
+          <t>ASC047</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -79467,30 +79571,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Break the egg into a bowl. Add the milk, salt and black pepper and beat well.</t>
+          <t>Roast the daliya in the ghee on low heat until golden, about 4 minutes.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Anda katori mein todo. Doodh, namak aur kali mirch daal ke achhe se phento.</t>
+          <t>Daliya ko ghee mein dheemi aanch pe sunehra hone tak bhuno, lagbhag 4 minute.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>अंडा कटोरी में तोड़ो। दूध, नमक और काली मिर्च डालकर अच्छे से फेंटो।</t>
+          <t>दलिये को घी में धीमी आँच पर सुनहरा होने तक भूनो, लगभग 4 मिनट।</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ਆਂਡਾ ਕੌਲੀ ਵਿੱਚ ਤੋੜੋ। ਦੁੱਧ, ਲੂਣ ਅਤੇ ਕਾਲੀ ਮਿਰਚ ਪਾ ਕੇ ਚੰਗੀ ਤਰ੍ਹਾਂ ਫੈਂਟੋ।</t>
-        </is>
+          <t>ਦਲੀਏ ਨੂੰ ਘਿਓ ਵਿੱਚ ਹੌਲੀ ਅੱਗ ਤੇ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ, ਲਗਭਗ 4 ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASC059</t>
+          <t>ASC047</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -79498,30 +79605,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Melt the butter in a pan on low heat.</t>
+          <t>Add half a cup of water, cover and cook until soft, about 10 minutes, or 2 whistles in a cooker.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pan mein dheemi aanch pe makhan pighlao.</t>
+          <t>Aadha cup paani daal ke dhak do aur naram hone tak pakao, lagbhag 10 minute, ya cooker mein 2 seeti.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>पैन में धीमी आँच पर मक्खन पिघलाओ।</t>
+          <t>आधा कप पानी डालकर ढक दो और नरम होने तक पकाओ, लगभग 10 मिनट, या कुकर में 2 सीटी।</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ਪੈਨ ਵਿੱਚ ਹੌਲੀ ਅੱਗ ਤੇ ਮੱਖਣ ਪਿਘਲਾਓ।</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>ਅੱਧਾ ਕੱਪ ਪਾਣੀ ਪਾ ਕੇ ਢੱਕ ਦਿਓ ਅਤੇ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 10 ਮਿੰਟ, ਜਾਂ ਕੁੱਕਰ ਵਿੱਚ 2 ਸੀਟੀਆਂ।</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Let the pressure go down fully before you open the cooker.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASC059</t>
+          <t>ASC047</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -79529,37 +79643,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pour in the egg and keep stirring slowly. Take it off the heat while it still looks a little soft, about 2 minutes.</t>
+          <t>Pour in the milk and simmer on low heat, stirring, until creamy, about 8 minutes.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Anda daal ke dheere dheere chalaate raho. Jab thoda naram dikhe tabhi gas se utaar lo, lagbhag 2 minute.</t>
+          <t>Doodh daal ke dheemi aanch pe chalaate hue creamy hone tak pakao, lagbhag 8 minute.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>अंडा डालकर धीरे-धीरे चलाते रहो। जब थोड़ा नरम दिखे तभी आँच से उतार लो, लगभग 2 मिनट।</t>
+          <t>दूध डालकर धीमी आँच पर चलाते हुए मलाईदार होने तक पकाओ, लगभग 8 मिनट।</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ਆਂਡਾ ਪਾ ਕੇ ਹੌਲੀ-ਹੌਲੀ ਹਿਲਾਉਂਦੇ ਰਹੋ। ਜਦੋਂ ਥੋੜ੍ਹਾ ਨਰਮ ਦਿਸੇ ਉਦੋਂ ਹੀ ਅੱਗ ਤੋਂ ਲਾਹ ਲਓ, ਲਗਭਗ 2 ਮਿੰਟ।</t>
+          <t>ਦੁੱਧ ਪਾ ਕੇ ਹੌਲੀ ਅੱਗ ਤੇ ਹਿਲਾਉਂਦੇ ਹੋਏ ਮਲਾਈਦਾਰ ਹੋਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 8 ਮਿੰਟ।</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Make sure no runny raw egg is left before you eat.</t>
+          <t>Milk boils over fast. Stay close and lower the heat when it rises.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASC059</t>
+          <t>ASC047</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -79567,22 +79681,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serve hot with toast, pav or roti.</t>
+          <t>Stir in the sugar until it dissolves and serve warm.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Garam garam toast, pav ya roti ke saath khao.</t>
+          <t>Cheeni ghulne tak milao aur garam garam khao.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>गरमागरम टोस्ट, पाव या रोटी के साथ खाओ।</t>
+          <t>चीनी घुलने तक मिलाओ और गरम-गरम खाओ।</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ਗਰਮਾ-ਗਰਮ ਟੋਸਟ, ਪਾਵ ਜਾਂ ਰੋਟੀ ਨਾਲ ਖਾਓ।</t>
+          <t>ਖੰਡ ਘੁਲਣ ਤੱਕ ਮਿਲਾਓ ਅਤੇ ਗਰਮ-ਗਰਮ ਖਾਓ।</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -79590,7 +79704,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ASC098</t>
+          <t>ASC050</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -79598,37 +79712,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boil the potatoes until soft, about 3 whistles in the cooker. Peel and mash them well.</t>
+          <t>Boil half a cup of water, add the oats and cook for 2 minutes, stirring.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aloo ko cooker mein 3 seeti tak ubaal lo. Chheel ke achhe se mash kar lo.</t>
+          <t>Aadha cup paani ubaalo, oats daal ke 2 minute chalaate hue pakao.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>आलू को कुकर में 3 सीटी तक उबाल लो। छीलकर अच्छे से मैश कर लो।</t>
+          <t>आधा कप पानी उबालो, ओट्स डालकर 2 मिनट चलाते हुए पकाओ।</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ਆਲੂਆਂ ਨੂੰ ਕੁੱਕਰ ਵਿੱਚ 3 ਸੀਟੀਆਂ ਤੱਕ ਉਬਾਲ ਲਓ। ਛਿੱਲ ਕੇ ਚੰਗੀ ਤਰ੍ਹਾਂ ਮੈਸ਼ ਕਰ ਲਓ।</t>
+          <t>ਅੱਧਾ ਕੱਪ ਪਾਣੀ ਉਬਾਲੋ, ਓਟਸ ਪਾ ਕੇ 2 ਮਿੰਟ ਹਿਲਾਉਂਦੇ ਹੋਏ ਪਕਾਓ।</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Let the pressure go down fully before you open the cooker.</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASC098</t>
+          <t>ASC050</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -79636,33 +79746,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mix the atta with a pinch of salt and about 4 tablespoons of water. Knead a soft dough, cover and rest it for 15 minutes.</t>
+          <t>Pour in the milk and simmer on low heat, stirring, until creamy, about 4 minutes.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Atte mein chutki bhar namak aur lagbhag 4 chammach paani daal ke naram aata goondh lo. Dhak ke 15 minute rakh do.</t>
+          <t>Doodh daal ke dheemi aanch pe chalaate hue creamy hone tak pakao, lagbhag 4 minute.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>आटे में चुटकी भर नमक और लगभग 4 चम्मच पानी डालकर नरम आटा गूँध लो। ढककर 15 मिनट रख दो।</t>
+          <t>दूध डालकर धीमी आँच पर चलाते हुए मलाईदार होने तक पकाओ, लगभग 4 मिनट।</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ਆਟੇ ਵਿੱਚ ਚੁਟਕੀ ਭਰ ਲੂਣ ਅਤੇ ਲਗਭਗ 4 ਚਮਚ ਪਾਣੀ ਪਾ ਕੇ ਨਰਮ ਆਟਾ ਗੁੰਨ੍ਹ ਲਓ। ਢੱਕ ਕੇ 15 ਮਿੰਟ ਰੱਖ ਦਿਓ।</t>
+          <t>ਦੁੱਧ ਪਾ ਕੇ ਹੌਲੀ ਅੱਗ ਤੇ ਹਿਲਾਉਂਦੇ ਹੋਏ ਮਲਾਈਦਾਰ ਹੋਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 4 ਮਿੰਟ।</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Milk boils over fast. Stay close and lower the heat when it rises.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASC098</t>
+          <t>ASC050</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -79670,22 +79784,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mix the mashed potato with finely chopped onion, green chilli and coriander. Add salt, red chilli powder, garam masala and amchur.</t>
+          <t>Stir in the sugar and serve warm. Top with banana or nuts if you have them.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mash kiye aloo mein barik kata pyaaz, hari mirch aur dhaniya milao. Namak, laal mirch, garam masala aur amchur daal do.</t>
+          <t>Cheeni milao aur garam garam khao. Kela ya meve ho to upar daal lo.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>मैश किए आलू में बारीक कटा प्याज़, हरी मिर्च और हरा धनिया मिलाओ। नमक, लाल मिर्च, गरम मसाला और अमचूर डाल दो।</t>
+          <t>चीनी मिलाओ और गरम-गरम खाओ। केला या मेवे हों तो ऊपर डाल लो।</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ਮੈਸ਼ ਕੀਤੇ ਆਲੂਆਂ ਵਿੱਚ ਬਾਰੀਕ ਕੱਟਿਆ ਪਿਆਜ਼, ਹਰੀ ਮਿਰਚ ਅਤੇ ਹਰਾ ਧਨੀਆ ਮਿਲਾਓ। ਲੂਣ, ਲਾਲ ਮਿਰਚ, ਗਰਮ ਮਸਾਲਾ ਅਤੇ ਅਮਚੂਰ ਪਾ ਦਿਓ।</t>
+          <t>ਖੰਡ ਮਿਲਾਓ ਅਤੇ ਗਰਮ-ਗਰਮ ਖਾਓ। ਕੇਲਾ ਜਾਂ ਮੇਵੇ ਹੋਣ ਤਾਂ ਉੱਤੇ ਪਾ ਲਓ।</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -79693,30 +79807,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ASC098</t>
+          <t>ASC059</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Make 3 dough balls. Roll one into a small circle, put stuffing in the middle, close it from all sides and roll it gently into a paratha.</t>
+          <t>Break the egg into a bowl. Add the milk, salt and black pepper and beat well.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Aate ki 3 loiyan bana lo. Ek ko chhota bel ke beech mein masala rakho, chaaron taraf se band karo aur halke haath se bel lo.</t>
+          <t>Anda katori mein todo. Doodh, namak aur kali mirch daal ke achhe se phento.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>आटे की 3 लोइयाँ बना लो। एक को छोटा बेलकर बीच में मसाला रखो, चारों तरफ़ से बंद करो और हल्के हाथ से बेल लो।</t>
+          <t>अंडा कटोरी में तोड़ो। दूध, नमक और काली मिर्च डालकर अच्छे से फेंटो।</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ਆਟੇ ਦੇ 3 ਪੇੜੇ ਬਣਾ ਲਓ। ਇੱਕ ਨੂੰ ਛੋਟਾ ਵੇਲ ਕੇ ਵਿੱਚ ਮਸਾਲਾ ਰੱਖੋ, ਚਾਰੇ ਪਾਸਿਓਂ ਬੰਦ ਕਰੋ ਅਤੇ ਹੌਲੀ ਹੱਥ ਨਾਲ ਵੇਲ ਲਓ।</t>
+          <t>ਆਂਡਾ ਕੌਲੀ ਵਿੱਚ ਤੋੜੋ। ਦੁੱਧ, ਲੂਣ ਅਤੇ ਕਾਲੀ ਮਿਰਚ ਪਾ ਕੇ ਚੰਗੀ ਤਰ੍ਹਾਂ ਫੈਂਟੋ।</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -79724,30 +79838,30 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASC098</t>
+          <t>ASC059</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cook it on a hot tawa on medium heat. Flip, spread ghee or oil on both sides and press lightly until golden spots appear.</t>
+          <t>Melt the butter in a pan on low heat.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Garam tawe par medium aanch pe sekho. Palat ke dono taraf ghee ya tel lagao aur halka dabaate hue sunehra hone tak sekho.</t>
+          <t>Pan mein dheemi aanch pe makhan pighlao.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>गरम तवे पर मध्यम आँच पर सेको। पलटकर दोनों तरफ़ घी या तेल लगाओ और हल्का दबाते हुए सुनहरा होने तक सेको।</t>
+          <t>पैन में धीमी आँच पर मक्खन पिघलाओ।</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ਗਰਮ ਤਵੇ ਤੇ ਦਰਮਿਆਨੀ ਅੱਗ ਤੇ ਸੇਕੋ। ਪਲਟ ਕੇ ਦੋਵੇਂ ਪਾਸੇ ਘਿਓ ਜਾਂ ਤੇਲ ਲਗਾਓ ਅਤੇ ਹਲਕਾ ਦਬਾਉਂਦੇ ਹੋਏ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਸੇਕੋ।</t>
+          <t>ਪੈਨ ਵਿੱਚ ਹੌਲੀ ਅੱਗ ਤੇ ਮੱਖਣ ਪਿਘਲਾਓ।</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -79755,61 +79869,68 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ASC098</t>
+          <t>ASC059</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Make the rest the same way. Serve hot with curd, butter or pickle.</t>
+          <t>Pour in the egg and keep stirring slowly. Take it off the heat while it still looks a little soft, about 2 minutes.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Baaki paranthe bhi aise hi banao. Garam garam dahi, makhan ya achaar ke saath khao.</t>
+          <t>Anda daal ke dheere dheere chalaate raho. Jab thoda naram dikhe tabhi gas se utaar lo, lagbhag 2 minute.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>बाकी परांठे भी ऐसे ही बनाओ। गरमागरम दही, मक्खन या अचार के साथ खाओ।</t>
+          <t>अंडा डालकर धीरे-धीरे चलाते रहो। जब थोड़ा नरम दिखे तभी आँच से उतार लो, लगभग 2 मिनट।</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ਬਾਕੀ ਪਰੌਂਠੇ ਵੀ ਇਸੇ ਤਰ੍ਹਾਂ ਬਣਾਓ। ਗਰਮਾ-ਗਰਮ ਦਹੀਂ, ਮੱਖਣ ਜਾਂ ਅਚਾਰ ਨਾਲ ਖਾਓ।</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>ਆਂਡਾ ਪਾ ਕੇ ਹੌਲੀ-ਹੌਲੀ ਹਿਲਾਉਂਦੇ ਰਹੋ। ਜਦੋਂ ਥੋੜ੍ਹਾ ਨਰਮ ਦਿਸੇ ਉਦੋਂ ਹੀ ਅੱਗ ਤੋਂ ਲਾਹ ਲਓ, ਲਗਭਗ 2 ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Make sure no runny raw egg is left before you eat.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ASC190</t>
+          <t>ASC059</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Shell the peas. Peel and cube the potato, chop the onion and tomato, and crush the ginger and garlic.</t>
+          <t>Serve hot with toast, pav or roti.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Matar chheel lo. Aloo chheel ke tukde karo, pyaaz aur tamatar kaato, adrak lehsun kooto.</t>
+          <t>Garam garam toast, pav ya roti ke saath khao.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>मटर छील लो। आलू छीलकर टुकड़े करो, प्याज़ और टमाटर काटो, अदरक लहसुन कूटो।</t>
+          <t>गरमागरम टोस्ट, पाव या रोटी के साथ खाओ।</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ਮਟਰ ਛਿੱਲ ਲਓ। ਆਲੂ ਛਿੱਲ ਕੇ ਟੁਕੜੇ ਕਰੋ, ਪਿਆਜ਼ ਅਤੇ ਟਮਾਟਰ ਕੱਟੋ, ਅਦਰਕ ਲਸਣ ਕੁੱਟੋ।</t>
+          <t>ਗਰਮਾ-ਗਰਮ ਟੋਸਟ, ਪਾਵ ਜਾਂ ਰੋਟੀ ਨਾਲ ਖਾਓ।</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -79817,133 +79938,133 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ASC190</t>
+          <t>ASC098</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Heat the ghee or oil and fry the onion until golden. Add the ginger, garlic and green chilli and stir for a minute.</t>
+          <t>Boil the potatoes until soft, about 3 whistles in the cooker. Peel and mash them well.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ghee ya tel garam karke pyaaz sunehra hone tak bhuno. Adrak, lehsun aur hari mirch daal ke ek minute chalao.</t>
+          <t>Aloo ko cooker mein 3 seeti tak ubaal lo. Chheel ke achhe se mash kar lo.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>घी या तेल गरम करके प्याज़ सुनहरा होने तक भूनो। अदरक, लहसुन और हरी मिर्च डालकर एक मिनट चलाओ।</t>
+          <t>आलू को कुकर में 3 सीटी तक उबाल लो। छीलकर अच्छे से मैश कर लो।</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ਘਿਓ ਜਾਂ ਤੇਲ ਗਰਮ ਕਰਕੇ ਪਿਆਜ਼ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ। ਅਦਰਕ, ਲਸਣ ਅਤੇ ਹਰੀ ਮਿਰਚ ਪਾ ਕੇ ਇੱਕ ਮਿੰਟ ਹਿਲਾਓ।</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>ਆਲੂਆਂ ਨੂੰ ਕੁੱਕਰ ਵਿੱਚ 3 ਸੀਟੀਆਂ ਤੱਕ ਉਬਾਲ ਲਓ। ਛਿੱਲ ਕੇ ਚੰਗੀ ਤਰ੍ਹਾਂ ਮੈਸ਼ ਕਰ ਲਓ।</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Let the pressure go down fully before you open the cooker.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ASC190</t>
+          <t>ASC098</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Add the tomato, turmeric, red chilli powder and salt. Cook until the tomato is mushy and oil shows at the sides, about 5 minutes.</t>
+          <t>Mix the atta with a pinch of salt and about 4 tablespoons of water. Knead a soft dough, cover and rest it for 15 minutes.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tamatar, haldi, laal mirch aur namak daalo. Tamatar gal jaaye aur kinaaron pe tel dikhe tab tak pakao, lagbhag 5 minute.</t>
+          <t>Atte mein chutki bhar namak aur lagbhag 4 chammach paani daal ke naram aata goondh lo. Dhak ke 15 minute rakh do.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>टमाटर, हल्दी, लाल मिर्च और नमक डालो। टमाटर गल जाए और किनारों पर तेल दिखे तब तक पकाओ, लगभग 5 मिनट।</t>
+          <t>आटे में चुटकी भर नमक और लगभग 4 चम्मच पानी डालकर नरम आटा गूँध लो। ढककर 15 मिनट रख दो।</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ਟਮਾਟਰ, ਹਲਦੀ, ਲਾਲ ਮਿਰਚ ਅਤੇ ਲੂਣ ਪਾਓ। ਟਮਾਟਰ ਗਲ ਜਾਵੇ ਅਤੇ ਕਿਨਾਰਿਆਂ ਤੇ ਤੇਲ ਦਿਸੇ ਤਦ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 5 ਮਿੰਟ।</t>
+          <t>ਆਟੇ ਵਿੱਚ ਚੁਟਕੀ ਭਰ ਲੂਣ ਅਤੇ ਲਗਭਗ 4 ਚਮਚ ਪਾਣੀ ਪਾ ਕੇ ਨਰਮ ਆਟਾ ਗੁੰਨ੍ਹ ਲਓ। ਢੱਕ ਕੇ 15 ਮਿੰਟ ਰੱਖ ਦਿਓ।</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ASC190</t>
+          <t>ASC098</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Add the potato, peas and 1 cup water. Cover and cook until the potato is soft, about 12 minutes, or 2 whistles in a cooker.</t>
+          <t>Mix the mashed potato with finely chopped onion, green chilli and coriander. Add salt, red chilli powder, garam masala and amchur.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Aloo, matar aur 1 cup paani daalo. Dhak ke aloo naram hone tak pakao, lagbhag 12 minute, ya cooker mein 2 seeti.</t>
+          <t>Mash kiye aloo mein barik kata pyaaz, hari mirch aur dhaniya milao. Namak, laal mirch, garam masala aur amchur daal do.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>आलू, मटर और 1 कप पानी डालो। ढककर आलू नरम होने तक पकाओ, लगभग 12 मिनट, या कुकर में 2 सीटी।</t>
+          <t>मैश किए आलू में बारीक कटा प्याज़, हरी मिर्च और हरा धनिया मिलाओ। नमक, लाल मिर्च, गरम मसाला और अमचूर डाल दो।</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ਆਲੂ, ਮਟਰ ਅਤੇ 1 ਕੱਪ ਪਾਣੀ ਪਾਓ। ਢੱਕ ਕੇ ਆਲੂ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 12 ਮਿੰਟ, ਜਾਂ ਕੁੱਕਰ ਵਿੱਚ 2 ਸੀਟੀਆਂ।</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>12</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Let the pressure go down fully before you open the cooker.</t>
-        </is>
-      </c>
+          <t>ਮੈਸ਼ ਕੀਤੇ ਆਲੂਆਂ ਵਿੱਚ ਬਾਰੀਕ ਕੱਟਿਆ ਪਿਆਜ਼, ਹਰੀ ਮਿਰਚ ਅਤੇ ਹਰਾ ਧਨੀਆ ਮਿਲਾਓ। ਲੂਣ, ਲਾਲ ਮਿਰਚ, ਗਰਮ ਮਸਾਲਾ ਅਤੇ ਅਮਚੂਰ ਪਾ ਦਿਓ।</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ASC190</t>
+          <t>ASC098</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Stir in the garam masala, top with coriander and serve with roti or rice.</t>
+          <t>Make 3 dough balls. Roll one into a small circle, put stuffing in the middle, close it from all sides and roll it gently into a paratha.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Garam masala milao, dhaniya daalo aur roti ya chawal ke saath khao.</t>
+          <t>Aate ki 3 loiyan bana lo. Ek ko chhota bel ke beech mein masala rakho, chaaron taraf se band karo aur halke haath se bel lo.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>गरम मसाला मिलाओ, हरा धनिया डालो और रोटी या चावल के साथ खाओ।</t>
+          <t>आटे की 3 लोइयाँ बना लो। एक को छोटा बेलकर बीच में मसाला रखो, चारों तरफ़ से बंद करो और हल्के हाथ से बेल लो।</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ਗਰਮ ਮਸਾਲਾ ਮਿਲਾਓ, ਹਰਾ ਧਨੀਆ ਪਾਓ ਅਤੇ ਰੋਟੀ ਜਾਂ ਚੌਲਾਂ ਨਾਲ ਖਾਓ।</t>
+          <t>ਆਟੇ ਦੇ 3 ਪੇੜੇ ਬਣਾ ਲਓ। ਇੱਕ ਨੂੰ ਛੋਟਾ ਵੇਲ ਕੇ ਵਿੱਚ ਮਸਾਲਾ ਰੱਖੋ, ਚਾਰੇ ਪਾਸਿਓਂ ਬੰਦ ਕਰੋ ਅਤੇ ਹੌਲੀ ਹੱਥ ਨਾਲ ਵੇਲ ਲਓ।</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -79951,30 +80072,30 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ASC191</t>
+          <t>ASC098</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Shell the peas, cube the paneer, chop the onion and tomato, and crush the ginger and garlic.</t>
+          <t>Cook it on a hot tawa on medium heat. Flip, spread ghee or oil on both sides and press lightly until golden spots appear.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Matar chheel lo, paneer ke tukde karo, pyaaz aur tamatar kaato, adrak lehsun kooto.</t>
+          <t>Garam tawe par medium aanch pe sekho. Palat ke dono taraf ghee ya tel lagao aur halka dabaate hue sunehra hone tak sekho.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>मटर छील लो, पनीर के टुकड़े करो, प्याज़ और टमाटर काटो, अदरक लहसुन कूटो।</t>
+          <t>गरम तवे पर मध्यम आँच पर सेको। पलटकर दोनों तरफ़ घी या तेल लगाओ और हल्का दबाते हुए सुनहरा होने तक सेको।</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ਮਟਰ ਛਿੱਲ ਲਓ, ਪਨੀਰ ਦੇ ਟੁਕੜੇ ਕਰੋ, ਪਿਆਜ਼ ਅਤੇ ਟਮਾਟਰ ਕੱਟੋ, ਅਦਰਕ ਲਸਣ ਕੁੱਟੋ।</t>
+          <t>ਗਰਮ ਤਵੇ ਤੇ ਦਰਮਿਆਨੀ ਅੱਗ ਤੇ ਸੇਕੋ। ਪਲਟ ਕੇ ਦੋਵੇਂ ਪਾਸੇ ਘਿਓ ਜਾਂ ਤੇਲ ਲਗਾਓ ਅਤੇ ਹਲਕਾ ਦਬਾਉਂਦੇ ਹੋਏ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਸੇਕੋ।</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -79982,30 +80103,30 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASC191</t>
+          <t>ASC098</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lightly fry the paneer cubes in a little ghee until golden at the edges. Keep them in warm water so they stay soft.</t>
+          <t>Make the rest the same way. Serve hot with curd, butter or pickle.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Paneer ke tukdon ko thode ghee mein halka sunehra hone tak sek lo. Naram rakhne ke liye gungune paani mein daal do.</t>
+          <t>Baaki paranthe bhi aise hi banao. Garam garam dahi, makhan ya achaar ke saath khao.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>पनीर के टुकड़ों को थोड़े घी में हल्का सुनहरा होने तक सेक लो। नरम रखने के लिए गुनगुने पानी में डाल दो।</t>
+          <t>बाकी परांठे भी ऐसे ही बनाओ। गरमागरम दही, मक्खन या अचार के साथ खाओ।</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ਪਨੀਰ ਦੇ ਟੁਕੜਿਆਂ ਨੂੰ ਥੋੜ੍ਹੇ ਘਿਓ ਵਿੱਚ ਹਲਕਾ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਸੇਕ ਲਓ। ਨਰਮ ਰੱਖਣ ਲਈ ਕੋਸੇ ਪਾਣੀ ਵਿੱਚ ਪਾ ਦਿਓ।</t>
+          <t>ਬਾਕੀ ਪਰੌਂਠੇ ਵੀ ਇਸੇ ਤਰ੍ਹਾਂ ਬਣਾਓ। ਗਰਮਾ-ਗਰਮ ਦਹੀਂ, ਮੱਖਣ ਜਾਂ ਅਚਾਰ ਨਾਲ ਖਾਓ।</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -80013,516 +80134,513 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASC191</t>
+          <t>ASC115</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>In the same pan fry the onion until golden, then add the ginger, garlic and green chilli for a minute.</t>
+          <t>Wash the rice and soak it for 20 minutes. Cut the carrot and beans into small pieces, shell the peas and slice the onion.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Usi pan mein pyaaz sunehra hone tak bhuno, phir adrak, lehsun aur hari mirch daal ke ek minute chalao.</t>
+          <t>Chawal dho ke 20 minute bhigo do. Gajar aur beans chhote kaato, matar chheelo aur pyaaz lambe kaato.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>उसी पैन में प्याज़ सुनहरा होने तक भूनो, फिर अदरक, लहसुन और हरी मिर्च डालकर एक मिनट चलाओ।</t>
+          <t>चावल धोकर 20 मिनट भिगो दो। गाजर और बीन्स छोटे काटो, मटर छीलो और प्याज़ लंबे काटो।</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ਉਸੇ ਪੈਨ ਵਿੱਚ ਪਿਆਜ਼ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ, ਫਿਰ ਅਦਰਕ, ਲਸਣ ਅਤੇ ਹਰੀ ਮਿਰਚ ਪਾ ਕੇ ਇੱਕ ਮਿੰਟ ਹਿਲਾਓ।</t>
-        </is>
+          <t>ਚੌਲ ਧੋ ਕੇ 20 ਮਿੰਟ ਭਿਓਂ ਦਿਓ। ਗਾਜਰ ਅਤੇ ਫਲੀਆਂ ਛੋਟੀਆਂ ਕੱਟੋ, ਮਟਰ ਛਿੱਲੋ ਅਤੇ ਪਿਆਜ਼ ਲੰਮਾ ਕੱਟੋ।</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>20</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ASC191</t>
+          <t>ASC115</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Add the tomato, turmeric, red chilli powder and salt. Cook until oil shows at the sides, about 5 minutes.</t>
+          <t>Heat the ghee or oil and add the bay leaf, cumin, black cardamom, cloves and cinnamon. Fry the onion until light golden.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tamatar, haldi, laal mirch aur namak daalo. Kinaaron pe tel dikhe tab tak pakao, lagbhag 5 minute.</t>
+          <t>Ghee ya tel garam karke tej patta, jeera, badi elaichi, laung aur dalchini daalo. Pyaaz halka sunehra hone tak bhuno.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>टमाटर, हल्दी, लाल मिर्च और नमक डालो। किनारों पर तेल दिखे तब तक पकाओ, लगभग 5 मिनट।</t>
+          <t>घी या तेल गरम करके तेज पत्ता, जीरा, बड़ी इलायची, लौंग और दालचीनी डालो। प्याज़ हल्का सुनहरा होने तक भूनो।</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ਟਮਾਟਰ, ਹਲਦੀ, ਲਾਲ ਮਿਰਚ ਅਤੇ ਲੂਣ ਪਾਓ। ਕਿਨਾਰਿਆਂ ਤੇ ਤੇਲ ਦਿਸੇ ਤਦ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 5 ਮਿੰਟ।</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>5</v>
+          <t>ਘਿਓ ਜਾਂ ਤੇਲ ਗਰਮ ਕਰਕੇ ਤੇਜ ਪੱਤਾ, ਜੀਰਾ, ਵੱਡੀ ਇਲਾਇਚੀ, ਲੌਂਗ ਅਤੇ ਦਾਲਚੀਨੀ ਪਾਓ। ਪਿਆਜ਼ ਹਲਕਾ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ।</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ASC191</t>
+          <t>ASC115</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Add the peas and 1 cup water. Cover and cook until the peas are soft, about 8 minutes.</t>
+          <t>Add the carrot, beans and peas and stir for 2 minutes. Add the drained rice and salt and stir gently.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Matar aur 1 cup paani daalo. Dhak ke matar naram hone tak pakao, lagbhag 8 minute.</t>
+          <t>Gajar, beans aur matar daal ke 2 minute chalao. Paani nikaale chawal aur namak daal ke halke se milao.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>मटर और 1 कप पानी डालो। ढककर मटर नरम होने तक पकाओ, लगभग 8 मिनट।</t>
+          <t>गाजर, बीन्स और मटर डालकर 2 मिनट चलाओ। पानी निकाले चावल और नमक डालकर हल्के से मिलाओ।</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ਮਟਰ ਅਤੇ 1 ਕੱਪ ਪਾਣੀ ਪਾਓ। ਢੱਕ ਕੇ ਮਟਰ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 8 ਮਿੰਟ।</t>
+          <t>ਗਾਜਰ, ਫਲੀਆਂ ਅਤੇ ਮਟਰ ਪਾ ਕੇ 2 ਮਿੰਟ ਹਿਲਾਓ। ਪਾਣੀ ਕੱਢੇ ਚੌਲ ਅਤੇ ਲੂਣ ਪਾ ਕੇ ਹੌਲੀ ਜਿਹੇ ਮਿਲਾਓ।</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ASC191</t>
+          <t>ASC115</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Add the paneer and garam masala and simmer for 2 minutes. Top with coriander and serve.</t>
+          <t>Add 160 ml water, bring to a boil, then cover and cook on the lowest heat for 12 minutes, or 2 whistles in a cooker.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Paneer aur garam masala daal ke 2 minute halki aanch pe pakao. Dhaniya daal ke serve karo.</t>
+          <t>160 ml paani daal ke ubaal aane do, phir dhak ke sabse dheemi aanch pe 12 minute pakao, ya cooker mein 2 seeti.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>पनीर और गरम मसाला डालकर 2 मिनट हल्की आँच पर पकाओ। हरा धनिया डालकर परोसो।</t>
+          <t>160 ml पानी डालकर उबाल आने दो, फिर ढककर सबसे धीमी आँच पर 12 मिनट पकाओ, या कुकर में 2 सीटी।</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ਪਨੀਰ ਅਤੇ ਗਰਮ ਮਸਾਲਾ ਪਾ ਕੇ 2 ਮਿੰਟ ਹਲਕੀ ਅੱਗ ਤੇ ਪਕਾਓ। ਹਰਾ ਧਨੀਆ ਪਾ ਕੇ ਪਰੋਸੋ।</t>
+          <t>160 ml ਪਾਣੀ ਪਾ ਕੇ ਉਬਾਲ ਆਉਣ ਦਿਓ, ਫਿਰ ਢੱਕ ਕੇ ਸਭ ਤੋਂ ਹੌਲੀ ਅੱਗ ਤੇ 12 ਮਿੰਟ ਪਕਾਓ, ਜਾਂ ਕੁੱਕਰ ਵਿੱਚ 2 ਸੀਟੀਆਂ।</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Let the pressure go down fully before you open the cooker.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ASC215</t>
+          <t>ASC115</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wash the spinach well. Put it into boiling water for 2 minutes, then straight into cold water. This keeps it green.</t>
+          <t>Leave it covered for 5 minutes off the heat, fluff with a fork and serve with raita.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Palak achhe se dho lo. Ubalte paani mein 2 minute daalo, phir turant thande paani mein. Isse rang hara rehta hai.</t>
+          <t>Gas band karke 5 minute dhaka rehne do, kaante se khol ke raite ke saath khao.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>पालक अच्छे से धो लो। उबलते पानी में 2 मिनट डालो, फिर तुरंत ठंडे पानी में। इससे रंग हरा रहता है।</t>
+          <t>गैस बंद करके 5 मिनट ढका रहने दो, काँटे से खोलकर रायते के साथ खाओ।</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ਪਾਲਕ ਚੰਗੀ ਤਰ੍ਹਾਂ ਧੋ ਲਓ। ਉਬਲਦੇ ਪਾਣੀ ਵਿੱਚ 2 ਮਿੰਟ ਪਾਓ, ਫਿਰ ਝੱਟ ਠੰਡੇ ਪਾਣੀ ਵਿੱਚ। ਇਸ ਨਾਲ ਰੰਗ ਹਰਾ ਰਹਿੰਦਾ ਹੈ।</t>
+          <t>ਗੈਸ ਬੰਦ ਕਰਕੇ 5 ਮਿੰਟ ਢੱਕਿਆ ਰਹਿਣ ਦਿਓ, ਕਾਂਟੇ ਨਾਲ ਖੋਲ੍ਹ ਕੇ ਰਾਇਤੇ ਨਾਲ ਖਾਓ।</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ASC215</t>
+          <t>ASC117</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Grind the spinach with the ginger and garlic into a smooth puree.</t>
+          <t>Wash the rice and soak it for 20 minutes. Rinse the moong sprouts, dice the carrot and slice the onion.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Palak ko adrak aur lehsun ke saath mixie mein pees ke smooth puree bana lo.</t>
+          <t>Chawal dho ke 20 minute bhigo do. Moong sprouts dho lo, gajar chhoti kaato aur pyaaz lambe kaato.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>पालक को अदरक और लहसुन के साथ मिक्सी में पीसकर चिकनी प्यूरी बना लो।</t>
+          <t>चावल धोकर 20 मिनट भिगो दो। अंकुरित मूंग धो लो, गाजर छोटी काटो और प्याज़ लंबे काटो।</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ਪਾਲਕ ਨੂੰ ਅਦਰਕ ਅਤੇ ਲਸਣ ਨਾਲ ਮਿਕਸੀ ਵਿੱਚ ਪੀਸ ਕੇ ਮੁਲਾਇਮ ਪਿਊਰੀ ਬਣਾ ਲਓ।</t>
-        </is>
+          <t>ਚੌਲ ਧੋ ਕੇ 20 ਮਿੰਟ ਭਿਓਂ ਦਿਓ। ਪੁੰਗਰੀ ਮੂੰਗੀ ਧੋ ਲਓ, ਗਾਜਰ ਛੋਟੀ ਕੱਟੋ ਅਤੇ ਪਿਆਜ਼ ਲੰਮਾ ਕੱਟੋ।</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>20</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ASC215</t>
+          <t>ASC117</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Heat the ghee and add cumin. When it crackles add the onion and cook until soft. Add the tomato, red chilli powder and salt and cook until mushy, about 4 minutes.</t>
+          <t>Heat the ghee or oil and add the bay leaf, cumin, black cardamom, cloves and cinnamon. Fry the onion until light golden.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ghee garam karke jeera daalo. Chatakne lage to pyaaz daal ke naram hone tak pakao. Tamatar, laal mirch aur namak daal ke gal jaane tak pakao, lagbhag 4 minute.</t>
+          <t>Ghee ya tel garam karke tej patta, jeera, badi elaichi, laung aur dalchini daalo. Pyaaz halka sunehra hone tak bhuno.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>घी गरम करके जीरा डालो। चटकने लगे तो प्याज़ डालकर नरम होने तक पकाओ। टमाटर, लाल मिर्च और नमक डालकर गलने तक पकाओ, लगभग 4 मिनट।</t>
+          <t>घी या तेल गरम करके तेज पत्ता, जीरा, बड़ी इलायची, लौंग और दालचीनी डालो। प्याज़ हल्का सुनहरा होने तक भूनो।</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ਘਿਓ ਗਰਮ ਕਰਕੇ ਜੀਰਾ ਪਾਓ। ਤਿੜਕਣ ਲੱਗੇ ਤਾਂ ਪਿਆਜ਼ ਪਾ ਕੇ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ। ਟਮਾਟਰ, ਲਾਲ ਮਿਰਚ ਅਤੇ ਲੂਣ ਪਾ ਕੇ ਗਲਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 4 ਮਿੰਟ।</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>4</v>
+          <t>ਘਿਓ ਜਾਂ ਤੇਲ ਗਰਮ ਕਰਕੇ ਤੇਜ ਪੱਤਾ, ਜੀਰਾ, ਵੱਡੀ ਇਲਾਇਚੀ, ਲੌਂਗ ਅਤੇ ਦਾਲਚੀਨੀ ਪਾਓ। ਪਿਆਜ਼ ਹਲਕਾ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ।</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ASC215</t>
+          <t>ASC117</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Add the spinach puree and a tablespoon of water. Cook for 3 minutes, stirring.</t>
+          <t>Add the sprouts and carrot and stir for 2 minutes. Add the drained rice and salt and mix gently.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Palak ki puree aur ek chammach paani daalo. 3 minute chalaate hue pakao.</t>
+          <t>Sprouts aur gajar daal ke 2 minute chalao. Paani nikaale chawal aur namak daal ke halke se milao.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>पालक की प्यूरी और एक चम्मच पानी डालो। 3 मिनट चलाते हुए पकाओ।</t>
+          <t>अंकुरित मूंग और गाजर डालकर 2 मिनट चलाओ। पानी निकाले चावल और नमक डालकर हल्के से मिलाओ।</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ਪਾਲਕ ਦੀ ਪਿਊਰੀ ਅਤੇ ਇੱਕ ਚਮਚ ਪਾਣੀ ਪਾਓ। 3 ਮਿੰਟ ਹਿਲਾਉਂਦੇ ਹੋਏ ਪਕਾਓ।</t>
+          <t>ਪੁੰਗਰੀ ਮੂੰਗੀ ਅਤੇ ਗਾਜਰ ਪਾ ਕੇ 2 ਮਿੰਟ ਹਿਲਾਓ। ਪਾਣੀ ਕੱਢੇ ਚੌਲ ਅਤੇ ਲੂਣ ਪਾ ਕੇ ਹੌਲੀ ਜਿਹੇ ਮਿਲਾਓ।</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ASC215</t>
+          <t>ASC117</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Add the paneer cubes and garam masala and simmer for 2 minutes. Serve hot with roti.</t>
+          <t>Add 160 ml water, bring to a boil, then cover and cook on the lowest heat for 12 minutes, or 2 whistles in a cooker.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Paneer ke tukde aur garam masala daal ke 2 minute halki aanch pe pakao. Garam garam roti ke saath khao.</t>
+          <t>160 ml paani daal ke ubaal aane do, phir dhak ke sabse dheemi aanch pe 12 minute pakao, ya cooker mein 2 seeti.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>पनीर के टुकड़े और गरम मसाला डालकर 2 मिनट हल्की आँच पर पकाओ। गरमागरम रोटी के साथ खाओ।</t>
+          <t>160 ml पानी डालकर उबाल आने दो, फिर ढककर सबसे धीमी आँच पर 12 मिनट पकाओ, या कुकर में 2 सीटी।</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ਪਨੀਰ ਦੇ ਟੁਕੜੇ ਅਤੇ ਗਰਮ ਮਸਾਲਾ ਪਾ ਕੇ 2 ਮਿੰਟ ਹਲਕੀ ਅੱਗ ਤੇ ਪਕਾਓ। ਗਰਮਾ-ਗਰਮ ਰੋਟੀ ਨਾਲ ਖਾਓ।</t>
+          <t>160 ml ਪਾਣੀ ਪਾ ਕੇ ਉਬਾਲ ਆਉਣ ਦਿਓ, ਫਿਰ ਢੱਕ ਕੇ ਸਭ ਤੋਂ ਹੌਲੀ ਅੱਗ ਤੇ 12 ਮਿੰਟ ਪਕਾਓ, ਜਾਂ ਕੁੱਕਰ ਵਿੱਚ 2 ਸੀਟੀਆਂ।</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Let the pressure go down fully before you open the cooker.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ASC240</t>
+          <t>ASC117</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wash the chicken. Mix it with the curd, turmeric and salt and leave it for 15 minutes.</t>
+          <t>Leave it covered for 5 minutes off the heat, fluff it up and serve with curd.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Chicken dho lo. Dahi, haldi aur namak mila ke 15 minute rakh do.</t>
+          <t>Gas band karke 5 minute dhaka rehne do, khol ke dahi ke saath khao.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>चिकन धो लो। दही, हल्दी और नमक मिलाकर 15 मिनट रख दो।</t>
+          <t>गैस बंद करके 5 मिनट ढका रहने दो, खोलकर दही के साथ खाओ।</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ਚਿਕਨ ਧੋ ਲਓ। ਦਹੀਂ, ਹਲਦੀ ਅਤੇ ਲੂਣ ਮਿਲਾ ਕੇ 15 ਮਿੰਟ ਰੱਖ ਦਿਓ।</t>
+          <t>ਗੈਸ ਬੰਦ ਕਰਕੇ 5 ਮਿੰਟ ਢੱਕਿਆ ਰਹਿਣ ਦਿਓ, ਖੋਲ੍ਹ ਕੇ ਦਹੀਂ ਨਾਲ ਖਾਓ।</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>15</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Wash your hands, knife and board with soap after touching raw chicken.</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ASC240</t>
+          <t>ASC118</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Heat the ghee or oil and add the bay leaf, cardamom, cloves, cinnamon, peppercorns and cumin. Add the onion and fry until deep golden, about 8 minutes.</t>
+          <t>Wash the rice and soak it for 20 minutes. Cut the paneer into cubes and slice the onion.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ghee ya tel garam karke tej patta, elaichi, laung, dalchini, kali mirch aur jeera daalo. Pyaaz daal ke gehra sunehra hone tak bhuno, lagbhag 8 minute.</t>
+          <t>Chawal dho ke 20 minute bhigo do. Paneer ke tukde karo aur pyaaz lambe kaato.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>घी या तेल गरम करके तेज पत्ता, इलायची, लौंग, दालचीनी, काली मिर्च और जीरा डालो। प्याज़ डालकर गहरा सुनहरा होने तक भूनो, लगभग 8 मिनट।</t>
+          <t>चावल धोकर 20 मिनट भिगो दो। पनीर के टुकड़े करो और प्याज़ लंबे काटो।</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ਘਿਓ ਜਾਂ ਤੇਲ ਗਰਮ ਕਰਕੇ ਤੇਜ ਪੱਤਾ, ਇਲਾਇਚੀ, ਲੌਂਗ, ਦਾਲਚੀਨੀ, ਕਾਲੀ ਮਿਰਚ ਅਤੇ ਜੀਰਾ ਪਾਓ। ਪਿਆਜ਼ ਪਾ ਕੇ ਗੂੜ੍ਹਾ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ, ਲਗਭਗ 8 ਮਿੰਟ।</t>
+          <t>ਚੌਲ ਧੋ ਕੇ 20 ਮਿੰਟ ਭਿਓਂ ਦਿਓ। ਪਨੀਰ ਦੇ ਟੁਕੜੇ ਕਰੋ ਅਤੇ ਪਿਆਜ਼ ਲੰਮਾ ਕੱਟੋ।</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ASC240</t>
+          <t>ASC118</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Add the ginger and garlic for a minute. Add the tomatoes, coriander powder, red chilli powder and ground poppy seeds, and cook until oil shows at the sides, about 5 minutes.</t>
+          <t>Fry the paneer cubes in a little ghee until golden at the edges and keep them aside.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Adrak lehsun daal ke ek minute chalao. Tamatar, dhaniya powder, laal mirch aur pisi khaskhas daal ke kinaaron pe tel dikhne tak pakao, lagbhag 5 minute.</t>
+          <t>Paneer ke tukde thode ghee mein kinaaron se sunehre hone tak sek ke alag rakh do.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>अदरक लहसुन डालकर एक मिनट चलाओ। टमाटर, धनिया पाउडर, लाल मिर्च और पिसी खसखस डालकर किनारों पर तेल दिखने तक पकाओ, लगभग 5 मिनट।</t>
+          <t>पनीर के टुकड़े थोड़े घी में किनारों से सुनहरे होने तक सेककर अलग रख दो।</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ਅਦਰਕ ਲਸਣ ਪਾ ਕੇ ਇੱਕ ਮਿੰਟ ਹਿਲਾਓ। ਟਮਾਟਰ, ਧਨੀਆ ਪਾਊਡਰ, ਲਾਲ ਮਿਰਚ ਅਤੇ ਪੀਸੀ ਖਸਖਸ ਪਾ ਕੇ ਕਿਨਾਰਿਆਂ ਤੇ ਤੇਲ ਦਿਸਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 5 ਮਿੰਟ।</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>5</v>
+          <t>ਪਨੀਰ ਦੇ ਟੁਕੜੇ ਥੋੜ੍ਹੇ ਘਿਓ ਵਿੱਚ ਕਿਨਾਰਿਆਂ ਤੋਂ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਸੇਕ ਕੇ ਵੱਖਰੇ ਰੱਖ ਦਿਓ।</t>
+        </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ASC240</t>
+          <t>ASC118</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Add the chicken and fry on high heat for 5 minutes until it changes colour.</t>
+          <t>In the same pan add the bay leaf, cumin, black cardamom, cloves and cinnamon. Fry the onion until light golden.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Chicken daal ke tez aanch pe 5 minute bhuno, jab tak rang badal jaaye.</t>
+          <t>Usi pan mein tej patta, jeera, badi elaichi, laung aur dalchini daalo. Pyaaz halka sunehra hone tak bhuno.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>चिकन डालकर तेज़ आँच पर 5 मिनट भूनो, जब तक रंग बदल जाए।</t>
+          <t>उसी पैन में तेज पत्ता, जीरा, बड़ी इलायची, लौंग और दालचीनी डालो। प्याज़ हल्का सुनहरा होने तक भूनो।</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ਚਿਕਨ ਪਾ ਕੇ ਤੇਜ਼ ਅੱਗ ਤੇ 5 ਮਿੰਟ ਭੁੰਨੋ, ਜਦੋਂ ਤੱਕ ਰੰਗ ਬਦਲ ਜਾਵੇ।</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>5</v>
+          <t>ਉਸੇ ਪੈਨ ਵਿੱਚ ਤੇਜ ਪੱਤਾ, ਜੀਰਾ, ਵੱਡੀ ਇਲਾਇਚੀ, ਲੌਂਗ ਅਤੇ ਦਾਲਚੀਨੀ ਪਾਓ। ਪਿਆਜ਼ ਹਲਕਾ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ।</t>
+        </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ASC240</t>
+          <t>ASC118</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Add 1 cup water, cover and simmer for 20 minutes, or 3 whistles in a cooker, until the chicken is cooked through.</t>
+          <t>Add the drained rice and salt, stir gently, then add 160 ml water. Bring to a boil, cover and cook on the lowest heat for 12 minutes.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1 cup paani daal ke dhak do aur 20 minute halki aanch pe pakao, ya cooker mein 3 seeti, jab tak chicken andar tak pak jaaye.</t>
+          <t>Paani nikaale chawal aur namak daal ke halke se milao, phir 160 ml paani daalo. Ubaal aane pe dhak ke sabse dheemi aanch pe 12 minute pakao.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1 कप पानी डालकर ढक दो और 20 मिनट हल्की आँच पर पकाओ, या कुकर में 3 सीटी, जब तक चिकन अंदर तक पक जाए।</t>
+          <t>पानी निकाले चावल और नमक डालकर हल्के से मिलाओ, फिर 160 ml पानी डालो। उबाल आने पर ढककर सबसे धीमी आँच पर 12 मिनट पकाओ।</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1 ਕੱਪ ਪਾਣੀ ਪਾ ਕੇ ਢੱਕ ਦਿਓ ਅਤੇ 20 ਮਿੰਟ ਹਲਕੀ ਅੱਗ ਤੇ ਪਕਾਓ, ਜਾਂ ਕੁੱਕਰ ਵਿੱਚ 3 ਸੀਟੀਆਂ, ਜਦੋਂ ਤੱਕ ਚਿਕਨ ਅੰਦਰ ਤੱਕ ਪੱਕ ਜਾਵੇ।</t>
+          <t>ਪਾਣੀ ਕੱਢੇ ਚੌਲ ਅਤੇ ਲੂਣ ਪਾ ਕੇ ਹੌਲੀ ਜਿਹੇ ਮਿਲਾਓ, ਫਿਰ 160 ml ਪਾਣੀ ਪਾਓ। ਉਬਾਲ ਆਉਣ ਤੇ ਢੱਕ ਕੇ ਸਭ ਤੋਂ ਹੌਲੀ ਅੱਗ ਤੇ 12 ਮਿੰਟ ਪਕਾਓ।</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>20</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Cut the thickest piece: it must be white all through, with no pink inside.</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ASC240</t>
+          <t>ASC118</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Stir in the garam masala, top with coriander and serve with rice or roti.</t>
+          <t>Gently fold in the paneer, cover and leave off the heat for 5 minutes. Serve with raita.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Garam masala milao, dhaniya daalo aur chawal ya roti ke saath khao.</t>
+          <t>Paneer halke haath se milao, dhak ke gas band karke 5 minute chhod do. Raite ke saath khao.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>गरम मसाला मिलाओ, हरा धनिया डालो और चावल या रोटी के साथ खाओ।</t>
+          <t>पनीर हल्के हाथ से मिलाओ, ढककर गैस बंद करके 5 मिनट छोड़ दो। रायते के साथ खाओ।</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ਗਰਮ ਮਸਾਲਾ ਮਿਲਾਓ, ਹਰਾ ਧਨੀਆ ਪਾਓ ਅਤੇ ਚੌਲਾਂ ਜਾਂ ਰੋਟੀ ਨਾਲ ਖਾਓ।</t>
-        </is>
+          <t>ਪਨੀਰ ਹੌਲੀ ਹੱਥ ਨਾਲ ਮਿਲਾਓ, ਢੱਕ ਕੇ ਗੈਸ ਬੰਦ ਕਰਕੇ 5 ਮਿੰਟ ਛੱਡ ਦਿਓ। ਰਾਇਤੇ ਨਾਲ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>5</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BFP039</t>
+          <t>ASC123</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -80530,33 +80648,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dry roast the suji on low heat, stirring, until it smells nutty and turns light golden, about 4 minutes. Take it out.</t>
+          <t>Wash the rice and soak it for 30 minutes. Soak the saffron in the warm milk. Cut all the vegetables into small pieces and slice the onion thin.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Suji ko dheemi aanch pe chalaate hue bhuno, jab tak khushboo aaye aur halki sunehri ho jaaye, lagbhag 4 minute. Nikaal lo.</t>
+          <t>Chawal dho ke 30 minute bhigo do. Kesar ko garam doodh mein bhigo do. Saari sabziyan chhoti kaato aur pyaaz patla lamba kaato.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>सूजी को धीमी आँच पर चलाते हुए भूनो, जब तक खुशबू आए और हल्की सुनहरी हो जाए, लगभग 4 मिनट। निकाल लो।</t>
+          <t>चावल धोकर 30 मिनट भिगो दो। केसर को गरम दूध में भिगो दो। सारी सब्ज़ियाँ छोटी काटो और प्याज़ पतला लंबा काटो।</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ਸੂਜੀ ਨੂੰ ਹੌਲੀ ਅੱਗ ਤੇ ਹਿਲਾਉਂਦੇ ਹੋਏ ਭੁੰਨੋ, ਜਦੋਂ ਤੱਕ ਖੁਸ਼ਬੂ ਆਵੇ ਅਤੇ ਹਲਕੀ ਸੁਨਹਿਰੀ ਹੋ ਜਾਵੇ, ਲਗਭਗ 4 ਮਿੰਟ। ਕੱਢ ਲਓ।</t>
+          <t>ਚੌਲ ਧੋ ਕੇ 30 ਮਿੰਟ ਭਿਓਂ ਦਿਓ। ਕੇਸਰ ਨੂੰ ਗਰਮ ਦੁੱਧ ਵਿੱਚ ਭਿਓਂ ਦਿਓ। ਸਾਰੀਆਂ ਸਬਜ਼ੀਆਂ ਛੋਟੀਆਂ ਕੱਟੋ ਅਤੇ ਪਿਆਜ਼ ਪਤਲਾ ਲੰਮਾ ਕੱਟੋ।</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BFP039</t>
+          <t>ASC123</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -80564,30 +80682,37 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Heat the oil. Add mustard seeds and urad dal and fry until the dal is golden. Add the dry red chilli, hing and curry leaves.</t>
+          <t>Boil plenty of water with salt and a bay leaf. Add the rice and cook until it is three-quarters done, about 6 minutes. Drain.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Tel garam karo. Rai aur urad dal daal ke dal sunehri hone tak bhuno. Sukhi laal mirch, hing aur kadi patta daalo.</t>
+          <t>Khoob paani mein namak aur tej patta daal ke ubaalo. Chawal daal ke teen-chauthai pakne tak, lagbhag 6 minute, ubaalo. Paani nitaar do.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>तेल गरम करो। राई और उड़द दाल डालकर दाल सुनहरी होने तक भूनो। सूखी लाल मिर्च, हींग और कड़ी पत्ता डालो।</t>
+          <t>खूब पानी में नमक और तेज पत्ता डालकर उबालो। चावल डालकर तीन-चौथाई पकने तक, लगभग 6 मिनट, उबालो। पानी निथार दो।</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ਤੇਲ ਗਰਮ ਕਰੋ। ਰਾਈ ਅਤੇ ਮਾਂਹ ਦੀ ਦਾਲ ਪਾ ਕੇ ਦਾਲ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ। ਸੁੱਕੀ ਲਾਲ ਮਿਰਚ, ਹਿੰਗ ਅਤੇ ਕੜੀ ਪੱਤਾ ਪਾਓ।</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>ਬਹੁਤੇ ਪਾਣੀ ਵਿੱਚ ਲੂਣ ਅਤੇ ਤੇਜ ਪੱਤਾ ਪਾ ਕੇ ਉਬਾਲੋ। ਚੌਲ ਪਾ ਕੇ ਤਿੰਨ-ਚੌਥਾਈ ਪੱਕਣ ਤੱਕ, ਲਗਭਗ 6 ਮਿੰਟ, ਉਬਾਲੋ। ਪਾਣੀ ਨਿਤਾਰ ਦਿਓ।</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Lower things into boiling water gently with a spoon, so it does not splash.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BFP039</t>
+          <t>ASC123</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -80595,22 +80720,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Add the chopped onion, green chilli and ginger. Cook until the onion is soft.</t>
+          <t>Heat the ghee and fry half the onion until brown and crisp. Take it out for the top.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Kata pyaaz, hari mirch aur adrak daal ke pyaaz naram hone tak pakao.</t>
+          <t>Ghee garam karke aadha pyaaz bhoora aur crispy hone tak talo. Upar daalne ke liye nikaal lo.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>कटा प्याज़, हरी मिर्च और अदरक डालकर प्याज़ नरम होने तक पकाओ।</t>
+          <t>घी गरम करके आधा प्याज़ भूरा और कुरकुरा होने तक तलो। ऊपर डालने के लिए निकाल लो।</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ਕੱਟਿਆ ਪਿਆਜ਼, ਹਰੀ ਮਿਰਚ ਅਤੇ ਅਦਰਕ ਪਾ ਕੇ ਪਿਆਜ਼ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ।</t>
+          <t>ਘਿਓ ਗਰਮ ਕਰਕੇ ਅੱਧਾ ਪਿਆਜ਼ ਭੂਰਾ ਅਤੇ ਕਰਾਰਾ ਹੋਣ ਤੱਕ ਤਲੋ। ਉੱਤੇ ਪਾਉਣ ਲਈ ਕੱਢ ਲਓ।</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -80618,7 +80743,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BFP039</t>
+          <t>ASC123</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -80626,30 +80751,33 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pour in 100 ml water, add salt and red chilli powder, and bring it to a boil.</t>
+          <t>In the same ghee add cumin, cloves, cardamom, cinnamon and peppercorns, then the rest of the onion, ginger and garlic. Add the vegetables, tomato, turmeric, red chilli, salt and curd, and cook until the vegetables are almost soft, about 8 minutes.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>100 ml paani daalo, namak aur laal mirch daal ke ubaal aane do.</t>
+          <t>Usi ghee mein jeera, laung, elaichi, dalchini aur kali mirch daalo, phir baaki pyaaz, adrak aur lehsun. Sabziyan, tamatar, haldi, laal mirch, namak aur dahi daal ke lagbhag naram hone tak pakao, lagbhag 8 minute.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>100 ml पानी डालो, नमक और लाल मिर्च डालकर उबाल आने दो।</t>
+          <t>उसी घी में जीरा, लौंग, इलायची, दालचीनी और काली मिर्च डालो, फिर बाकी प्याज़, अदरक और लहसुन। सब्ज़ियाँ, टमाटर, हल्दी, लाल मिर्च, नमक और दही डालकर लगभग नरम होने तक पकाओ, लगभग 8 मिनट।</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>100 ml ਪਾਣੀ ਪਾਓ, ਲੂਣ ਅਤੇ ਲਾਲ ਮਿਰਚ ਪਾ ਕੇ ਉਬਾਲ ਆਉਣ ਦਿਓ।</t>
-        </is>
+          <t>ਉਸੇ ਘਿਓ ਵਿੱਚ ਜੀਰਾ, ਲੌਂਗ, ਇਲਾਇਚੀ, ਦਾਲਚੀਨੀ ਅਤੇ ਕਾਲੀ ਮਿਰਚ ਪਾਓ, ਫਿਰ ਬਾਕੀ ਪਿਆਜ਼, ਅਦਰਕ ਅਤੇ ਲਸਣ। ਸਬਜ਼ੀਆਂ, ਟਮਾਟਰ, ਹਲਦੀ, ਲਾਲ ਮਿਰਚ, ਲੂਣ ਅਤੇ ਦਹੀਂ ਪਾ ਕੇ ਲਗਭਗ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 8 ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>8</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BFP039</t>
+          <t>ASC123</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -80657,37 +80785,33 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turn the heat low. Add the roasted suji slowly while stirring all the time so no lumps form. Cover and cook for 2 minutes.</t>
+          <t>Spread the rice over the vegetables. Pour the saffron milk on top, scatter the fried onion, cover tightly and cook on the lowest heat for 15 minutes.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Aanch dheemi karo. Bhuni suji dheere dheere daalo aur lagaataar chalaate raho taaki gutliyaan na banein. Dhak ke 2 minute pakao.</t>
+          <t>Sabziyon ke upar chawal ki parat bichha do. Upar kesar wala doodh aur tala pyaaz daalo, kas ke dhak do aur sabse dheemi aanch pe 15 minute dum pe pakao.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>आँच धीमी करो। भुनी सूजी धीरे-धीरे डालो और लगातार चलाते रहो ताकि गुठलियाँ न बनें। ढककर 2 मिनट पकाओ।</t>
+          <t>सब्ज़ियों के ऊपर चावल की परत बिछा दो। ऊपर केसर वाला दूध और तला प्याज़ डालो, कसकर ढक दो और सबसे धीमी आँच पर 15 मिनट दम पर पकाओ।</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ਅੱਗ ਹੌਲੀ ਕਰੋ। ਭੁੰਨੀ ਸੂਜੀ ਹੌਲੀ-ਹੌਲੀ ਪਾਓ ਅਤੇ ਲਗਾਤਾਰ ਹਿਲਾਉਂਦੇ ਰਹੋ ਤਾਂ ਜੋ ਗੰਢਾਂ ਨਾ ਬਣਨ। ਢੱਕ ਕੇ 2 ਮਿੰਟ ਪਕਾਓ।</t>
+          <t>ਸਬਜ਼ੀਆਂ ਉੱਤੇ ਚੌਲਾਂ ਦੀ ਤਹਿ ਵਿਛਾ ਦਿਓ। ਉੱਤੇ ਕੇਸਰ ਵਾਲਾ ਦੁੱਧ ਅਤੇ ਤਲਿਆ ਪਿਆਜ਼ ਪਾਓ, ਘੁੱਟ ਕੇ ਢੱਕ ਦਿਓ ਅਤੇ ਸਭ ਤੋਂ ਹੌਲੀ ਅੱਗ ਤੇ 15 ਮਿੰਟ ਦਮ ਤੇ ਪਕਾਓ।</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>It splutters while it cooks. Keep your hand back and stir with a long spoon.</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BFP039</t>
+          <t>ASC123</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -80695,30 +80819,33 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Squeeze in the lemon, sprinkle coriander and serve hot.</t>
+          <t>Leave it closed for 5 minutes, then mix gently from the bottom and serve with raita.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Nimbu nichodo, dhaniya daalo aur garam garam khao.</t>
+          <t>5 minute band rehne do, phir neeche se halke haath se milao aur raite ke saath khao.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>नींबू निचोड़ो, हरा धनिया डालो और गरमागरम खाओ।</t>
+          <t>5 मिनट बंद रहने दो, फिर नीचे से हल्के हाथ से मिलाओ और रायते के साथ खाओ।</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ਨਿੰਬੂ ਨਿਚੋੜੋ, ਹਰਾ ਧਨੀਆ ਪਾਓ ਅਤੇ ਗਰਮਾ-ਗਰਮ ਖਾਓ।</t>
-        </is>
+          <t>5 ਮਿੰਟ ਬੰਦ ਰਹਿਣ ਦਿਓ, ਫਿਰ ਹੇਠੋਂ ਹੌਲੀ ਹੱਥ ਨਾਲ ਮਿਲਾਓ ਅਤੇ ਰਾਇਤੇ ਨਾਲ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>5</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BFP044</t>
+          <t>ASC144</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -80726,33 +80853,30 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Rinse the poha in a strainer under running water and drain. Mix in the turmeric and salt and leave it for 5 minutes to soften.</t>
+          <t>Wash the rice and urad dal and soak them separately for 6 hours.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Poha ko chhalni mein paani se dho ke paani nikaal do. Haldi aur namak mila ke 5 minute naram hone do.</t>
+          <t>Chawal aur urad dal dho ke alag alag 6 ghante bhigo do.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>पोहे को छलनी में पानी से धोकर पानी निकाल दो। हल्दी और नमक मिलाकर 5 मिनट नरम होने दो।</t>
+          <t>चावल और उड़द दाल धोकर अलग-अलग 6 घंटे भिगो दो।</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ਪੋਹੇ ਨੂੰ ਛਾਨਣੀ ਵਿੱਚ ਪਾਣੀ ਨਾਲ ਧੋ ਕੇ ਪਾਣੀ ਕੱਢ ਦਿਓ। ਹਲਦੀ ਅਤੇ ਲੂਣ ਮਿਲਾ ਕੇ 5 ਮਿੰਟ ਨਰਮ ਹੋਣ ਦਿਓ।</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>5</v>
+          <t>ਚੌਲ ਅਤੇ ਮਾਂਹ ਦੀ ਦਾਲ ਧੋ ਕੇ ਵੱਖ-ਵੱਖ 6 ਘੰਟੇ ਭਿਓਂ ਦਿਓ।</t>
+        </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BFP044</t>
+          <t>ASC144</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -80760,22 +80884,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Heat the oil in a pan and fry the peanuts until crunchy. Take them out.</t>
+          <t>Grind the urad dal with a little water until light and fluffy. Grind the rice a little coarse. Mix both with salt into a thick batter.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Kadhai mein tel garam karke moongphali crunchy hone tak bhuno aur nikaal lo.</t>
+          <t>Urad dal ko thode paani ke saath halka aur phoola hone tak pees lo. Chawal thoda mota peeso. Dono ko namak ke saath mila ke gaadha ghol bana lo.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>कड़ाही में तेल गरम करके मूंगफली कुरकुरी होने तक भूनो और निकाल लो।</t>
+          <t>उड़द दाल को थोड़े पानी के साथ हल्का और फूला होने तक पीस लो। चावल थोड़ा मोटा पीसो। दोनों को नमक के साथ मिलाकर गाढ़ा घोल बना लो।</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ਕੜਾਹੀ ਵਿੱਚ ਤੇਲ ਗਰਮ ਕਰਕੇ ਮੂੰਗਫਲੀ ਕਰਾਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ ਅਤੇ ਕੱਢ ਲਓ।</t>
+          <t>ਮਾਂਹ ਦੀ ਦਾਲ ਨੂੰ ਥੋੜ੍ਹੇ ਪਾਣੀ ਨਾਲ ਹਲਕਾ ਅਤੇ ਫੁੱਲਿਆ ਹੋਣ ਤੱਕ ਪੀਸ ਲਓ। ਚੌਲ ਥੋੜ੍ਹਾ ਮੋਟਾ ਪੀਸੋ। ਦੋਵਾਂ ਨੂੰ ਲੂਣ ਨਾਲ ਮਿਲਾ ਕੇ ਗਾੜ੍ਹਾ ਘੋਲ ਬਣਾ ਲਓ।</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -80783,7 +80907,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BFP044</t>
+          <t>ASC144</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -80791,33 +80915,30 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>In the same oil add mustard seeds. When they crackle add hing, curry leaves and green chilli, then the small potato cubes. Cover and cook on low heat until soft, about 5 minutes.</t>
+          <t>Cover and leave the batter in a warm place for 8 to 12 hours, until it rises and smells a little sour.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Usi tel mein rai daalo. Chatakne lage to hing, kadi patta aur hari mirch daalo, phir chhote kate aloo. Dhak ke dheemi aanch pe 5 minute naram hone tak pakao.</t>
+          <t>Dhak ke ghol ko garam jagah 8 se 12 ghante rakho, jab tak phool jaaye aur halki khatti khushboo aaye.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>उसी तेल में राई डालो। चटकने लगे तो हींग, कड़ी पत्ता और हरी मिर्च डालो, फिर छोटे कटे आलू। ढककर धीमी आँच पर 5 मिनट नरम होने तक पकाओ।</t>
+          <t>ढककर घोल को गरम जगह 8 से 12 घंटे रखो, जब तक फूल जाए और हल्की खट्टी खुशबू आए।</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ਉਸੇ ਤੇਲ ਵਿੱਚ ਰਾਈ ਪਾਓ। ਤਿੜਕਣ ਲੱਗੇ ਤਾਂ ਹਿੰਗ, ਕੜੀ ਪੱਤਾ ਅਤੇ ਹਰੀ ਮਿਰਚ ਪਾਓ, ਫਿਰ ਛੋਟੇ ਕੱਟੇ ਆਲੂ। ਢੱਕ ਕੇ ਹੌਲੀ ਅੱਗ ਤੇ 5 ਮਿੰਟ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ।</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>5</v>
+          <t>ਢੱਕ ਕੇ ਘੋਲ ਨੂੰ ਗਰਮ ਥਾਂ 8 ਤੋਂ 12 ਘੰਟੇ ਰੱਖੋ, ਜਦੋਂ ਤੱਕ ਫੁੱਲ ਜਾਵੇ ਅਤੇ ਹਲਕੀ ਖੱਟੀ ਖੁਸ਼ਬੂ ਆਵੇ।</t>
+        </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BFP044</t>
+          <t>ASC144</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -80825,33 +80946,33 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Add the poha and red chilli powder. Mix gently so the poha does not break, cover and steam on low heat for 2 minutes.</t>
+          <t>Grease the idli moulds, fill them three-quarters with batter and steam for 12 minutes.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Poha aur laal mirch daal ke halke haath se milao taaki poha toote nahi. Dhak ke dheemi aanch pe 2 minute rakho.</t>
+          <t>Idli ke saanchon mein tel lagao, teen-chauthai ghol bharo aur 12 minute bhaap mein pakao.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>पोहा और लाल मिर्च डालकर हल्के हाथ से मिलाओ ताकि पोहा टूटे नहीं। ढककर धीमी आँच पर 2 मिनट रखो।</t>
+          <t>इडली के साँचों में तेल लगाओ, तीन-चौथाई घोल भरो और 12 मिनट भाप में पकाओ।</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ਪੋਹਾ ਅਤੇ ਲਾਲ ਮਿਰਚ ਪਾ ਕੇ ਹੌਲੀ ਹੱਥ ਨਾਲ ਮਿਲਾਓ ਤਾਂ ਜੋ ਪੋਹਾ ਟੁੱਟੇ ਨਾ। ਢੱਕ ਕੇ ਹੌਲੀ ਅੱਗ ਤੇ 2 ਮਿੰਟ ਰੱਖੋ।</t>
+          <t>ਇਡਲੀ ਦੇ ਸਾਂਚਿਆਂ ਵਿੱਚ ਤੇਲ ਲਗਾਓ, ਤਿੰਨ-ਚੌਥਾਈ ਘੋਲ ਭਰੋ ਅਤੇ 12 ਮਿੰਟ ਭਾਫ਼ ਵਿੱਚ ਪਕਾਓ।</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BFP044</t>
+          <t>ASC144</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -80859,30 +80980,37 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turn off the heat. Squeeze in the lemon, add the peanuts and coriander, and serve hot.</t>
+          <t>Check with a knife: it should come out clean. Rest 2 minutes, take the idlis out with a wet spoon and serve with chutney or sambar.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Gas band karo. Nimbu nichodo, moongphali aur dhaniya daal ke garam garam khao.</t>
+          <t>Chaaku daal ke dekho, saaf nikle to ban gayi. 2 minute rukh ke geele chammach se idli nikaalo aur chutney ya sambar ke saath khao.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>गैस बंद करो। नींबू निचोड़ो, मूंगफली और हरा धनिया डालकर गरमागरम खाओ।</t>
+          <t>चाकू डालकर देखो, साफ़ निकले तो बन गई। 2 मिनट रुककर गीले चम्मच से इडली निकालो और चटनी या सांभर के साथ खाओ।</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ਗੈਸ ਬੰਦ ਕਰੋ। ਨਿੰਬੂ ਨਿਚੋੜੋ, ਮੂੰਗਫਲੀ ਅਤੇ ਹਰਾ ਧਨੀਆ ਪਾ ਕੇ ਗਰਮਾ-ਗਰਮ ਖਾਓ।</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>ਚਾਕੂ ਪਾ ਕੇ ਵੇਖੋ, ਸਾਫ਼ ਨਿਕਲੇ ਤਾਂ ਬਣ ਗਈ। 2 ਮਿੰਟ ਰੁਕ ਕੇ ਗਿੱਲੇ ਚਮਚ ਨਾਲ ਇਡਲੀ ਕੱਢੋ ਅਤੇ ਚਟਣੀ ਜਾਂ ਸਾਂਭਰ ਨਾਲ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Lower things into boiling water gently with a spoon, so it does not splash.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BFP136</t>
+          <t>ASC146</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -80890,33 +81018,30 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wash the rice 2 or 3 times and soak it in water for 20 minutes.</t>
+          <t>Soak the rice, and separately the urad dal with methi seeds, for 6 hours. Grind them with a little water into a smooth batter, add salt and leave it overnight to ferment.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Chawal 2-3 baar dho ke 20 minute paani mein bhigo do.</t>
+          <t>Chawal, aur alag se urad dal methi dane ke saath, 6 ghante bhigo do. Thode paani ke saath smooth ghol pees lo, namak daalo aur raat bhar khameer uthne do.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>चावल 2-3 बार धोकर 20 मिनट पानी में भिगो दो।</t>
+          <t>चावल, और अलग से उड़द दाल मेथी दाने के साथ, 6 घंटे भिगो दो। थोड़े पानी के साथ चिकना घोल पीस लो, नमक डालो और रात भर खमीर उठने दो।</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ਚੌਲ 2-3 ਵਾਰ ਧੋ ਕੇ 20 ਮਿੰਟ ਪਾਣੀ ਵਿੱਚ ਭਿਓਂ ਦਿਓ।</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>20</v>
+          <t>ਚੌਲ, ਅਤੇ ਵੱਖਰੀ ਮਾਂਹ ਦੀ ਦਾਲ ਮੇਥੀ ਦਾਣੇ ਨਾਲ, 6 ਘੰਟੇ ਭਿਓਂ ਦਿਓ। ਥੋੜ੍ਹੇ ਪਾਣੀ ਨਾਲ ਮੁਲਾਇਮ ਘੋਲ ਪੀਸ ਲਓ, ਲੂਣ ਪਾਓ ਅਤੇ ਰਾਤ ਭਰ ਖਮੀਰ ਉੱਠਣ ਦਿਓ।</t>
+        </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BFP136</t>
+          <t>ASC146</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -80924,22 +81049,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Heat the oil and add the bay leaf, cumin, cardamom, cloves and cinnamon. When they sizzle, add the sliced onion and cook until light golden.</t>
+          <t>For the filling, heat oil, add mustard seeds, chana dal, urad dal, dry red chilli and curry leaves. Add the sliced onion and cook until soft.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tel garam karke tej patta, jeera, elaichi, laung aur dalchini daalo. Chatakne lagein to kata pyaaz daal ke halka sunehra hone tak bhuno.</t>
+          <t>Bharaai ke liye tel garam karke rai, chana dal, urad dal, sukhi laal mirch aur kadi patta daalo. Lamba kata pyaaz daal ke naram hone tak pakao.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>तेल गरम करके तेज पत्ता, जीरा, इलायची, लौंग और दालचीनी डालो। चटकने लगें तो कटा प्याज़ डालकर हल्का सुनहरा होने तक भूनो।</t>
+          <t>भराई के लिए तेल गरम करके राई, चना दाल, उड़द दाल, सूखी लाल मिर्च और कड़ी पत्ता डालो। लंबा कटा प्याज़ डालकर नरम होने तक पकाओ।</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ਤੇਲ ਗਰਮ ਕਰਕੇ ਤੇਜ ਪੱਤਾ, ਜੀਰਾ, ਇਲਾਇਚੀ, ਲੌਂਗ ਅਤੇ ਦਾਲਚੀਨੀ ਪਾਓ। ਤਿੜਕਣ ਲੱਗਣ ਤਾਂ ਕੱਟਿਆ ਪਿਆਜ਼ ਪਾ ਕੇ ਹਲਕਾ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ।</t>
+          <t>ਭਰਾਈ ਲਈ ਤੇਲ ਗਰਮ ਕਰਕੇ ਰਾਈ, ਛੋਲਿਆਂ ਦੀ ਦਾਲ, ਮਾਂਹ ਦੀ ਦਾਲ, ਸੁੱਕੀ ਲਾਲ ਮਿਰਚ ਅਤੇ ਕੜੀ ਪੱਤਾ ਪਾਓ। ਲੰਮਾ ਕੱਟਿਆ ਪਿਆਜ਼ ਪਾ ਕੇ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ।</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -80947,7 +81072,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BFP136</t>
+          <t>ASC146</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -80955,30 +81080,33 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Add the peas, the drained rice and salt. Stir gently for a minute.</t>
+          <t>Add turmeric, salt and the boiled, roughly mashed potatoes. Mix with 2 tablespoons of water and cook for 3 minutes.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Matar, paani nikaale chawal aur namak daalo. Ek minute halke haath se chalao.</t>
+          <t>Haldi, namak aur ubale, mote mash kiye aloo daalo. 2 chammach paani ke saath milao aur 3 minute pakao.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>मटर, पानी निकाले चावल और नमक डालो। एक मिनट हल्के हाथ से चलाओ।</t>
+          <t>हल्दी, नमक और उबले, मोटे मैश किए आलू डालो। 2 चम्मच पानी के साथ मिलाओ और 3 मिनट पकाओ।</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ਮਟਰ, ਪਾਣੀ ਕੱਢੇ ਚੌਲ ਅਤੇ ਲੂਣ ਪਾਓ। ਇੱਕ ਮਿੰਟ ਹੌਲੀ ਹੱਥ ਨਾਲ ਹਿਲਾਓ।</t>
-        </is>
+          <t>ਹਲਦੀ, ਲੂਣ ਅਤੇ ਉਬਲੇ, ਮੋਟੇ ਮੈਸ਼ ਕੀਤੇ ਆਲੂ ਪਾਓ। 2 ਚਮਚ ਪਾਣੀ ਨਾਲ ਮਿਲਾਓ ਅਤੇ 3 ਮਿੰਟ ਪਕਾਓ।</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>3</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BFP136</t>
+          <t>ASC146</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -80986,37 +81114,30 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Add 160 ml water and bring it to a boil. Cover and cook on the lowest heat for 12 minutes, or 2 whistles in a cooker.</t>
+          <t>Heat a tawa well, sprinkle water and wipe it. Pour a ladle of batter in the middle and spread it thin in circles. Drizzle oil around the edge.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>160 ml paani daal ke ubaal aane do. Dhak ke sabse dheemi aanch pe 12 minute pakao, ya cooker mein 2 seeti.</t>
+          <t>Tawa achhe se garam karo, paani chhidak ke ponchh lo. Beech mein ek kalchhi ghol daal ke gol ghumaate hue patla faila do. Kinaaron pe tel daalo.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>160 ml पानी डालकर उबाल आने दो। ढककर सबसे धीमी आँच पर 12 मिनट पकाओ, या कुकर में 2 सीटी।</t>
+          <t>तवा अच्छे से गरम करो, पानी छिड़ककर पोंछ लो। बीच में एक कलछी घोल डालकर गोल घुमाते हुए पतला फैला दो। किनारों पर तेल डालो।</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>160 ml ਪਾਣੀ ਪਾ ਕੇ ਉਬਾਲ ਆਉਣ ਦਿਓ। ਢੱਕ ਕੇ ਸਭ ਤੋਂ ਹੌਲੀ ਅੱਗ ਤੇ 12 ਮਿੰਟ ਪਕਾਓ, ਜਾਂ ਕੁੱਕਰ ਵਿੱਚ 2 ਸੀਟੀਆਂ।</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>12</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Let the pressure go down fully before you open the cooker.</t>
-        </is>
-      </c>
+          <t>ਤਵਾ ਚੰਗੀ ਤਰ੍ਹਾਂ ਗਰਮ ਕਰੋ, ਪਾਣੀ ਛਿੜਕ ਕੇ ਪੂੰਝ ਲਓ। ਵਿੱਚਕਾਰ ਇੱਕ ਕੜਛੀ ਘੋਲ ਪਾ ਕੇ ਗੋਲ ਘੁਮਾਉਂਦੇ ਹੋਏ ਪਤਲਾ ਫੈਲਾ ਦਿਓ। ਕਿਨਾਰਿਆਂ ਤੇ ਤੇਲ ਪਾਓ।</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BFP136</t>
+          <t>ASC146</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -81024,33 +81145,33 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turn off the heat and leave it covered for 5 minutes. Fluff it gently with a fork and serve.</t>
+          <t>Cook until the bottom is golden and crisp, about 2 minutes. Put the potato filling on one half, fold and serve hot with chutney.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Gas band karke 5 minute dhaka rehne do. Kaante se halka sa khol ke serve karo.</t>
+          <t>Neeche se sunehra aur crispy hone tak sekho, lagbhag 2 minute. Aadhe hisse pe aloo masala rakho, mod ke chutney ke saath garam garam khao.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>गैस बंद करके 5 मिनट ढका रहने दो। काँटे से हल्का सा खोलकर परोसो।</t>
+          <t>नीचे से सुनहरा और कुरकुरा होने तक सेको, लगभग 2 मिनट। आधे हिस्से पर आलू मसाला रखो, मोड़कर चटनी के साथ गरमागरम खाओ।</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ਗੈਸ ਬੰਦ ਕਰਕੇ 5 ਮਿੰਟ ਢੱਕਿਆ ਰਹਿਣ ਦਿਓ। ਕਾਂਟੇ ਨਾਲ ਹਲਕਾ ਜਿਹਾ ਖੋਲ੍ਹ ਕੇ ਪਰੋਸੋ।</t>
+          <t>ਹੇਠੋਂ ਸੁਨਹਿਰੀ ਅਤੇ ਕਰਾਰਾ ਹੋਣ ਤੱਕ ਸੇਕੋ, ਲਗਭਗ 2 ਮਿੰਟ। ਅੱਧੇ ਹਿੱਸੇ ਤੇ ਆਲੂ ਮਸਾਲਾ ਰੱਖੋ, ਮੋੜ ਕੇ ਚਟਣੀ ਨਾਲ ਗਰਮਾ-ਗਰਮ ਖਾਓ।</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BFP240</t>
+          <t>ASC147</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -81058,37 +81179,33 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lower the egg gently into boiling water and boil for 10 minutes. Cool it in cold water, peel, and make 2 small cuts on it.</t>
+          <t>Mix the suji, maida, curd, finely chopped onion, green chilli, ginger, curry leaves and salt. Add water to make a thin, runny batter and rest it for 15 minutes.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Anda ubalte paani mein dheere se daalo aur 10 minute ubaalo. Thande paani mein thanda karke chheel lo aur do chhote cheere laga do.</t>
+          <t>Suji, maida, dahi, barik kata pyaaz, hari mirch, adrak, kadi patta aur namak milao. Paani daal ke patla behta ghol banao aur 15 minute rakh do.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>अंडा उबलते पानी में धीरे से डालो और 10 मिनट उबालो। ठंडे पानी में ठंडा करके छील लो और दो छोटे चीरे लगा दो।</t>
+          <t>सूजी, मैदा, दही, बारीक कटा प्याज़, हरी मिर्च, अदरक, कड़ी पत्ता और नमक मिलाओ। पानी डालकर पतला बहता घोल बनाओ और 15 मिनट रख दो।</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ਆਂਡਾ ਉਬਲਦੇ ਪਾਣੀ ਵਿੱਚ ਹੌਲੀ ਜਿਹੇ ਪਾਓ ਅਤੇ 10 ਮਿੰਟ ਉਬਾਲੋ। ਠੰਡੇ ਪਾਣੀ ਵਿੱਚ ਠੰਡਾ ਕਰਕੇ ਛਿੱਲ ਲਓ ਅਤੇ ਦੋ ਛੋਟੇ ਚੀਰੇ ਲਗਾ ਦਿਓ।</t>
+          <t>ਸੂਜੀ, ਮੈਦਾ, ਦਹੀਂ, ਬਾਰੀਕ ਕੱਟਿਆ ਪਿਆਜ਼, ਹਰੀ ਮਿਰਚ, ਅਦਰਕ, ਕੜੀ ਪੱਤਾ ਅਤੇ ਲੂਣ ਮਿਲਾਓ। ਪਾਣੀ ਪਾ ਕੇ ਪਤਲਾ ਵਗਦਾ ਘੋਲ ਬਣਾਓ ਅਤੇ 15 ਮਿੰਟ ਰੱਖ ਦਿਓ।</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>10</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Lower things into boiling water gently with a spoon, so it does not splash.</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BFP240</t>
+          <t>ASC147</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -81096,22 +81213,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Heat the oil and add the bay leaf and cumin. Add the onion and fry until golden, then the ginger, garlic and green chilli for a minute.</t>
+          <t>Stir in the baking soda and, if the batter has thickened, a little more water.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Tel garam karke tej patta aur jeera daalo. Pyaaz daal ke sunehra hone tak bhuno, phir adrak, lehsun aur hari mirch ek minute.</t>
+          <t>Meetha soda milao, aur ghol gaadha ho gaya ho to thoda paani aur.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>तेल गरम करके तेज पत्ता और जीरा डालो। प्याज़ डालकर सुनहरा होने तक भूनो, फिर अदरक, लहसुन और हरी मिर्च एक मिनट।</t>
+          <t>मीठा सोडा मिलाओ, और घोल गाढ़ा हो गया हो तो थोड़ा पानी और।</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ਤੇਲ ਗਰਮ ਕਰਕੇ ਤੇਜ ਪੱਤਾ ਅਤੇ ਜੀਰਾ ਪਾਓ। ਪਿਆਜ਼ ਪਾ ਕੇ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ, ਫਿਰ ਅਦਰਕ, ਲਸਣ ਅਤੇ ਹਰੀ ਮਿਰਚ ਇੱਕ ਮਿੰਟ।</t>
+          <t>ਮਿੱਠਾ ਸੋਡਾ ਮਿਲਾਓ, ਅਤੇ ਘੋਲ ਗਾੜ੍ਹਾ ਹੋ ਗਿਆ ਹੋਵੇ ਤਾਂ ਥੋੜ੍ਹਾ ਪਾਣੀ ਹੋਰ।</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -81119,7 +81236,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BFP240</t>
+          <t>ASC147</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -81127,33 +81244,30 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Add the tomato, turmeric, coriander powder, red chilli powder and salt. Cook until oil shows at the sides, about 5 minutes.</t>
+          <t>Heat a tawa until very hot. Pour the batter from a height all over the tawa, starting from the edges. Do not spread it.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tamatar, haldi, dhaniya powder, laal mirch aur namak daalo. Kinaaron pe tel dikhe tab tak pakao, lagbhag 5 minute.</t>
+          <t>Tawa bahut garam karo. Ghol ko upar se kinaaron se shuru karke poore tawe pe daalo. Failana nahi hai.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>टमाटर, हल्दी, धनिया पाउडर, लाल मिर्च और नमक डालो। किनारों पर तेल दिखे तब तक पकाओ, लगभग 5 मिनट।</t>
+          <t>तवा बहुत गरम करो। घोल को ऊपर से किनारों से शुरू करके पूरे तवे पर डालो। फैलाना नहीं है।</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ਟਮਾਟਰ, ਹਲਦੀ, ਧਨੀਆ ਪਾਊਡਰ, ਲਾਲ ਮਿਰਚ ਅਤੇ ਲੂਣ ਪਾਓ। ਕਿਨਾਰਿਆਂ ਤੇ ਤੇਲ ਦਿਸੇ ਤਦ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 5 ਮਿੰਟ।</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>5</v>
+          <t>ਤਵਾ ਬਹੁਤ ਗਰਮ ਕਰੋ। ਘੋਲ ਨੂੰ ਉੱਪਰੋਂ ਕਿਨਾਰਿਆਂ ਤੋਂ ਸ਼ੁਰੂ ਕਰਕੇ ਪੂਰੇ ਤਵੇ ਤੇ ਪਾਓ। ਫੈਲਾਉਣਾ ਨਹੀਂ ਹੈ।</t>
+        </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BFP240</t>
+          <t>ASC147</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -81161,118 +81275,128 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Add 1 cup water and bring it to a boil. Add the egg and simmer for 5 minutes.</t>
+          <t>Drizzle oil and cook on medium heat until golden and crisp, about 3 minutes. Fold and serve hot with chutney.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1 cup paani daal ke ubaal aane do. Anda daal ke 5 minute halki aanch pe pakao.</t>
+          <t>Tel daal ke medium aanch pe sunehra aur crispy hone tak sekho, lagbhag 3 minute. Mod ke chutney ke saath garam garam khao.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1 कप पानी डालकर उबाल आने दो। अंडा डालकर 5 मिनट हल्की आँच पर पकाओ।</t>
+          <t>तेल डालकर मध्यम आँच पर सुनहरा और कुरकुरा होने तक सेको, लगभग 3 मिनट। मोड़कर चटनी के साथ गरमागरम खाओ।</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1 ਕੱਪ ਪਾਣੀ ਪਾ ਕੇ ਉਬਾਲ ਆਉਣ ਦਿਓ। ਆਂਡਾ ਪਾ ਕੇ 5 ਮਿੰਟ ਹਲਕੀ ਅੱਗ ਤੇ ਪਕਾਓ।</t>
+          <t>ਤੇਲ ਪਾ ਕੇ ਦਰਮਿਆਨੀ ਅੱਗ ਤੇ ਸੁਨਹਿਰੀ ਅਤੇ ਕਰਾਰਾ ਹੋਣ ਤੱਕ ਸੇਕੋ, ਲਗਭਗ 3 ਮਿੰਟ। ਮੋੜ ਕੇ ਚਟਣੀ ਨਾਲ ਗਰਮਾ-ਗਰਮ ਖਾਓ।</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BFP240</t>
+          <t>ASC155</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Stir in the garam masala, top with coriander and serve with rice or roti.</t>
+          <t>Wash the chana dal, urad and moong together and soak them for 30 minutes.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Garam masala milao, dhaniya daalo aur chawal ya roti ke saath khao.</t>
+          <t>Chana dal, urad aur moong ek saath dho ke 30 minute bhigo do.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>गरम मसाला मिलाओ, हरा धनिया डालो और चावल या रोटी के साथ खाओ।</t>
+          <t>चना दाल, उड़द और मूंग एक साथ धोकर 30 मिनट भिगो दो।</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ਗਰਮ ਮਸਾਲਾ ਮਿਲਾਓ, ਹਰਾ ਧਨੀਆ ਪਾਓ ਅਤੇ ਚੌਲਾਂ ਜਾਂ ਰੋਟੀ ਨਾਲ ਖਾਓ।</t>
-        </is>
+          <t>ਛੋਲਿਆਂ ਦੀ ਦਾਲ, ਮਾਂਹ ਅਤੇ ਮੂੰਗੀ ਇਕੱਠੀਆਂ ਧੋ ਕੇ 30 ਮਿੰਟ ਭਿਓਂ ਦਿਓ।</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>30</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>OSR100</t>
+          <t>ASC155</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chop the onion, tomato, green chilli, ginger and coriander very finely.</t>
+          <t>Pressure cook them with 1 cup water, turmeric and salt for about 4 whistles, until soft.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Pyaaz, tamatar, hari mirch, adrak aur dhaniya bahut barik kaat lo.</t>
+          <t>1 cup paani, haldi aur namak ke saath cooker mein lagbhag 4 seeti tak naram hone tak pakao.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>प्याज़, टमाटर, हरी मिर्च, अदरक और हरा धनिया बहुत बारीक काट लो।</t>
+          <t>1 कप पानी, हल्दी और नमक के साथ कुकर में लगभग 4 सीटी तक नरम होने तक पकाओ।</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ਪਿਆਜ਼, ਟਮਾਟਰ, ਹਰੀ ਮਿਰਚ, ਅਦਰਕ ਅਤੇ ਹਰਾ ਧਨੀਆ ਬਹੁਤ ਬਾਰੀਕ ਕੱਟ ਲਓ।</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>1 ਕੱਪ ਪਾਣੀ, ਹਲਦੀ ਅਤੇ ਲੂਣ ਨਾਲ ਕੁੱਕਰ ਵਿੱਚ ਲਗਭਗ 4 ਸੀਟੀਆਂ ਤੱਕ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ।</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>15</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Let the pressure go down fully before you open the cooker.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>OSR100</t>
+          <t>ASC155</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mix the besan with turmeric, red chilli powder, ajwain and salt. Add about half a cup of water slowly to make a smooth pouring batter, then mix in the chopped vegetables.</t>
+          <t>Heat the ghee or oil, add cumin, then the onion and ginger. Fry until the onion is golden.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Besan mein haldi, laal mirch, ajwain aur namak milao. Lagbhag aadha cup paani dheere dheere daal ke smooth ghol banao, phir kati sabziyan mila do.</t>
+          <t>Ghee ya tel garam karke jeera daalo, phir pyaaz aur adrak. Pyaaz sunehra hone tak bhuno.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>बेसन में हल्दी, लाल मिर्च, अजवाइन और नमक मिलाओ। लगभग आधा कप पानी धीरे-धीरे डालकर चिकना घोल बनाओ, फिर कटी सब्ज़ियाँ मिला दो।</t>
+          <t>घी या तेल गरम करके जीरा डालो, फिर प्याज़ और अदरक। प्याज़ सुनहरा होने तक भूनो।</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ਵੇਸਣ ਵਿੱਚ ਹਲਦੀ, ਲਾਲ ਮਿਰਚ, ਅਜਵਾਇਣ ਅਤੇ ਲੂਣ ਮਿਲਾਓ। ਲਗਭਗ ਅੱਧਾ ਕੱਪ ਪਾਣੀ ਹੌਲੀ-ਹੌਲੀ ਪਾ ਕੇ ਮੁਲਾਇਮ ਘੋਲ ਬਣਾਓ, ਫਿਰ ਕੱਟੀਆਂ ਸਬਜ਼ੀਆਂ ਮਿਲਾ ਦਿਓ।</t>
+          <t>ਘਿਓ ਜਾਂ ਤੇਲ ਗਰਮ ਕਰਕੇ ਜੀਰਾ ਪਾਓ, ਫਿਰ ਪਿਆਜ਼ ਅਤੇ ਅਦਰਕ। ਪਿਆਜ਼ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ।</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -81280,98 +81404,3926 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>OSR100</t>
+          <t>ASC155</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Heat a tawa and grease it with a few drops of oil. Pour a ladle of batter and spread it into a thin circle.</t>
+          <t>Add the red chilli powder, pour in the cooked dal and simmer for 5 minutes. Stir in the garam masala and serve.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tawa garam karke kuch boond tel lagao. Ek kalchhi ghol daal ke patla gol faila do.</t>
+          <t>Laal mirch daalo, paki dal daal ke 5 minute halki aanch pe pakao. Garam masala milao aur serve karo.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>तवा गरम करके कुछ बूँद तेल लगाओ। एक कलछी घोल डालकर पतला गोल फैला दो।</t>
+          <t>लाल मिर्च डालो, पकी दाल डालकर 5 मिनट हल्की आँच पर पकाओ। गरम मसाला मिलाओ और परोसो।</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ਤਵਾ ਗਰਮ ਕਰਕੇ ਕੁਝ ਬੂੰਦਾਂ ਤੇਲ ਲਗਾਓ। ਇੱਕ ਕੜਛੀ ਘੋਲ ਪਾ ਕੇ ਪਤਲਾ ਗੋਲ ਫੈਲਾ ਦਿਓ।</t>
-        </is>
+          <t>ਲਾਲ ਮਿਰਚ ਪਾਓ, ਪੱਕੀ ਦਾਲ ਪਾ ਕੇ 5 ਮਿੰਟ ਹਲਕੀ ਅੱਗ ਤੇ ਪਕਾਓ। ਗਰਮ ਮਸਾਲਾ ਮਿਲਾਓ ਅਤੇ ਪਰੋਸੋ।</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>5</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>OSR100</t>
+          <t>ASC175</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cook on medium heat until the edges lift, about 2 minutes. Drizzle a little oil, flip and cook the other side for a minute.</t>
+          <t>Pick the methi leaves off the stems, wash them well and chop. Peel and cube the potato.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Medium aanch pe kinaare uthne tak sekho, lagbhag 2 minute. Thoda tel daal ke palto aur doosri taraf ek minute sekho.</t>
+          <t>Methi ke patte dandal se tod lo, achhe se dho ke kaat lo. Aloo chheel ke tukde karo.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>मध्यम आँच पर किनारे उठने तक सेको, लगभग 2 मिनट। थोड़ा तेल डालकर पलटो और दूसरी तरफ़ एक मिनट सेको।</t>
+          <t>मेथी के पत्ते डंठल से तोड़ लो, अच्छे से धोकर काट लो। आलू छीलकर टुकड़े करो।</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ਦਰਮਿਆਨੀ ਅੱਗ ਤੇ ਕਿਨਾਰੇ ਉੱਠਣ ਤੱਕ ਸੇਕੋ, ਲਗਭਗ 2 ਮਿੰਟ। ਥੋੜ੍ਹਾ ਤੇਲ ਪਾ ਕੇ ਪਲਟੋ ਅਤੇ ਦੂਜੇ ਪਾਸੇ ਇੱਕ ਮਿੰਟ ਸੇਕੋ।</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>2</v>
+          <t>ਮੇਥੀ ਦੇ ਪੱਤੇ ਡੰਡੀਆਂ ਤੋਂ ਤੋੜ ਲਓ, ਚੰਗੀ ਤਰ੍ਹਾਂ ਧੋ ਕੇ ਕੱਟ ਲਓ। ਆਲੂ ਛਿੱਲ ਕੇ ਟੁਕੜੇ ਕਰੋ।</t>
+        </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>ASC175</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Heat the ghee or oil, add the ginger and green chilli, then the potato. Cover and cook on low heat, stirring now and then, until almost soft, about 10 minutes.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Ghee ya tel garam karke adrak aur hari mirch daalo, phir aloo. Dhak ke dheemi aanch pe beech beech mein chalaate hue lagbhag naram hone tak pakao, lagbhag 10 minute.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>घी या तेल गरम करके अदरक और हरी मिर्च डालो, फिर आलू। ढककर धीमी आँच पर बीच-बीच में चलाते हुए लगभग नरम होने तक पकाओ, लगभग 10 मिनट।</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>ਘਿਓ ਜਾਂ ਤੇਲ ਗਰਮ ਕਰਕੇ ਅਦਰਕ ਅਤੇ ਹਰੀ ਮਿਰਚ ਪਾਓ, ਫਿਰ ਆਲੂ। ਢੱਕ ਕੇ ਹੌਲੀ ਅੱਗ ਤੇ ਵਿੱਚ-ਵਿੱਚ ਹਿਲਾਉਂਦੇ ਹੋਏ ਲਗਭਗ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 10 ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>10</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ASC175</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Add the methi, red chilli powder and salt. Cook uncovered for 5 minutes until the methi wilts and the potato is soft.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Methi, laal mirch aur namak daalo. Bina dhake 5 minute pakao, jab tak methi murjha jaaye aur aloo naram ho jaaye.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>मेथी, लाल मिर्च और नमक डालो। बिना ढके 5 मिनट पकाओ, जब तक मेथी मुरझा जाए और आलू नरम हो जाए।</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ਮੇਥੀ, ਲਾਲ ਮਿਰਚ ਅਤੇ ਲੂਣ ਪਾਓ। ਬਿਨਾਂ ਢੱਕੇ 5 ਮਿੰਟ ਪਕਾਓ, ਜਦੋਂ ਤੱਕ ਮੇਥੀ ਮੁਰਝਾ ਜਾਵੇ ਅਤੇ ਆਲੂ ਨਰਮ ਹੋ ਜਾਣ।</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>5</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ASC175</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>4</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Sprinkle the garam masala, mix and serve with roti or dal and rice.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Garam masala chhidko, milao aur roti ya dal chawal ke saath khao.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>गरम मसाला छिड़को, मिलाओ और रोटी या दाल चावल के साथ खाओ।</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ਗਰਮ ਮਸਾਲਾ ਛਿੜਕੋ, ਮਿਲਾਓ ਅਤੇ ਰੋਟੀ ਜਾਂ ਦਾਲ ਚੌਲਾਂ ਨਾਲ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ASC190</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Shell the peas. Peel and cube the potato, chop the onion and tomato, and crush the ginger and garlic.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Matar chheel lo. Aloo chheel ke tukde karo, pyaaz aur tamatar kaato, adrak lehsun kooto.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>मटर छील लो। आलू छीलकर टुकड़े करो, प्याज़ और टमाटर काटो, अदरक लहसुन कूटो।</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ਮਟਰ ਛਿੱਲ ਲਓ। ਆਲੂ ਛਿੱਲ ਕੇ ਟੁਕੜੇ ਕਰੋ, ਪਿਆਜ਼ ਅਤੇ ਟਮਾਟਰ ਕੱਟੋ, ਅਦਰਕ ਲਸਣ ਕੁੱਟੋ।</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ASC190</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>2</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Heat the ghee or oil and fry the onion until golden. Add the ginger, garlic and green chilli and stir for a minute.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Ghee ya tel garam karke pyaaz sunehra hone tak bhuno. Adrak, lehsun aur hari mirch daal ke ek minute chalao.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>घी या तेल गरम करके प्याज़ सुनहरा होने तक भूनो। अदरक, लहसुन और हरी मिर्च डालकर एक मिनट चलाओ।</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ਘਿਓ ਜਾਂ ਤੇਲ ਗਰਮ ਕਰਕੇ ਪਿਆਜ਼ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ। ਅਦਰਕ, ਲਸਣ ਅਤੇ ਹਰੀ ਮਿਰਚ ਪਾ ਕੇ ਇੱਕ ਮਿੰਟ ਹਿਲਾਓ।</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ASC190</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Add the tomato, turmeric, red chilli powder and salt. Cook until the tomato is mushy and oil shows at the sides, about 5 minutes.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Tamatar, haldi, laal mirch aur namak daalo. Tamatar gal jaaye aur kinaaron pe tel dikhe tab tak pakao, lagbhag 5 minute.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>टमाटर, हल्दी, लाल मिर्च और नमक डालो। टमाटर गल जाए और किनारों पर तेल दिखे तब तक पकाओ, लगभग 5 मिनट।</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>ਟਮਾਟਰ, ਹਲਦੀ, ਲਾਲ ਮਿਰਚ ਅਤੇ ਲੂਣ ਪਾਓ। ਟਮਾਟਰ ਗਲ ਜਾਵੇ ਅਤੇ ਕਿਨਾਰਿਆਂ ਤੇ ਤੇਲ ਦਿਸੇ ਤਦ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 5 ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>5</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ASC190</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>4</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Add the potato, peas and 1 cup water. Cover and cook until the potato is soft, about 12 minutes, or 2 whistles in a cooker.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Aloo, matar aur 1 cup paani daalo. Dhak ke aloo naram hone tak pakao, lagbhag 12 minute, ya cooker mein 2 seeti.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>आलू, मटर और 1 कप पानी डालो। ढककर आलू नरम होने तक पकाओ, लगभग 12 मिनट, या कुकर में 2 सीटी।</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>ਆਲੂ, ਮਟਰ ਅਤੇ 1 ਕੱਪ ਪਾਣੀ ਪਾਓ। ਢੱਕ ਕੇ ਆਲੂ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 12 ਮਿੰਟ, ਜਾਂ ਕੁੱਕਰ ਵਿੱਚ 2 ਸੀਟੀਆਂ।</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>12</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Let the pressure go down fully before you open the cooker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ASC190</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>5</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Stir in the garam masala, top with coriander and serve with roti or rice.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Garam masala milao, dhaniya daalo aur roti ya chawal ke saath khao.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>गरम मसाला मिलाओ, हरा धनिया डालो और रोटी या चावल के साथ खाओ।</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>ਗਰਮ ਮਸਾਲਾ ਮਿਲਾਓ, ਹਰਾ ਧਨੀਆ ਪਾਓ ਅਤੇ ਰੋਟੀ ਜਾਂ ਚੌਲਾਂ ਨਾਲ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ASC191</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Shell the peas, cube the paneer, chop the onion and tomato, and crush the ginger and garlic.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Matar chheel lo, paneer ke tukde karo, pyaaz aur tamatar kaato, adrak lehsun kooto.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>मटर छील लो, पनीर के टुकड़े करो, प्याज़ और टमाटर काटो, अदरक लहसुन कूटो।</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>ਮਟਰ ਛਿੱਲ ਲਓ, ਪਨੀਰ ਦੇ ਟੁਕੜੇ ਕਰੋ, ਪਿਆਜ਼ ਅਤੇ ਟਮਾਟਰ ਕੱਟੋ, ਅਦਰਕ ਲਸਣ ਕੁੱਟੋ।</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ASC191</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Lightly fry the paneer cubes in a little ghee until golden at the edges. Keep them in warm water so they stay soft.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Paneer ke tukdon ko thode ghee mein halka sunehra hone tak sek lo. Naram rakhne ke liye gungune paani mein daal do.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>पनीर के टुकड़ों को थोड़े घी में हल्का सुनहरा होने तक सेक लो। नरम रखने के लिए गुनगुने पानी में डाल दो।</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>ਪਨੀਰ ਦੇ ਟੁਕੜਿਆਂ ਨੂੰ ਥੋੜ੍ਹੇ ਘਿਓ ਵਿੱਚ ਹਲਕਾ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਸੇਕ ਲਓ। ਨਰਮ ਰੱਖਣ ਲਈ ਕੋਸੇ ਪਾਣੀ ਵਿੱਚ ਪਾ ਦਿਓ।</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ASC191</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>In the same pan fry the onion until golden, then add the ginger, garlic and green chilli for a minute.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Usi pan mein pyaaz sunehra hone tak bhuno, phir adrak, lehsun aur hari mirch daal ke ek minute chalao.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>उसी पैन में प्याज़ सुनहरा होने तक भूनो, फिर अदरक, लहसुन और हरी मिर्च डालकर एक मिनट चलाओ।</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>ਉਸੇ ਪੈਨ ਵਿੱਚ ਪਿਆਜ਼ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ, ਫਿਰ ਅਦਰਕ, ਲਸਣ ਅਤੇ ਹਰੀ ਮਿਰਚ ਪਾ ਕੇ ਇੱਕ ਮਿੰਟ ਹਿਲਾਓ।</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ASC191</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Add the tomato, turmeric, red chilli powder and salt. Cook until oil shows at the sides, about 5 minutes.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Tamatar, haldi, laal mirch aur namak daalo. Kinaaron pe tel dikhe tab tak pakao, lagbhag 5 minute.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>टमाटर, हल्दी, लाल मिर्च और नमक डालो। किनारों पर तेल दिखे तब तक पकाओ, लगभग 5 मिनट।</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>ਟਮਾਟਰ, ਹਲਦੀ, ਲਾਲ ਮਿਰਚ ਅਤੇ ਲੂਣ ਪਾਓ। ਕਿਨਾਰਿਆਂ ਤੇ ਤੇਲ ਦਿਸੇ ਤਦ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 5 ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>5</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ASC191</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>5</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Add the peas and 1 cup water. Cover and cook until the peas are soft, about 8 minutes.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Matar aur 1 cup paani daalo. Dhak ke matar naram hone tak pakao, lagbhag 8 minute.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>मटर और 1 कप पानी डालो। ढककर मटर नरम होने तक पकाओ, लगभग 8 मिनट।</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>ਮਟਰ ਅਤੇ 1 ਕੱਪ ਪਾਣੀ ਪਾਓ। ਢੱਕ ਕੇ ਮਟਰ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 8 ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>8</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ASC191</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>6</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Add the paneer and garam masala and simmer for 2 minutes. Top with coriander and serve.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Paneer aur garam masala daal ke 2 minute halki aanch pe pakao. Dhaniya daal ke serve karo.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>पनीर और गरम मसाला डालकर 2 मिनट हल्की आँच पर पकाओ। हरा धनिया डालकर परोसो।</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>ਪਨੀਰ ਅਤੇ ਗਰਮ ਮਸਾਲਾ ਪਾ ਕੇ 2 ਮਿੰਟ ਹਲਕੀ ਅੱਗ ਤੇ ਪਕਾਓ। ਹਰਾ ਧਨੀਆ ਪਾ ਕੇ ਪਰੋਸੋ।</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ASC192</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Wipe the mushrooms clean and slice them. Shell the peas, chop the onion and tomato, and crush the ginger and garlic.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Mushroom ko kapde se saaf karke kaat lo. Matar chheelo, pyaaz tamatar kaato, adrak lehsun kooto.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>मशरूम को कपड़े से साफ़ करके काट लो। मटर छीलो, प्याज़ टमाटर काटो, अदरक लहसुन कूटो।</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>ਮਸ਼ਰੂਮ ਨੂੰ ਕੱਪੜੇ ਨਾਲ ਸਾਫ਼ ਕਰਕੇ ਕੱਟ ਲਓ। ਮਟਰ ਛਿੱਲੋ, ਪਿਆਜ਼ ਟਮਾਟਰ ਕੱਟੋ, ਅਦਰਕ ਲਸਣ ਕੁੱਟੋ।</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ASC192</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Heat the ghee or oil and fry the onion until golden. Add the ginger, garlic and green chilli for a minute.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Ghee ya tel garam karke pyaaz sunehra hone tak bhuno. Adrak, lehsun aur hari mirch ek minute chalao.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>घी या तेल गरम करके प्याज़ सुनहरा होने तक भूनो। अदरक, लहसुन और हरी मिर्च एक मिनट चलाओ।</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>ਘਿਓ ਜਾਂ ਤੇਲ ਗਰਮ ਕਰਕੇ ਪਿਆਜ਼ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ। ਅਦਰਕ, ਲਸਣ ਅਤੇ ਹਰੀ ਮਿਰਚ ਇੱਕ ਮਿੰਟ ਹਿਲਾਓ।</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ASC192</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>3</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Add the tomato, turmeric, red chilli powder and salt and cook until oil shows at the sides, about 5 minutes.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Tamatar, haldi, laal mirch aur namak daal ke kinaaron pe tel dikhne tak pakao, lagbhag 5 minute.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>टमाटर, हल्दी, लाल मिर्च और नमक डालकर किनारों पर तेल दिखने तक पकाओ, लगभग 5 मिनट।</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>ਟਮਾਟਰ, ਹਲਦੀ, ਲਾਲ ਮਿਰਚ ਅਤੇ ਲੂਣ ਪਾ ਕੇ ਕਿਨਾਰਿਆਂ ਤੇ ਤੇਲ ਦਿਸਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 5 ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>5</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ASC192</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>4</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Add the peas and half a cup of water, cover and cook for 5 minutes. Add the mushrooms and cook uncovered for 5 more minutes.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Matar aur aadha cup paani daal ke dhak ke 5 minute pakao. Phir mushroom daal ke bina dhake 5 minute aur pakao.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>मटर और आधा कप पानी डालकर ढककर 5 मिनट पकाओ। फिर मशरूम डालकर बिना ढके 5 मिनट और पकाओ।</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>ਮਟਰ ਅਤੇ ਅੱਧਾ ਕੱਪ ਪਾਣੀ ਪਾ ਕੇ ਢੱਕ ਕੇ 5 ਮਿੰਟ ਪਕਾਓ। ਫਿਰ ਮਸ਼ਰੂਮ ਪਾ ਕੇ ਬਿਨਾਂ ਢੱਕੇ 5 ਮਿੰਟ ਹੋਰ ਪਕਾਓ।</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>10</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ASC192</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>5</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Stir in the garam masala and coriander and serve with roti or rice.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Garam masala aur dhaniya milao aur roti ya chawal ke saath khao.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>गरम मसाला और हरा धनिया मिलाओ और रोटी या चावल के साथ खाओ।</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>ਗਰਮ ਮਸਾਲਾ ਅਤੇ ਹਰਾ ਧਨੀਆ ਮਿਲਾਓ ਅਤੇ ਰੋਟੀ ਜਾਂ ਚੌਲਾਂ ਨਾਲ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ASC193</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Shell the peas. Chop the onion and tomato, and crush the ginger and garlic.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Matar chheel lo. Pyaaz aur tamatar kaato, adrak lehsun kooto.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>मटर छील लो। प्याज़ और टमाटर काटो, अदरक लहसुन कूटो।</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>ਮਟਰ ਛਿੱਲ ਲਓ। ਪਿਆਜ਼ ਅਤੇ ਟਮਾਟਰ ਕੱਟੋ, ਅਦਰਕ ਲਸਣ ਕੁੱਟੋ।</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ASC193</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Heat the ghee or oil and fry the onion until golden. Add the ginger, garlic and green chilli for a minute.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Ghee ya tel garam karke pyaaz sunehra hone tak bhuno. Adrak, lehsun aur hari mirch daal ke ek minute chalao.</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>घी या तेल गरम करके प्याज़ सुनहरा होने तक भूनो। अदरक, लहसुन और हरी मिर्च डालकर एक मिनट चलाओ।</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>ਘਿਓ ਜਾਂ ਤੇਲ ਗਰਮ ਕਰਕੇ ਪਿਆਜ਼ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ। ਅਦਰਕ, ਲਸਣ ਅਤੇ ਹਰੀ ਮਿਰਚ ਪਾ ਕੇ ਇੱਕ ਮਿੰਟ ਹਿਲਾਓ।</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ASC193</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>3</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Add the tomato, turmeric, red chilli powder and salt and cook until oil shows at the sides, about 5 minutes.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Tamatar, haldi, laal mirch aur namak daal ke kinaaron pe tel dikhne tak pakao, lagbhag 5 minute.</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>टमाटर, हल्दी, लाल मिर्च और नमक डालकर किनारों पर तेल दिखने तक पकाओ, लगभग 5 मिनट।</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>ਟਮਾਟਰ, ਹਲਦੀ, ਲਾਲ ਮਿਰਚ ਅਤੇ ਲੂਣ ਪਾ ਕੇ ਕਿਨਾਰਿਆਂ ਤੇ ਤੇਲ ਦਿਸਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 5 ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>5</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ASC193</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>4</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Add the peas and half a cup of water. Cover and cook until the peas are soft, about 8 minutes.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Matar aur aadha cup paani daalo. Dhak ke matar naram hone tak pakao, lagbhag 8 minute.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>मटर और आधा कप पानी डालो। ढककर मटर नरम होने तक पकाओ, लगभग 8 मिनट।</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>ਮਟਰ ਅਤੇ ਅੱਧਾ ਕੱਪ ਪਾਣੀ ਪਾਓ। ਢੱਕ ਕੇ ਮਟਰ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 8 ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>8</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ASC193</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>5</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Stir in the garam masala and coriander and serve with roti.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Garam masala aur dhaniya milao aur roti ke saath khao.</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>गरम मसाला और हरा धनिया मिलाओ और रोटी के साथ खाओ।</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ਗਰਮ ਮਸਾਲਾ ਅਤੇ ਹਰਾ ਧਨੀਆ ਮਿਲਾਓ ਅਤੇ ਰੋਟੀ ਨਾਲ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ASC214</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Boil small potatoes until just soft, about 2 whistles. Peel them and prick all over with a fork.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Chhote aloo cooker mein 2 seeti tak ubaal lo. Chheel ke kaante se chaaron taraf chhed kar do.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>छोटे आलू कुकर में 2 सीटी तक उबाल लो। छीलकर काँटे से चारों तरफ़ छेद कर दो।</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>ਛੋਟੇ ਆਲੂ ਕੁੱਕਰ ਵਿੱਚ 2 ਸੀਟੀਆਂ ਤੱਕ ਉਬਾਲ ਲਓ। ਛਿੱਲ ਕੇ ਕਾਂਟੇ ਨਾਲ ਚਾਰੇ ਪਾਸੇ ਛੇਕ ਕਰ ਦਿਓ।</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>8</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Let the pressure go down fully before you open the cooker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ASC214</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>2</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Fry the potatoes in hot oil until golden all over. Take them out on a plate.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Aloo ko garam tel mein chaaron taraf se sunehra hone tak talo. Plate mein nikaal lo.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>आलू को गरम तेल में चारों तरफ़ से सुनहरा होने तक तलो। प्लेट में निकाल लो।</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ਆਲੂਆਂ ਨੂੰ ਗਰਮ ਤੇਲ ਵਿੱਚ ਚਾਰੇ ਪਾਸਿਓਂ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਤਲੋ। ਪਲੇਟ ਵਿੱਚ ਕੱਢ ਲਓ।</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Slide food into hot oil gently, away from you. Never let water touch hot oil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ASC214</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>3</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Grind the onion, garlic, green chilli, coconut, poppy seeds and the whole spices into a paste.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Pyaaz, lehsun, hari mirch, nariyal, khaskhas aur saabut masaale pees ke paste bana lo.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>प्याज़, लहसुन, हरी मिर्च, नारियल, खसखस और साबुत मसाले पीसकर पेस्ट बना लो।</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>ਪਿਆਜ਼, ਲਸਣ, ਹਰੀ ਮਿਰਚ, ਨਾਰੀਅਲ, ਖਸਖਸ ਅਤੇ ਸਾਬਤ ਮਸਾਲੇ ਪੀਸ ਕੇ ਪੇਸਟ ਬਣਾ ਲਓ।</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ASC214</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>4</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>In a spoon of oil, fry the paste until it smells cooked, about 5 minutes. Add turmeric, red chilli and salt.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Ek chammach tel mein paste ko pakne ki khushboo aane tak bhuno, lagbhag 5 minute. Haldi, laal mirch aur namak daalo.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>एक चम्मच तेल में पेस्ट को पकने की खुशबू आने तक भूनो, लगभग 5 मिनट। हल्दी, लाल मिर्च और नमक डालो।</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>ਇੱਕ ਚਮਚ ਤੇਲ ਵਿੱਚ ਪੇਸਟ ਨੂੰ ਪੱਕਣ ਦੀ ਖੁਸ਼ਬੂ ਆਉਣ ਤੱਕ ਭੁੰਨੋ, ਲਗਭਗ 5 ਮਿੰਟ। ਹਲਦੀ, ਲਾਲ ਮਿਰਚ ਅਤੇ ਲੂਣ ਪਾਓ।</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>5</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ASC214</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>5</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Turn the heat low and stir in the beaten curd slowly so it does not split. Add half a cup of water.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Aanch dheemi karke phenta hua dahi dheere dheere milao taaki phate nahi. Aadha cup paani daalo.</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>आँच धीमी करके फेंटा हुआ दही धीरे-धीरे मिलाओ ताकि फटे नहीं। आधा कप पानी डालो।</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>ਅੱਗ ਹੌਲੀ ਕਰਕੇ ਫੈਂਟਿਆ ਹੋਇਆ ਦਹੀਂ ਹੌਲੀ-ਹੌਲੀ ਮਿਲਾਓ ਤਾਂ ਜੋ ਫਟੇ ਨਾ। ਅੱਧਾ ਕੱਪ ਪਾਣੀ ਪਾਓ।</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ASC214</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>6</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Add the potatoes, cover tightly and cook on the lowest heat for 10 minutes. Sprinkle garam masala and coriander and serve.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Aloo daal ke kas ke dhak do aur sabse dheemi aanch pe 10 minute dum pe pakao. Garam masala aur dhaniya daal ke serve karo.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>आलू डालकर कसकर ढक दो और सबसे धीमी आँच पर 10 मिनट दम पर पकाओ। गरम मसाला और हरा धनिया डालकर परोसो।</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>ਆਲੂ ਪਾ ਕੇ ਘੁੱਟ ਕੇ ਢੱਕ ਦਿਓ ਅਤੇ ਸਭ ਤੋਂ ਹੌਲੀ ਅੱਗ ਤੇ 10 ਮਿੰਟ ਦਮ ਤੇ ਪਕਾਓ। ਗਰਮ ਮਸਾਲਾ ਅਤੇ ਹਰਾ ਧਨੀਆ ਪਾ ਕੇ ਪਰੋਸੋ।</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>10</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ASC215</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Wash the spinach well. Put it into boiling water for 2 minutes, then straight into cold water. This keeps it green.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Palak achhe se dho lo. Ubalte paani mein 2 minute daalo, phir turant thande paani mein. Isse rang hara rehta hai.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>पालक अच्छे से धो लो। उबलते पानी में 2 मिनट डालो, फिर तुरंत ठंडे पानी में। इससे रंग हरा रहता है।</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>ਪਾਲਕ ਚੰਗੀ ਤਰ੍ਹਾਂ ਧੋ ਲਓ। ਉਬਲਦੇ ਪਾਣੀ ਵਿੱਚ 2 ਮਿੰਟ ਪਾਓ, ਫਿਰ ਝੱਟ ਠੰਡੇ ਪਾਣੀ ਵਿੱਚ। ਇਸ ਨਾਲ ਰੰਗ ਹਰਾ ਰਹਿੰਦਾ ਹੈ।</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>2</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ASC215</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>2</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Grind the spinach with the ginger and garlic into a smooth puree.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Palak ko adrak aur lehsun ke saath mixie mein pees ke smooth puree bana lo.</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>पालक को अदरक और लहसुन के साथ मिक्सी में पीसकर चिकनी प्यूरी बना लो।</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>ਪਾਲਕ ਨੂੰ ਅਦਰਕ ਅਤੇ ਲਸਣ ਨਾਲ ਮਿਕਸੀ ਵਿੱਚ ਪੀਸ ਕੇ ਮੁਲਾਇਮ ਪਿਊਰੀ ਬਣਾ ਲਓ।</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ASC215</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>3</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Heat the ghee and add cumin. When it crackles add the onion and cook until soft. Add the tomato, red chilli powder and salt and cook until mushy, about 4 minutes.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Ghee garam karke jeera daalo. Chatakne lage to pyaaz daal ke naram hone tak pakao. Tamatar, laal mirch aur namak daal ke gal jaane tak pakao, lagbhag 4 minute.</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>घी गरम करके जीरा डालो। चटकने लगे तो प्याज़ डालकर नरम होने तक पकाओ। टमाटर, लाल मिर्च और नमक डालकर गलने तक पकाओ, लगभग 4 मिनट।</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>ਘਿਓ ਗਰਮ ਕਰਕੇ ਜੀਰਾ ਪਾਓ। ਤਿੜਕਣ ਲੱਗੇ ਤਾਂ ਪਿਆਜ਼ ਪਾ ਕੇ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ। ਟਮਾਟਰ, ਲਾਲ ਮਿਰਚ ਅਤੇ ਲੂਣ ਪਾ ਕੇ ਗਲਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 4 ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>4</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ASC215</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>4</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Add the spinach puree and a tablespoon of water. Cook for 3 minutes, stirring.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Palak ki puree aur ek chammach paani daalo. 3 minute chalaate hue pakao.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>पालक की प्यूरी और एक चम्मच पानी डालो। 3 मिनट चलाते हुए पकाओ।</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>ਪਾਲਕ ਦੀ ਪਿਊਰੀ ਅਤੇ ਇੱਕ ਚਮਚ ਪਾਣੀ ਪਾਓ। 3 ਮਿੰਟ ਹਿਲਾਉਂਦੇ ਹੋਏ ਪਕਾਓ।</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>3</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ASC215</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>5</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Add the paneer cubes and garam masala and simmer for 2 minutes. Serve hot with roti.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Paneer ke tukde aur garam masala daal ke 2 minute halki aanch pe pakao. Garam garam roti ke saath khao.</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>पनीर के टुकड़े और गरम मसाला डालकर 2 मिनट हल्की आँच पर पकाओ। गरमागरम रोटी के साथ खाओ।</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>ਪਨੀਰ ਦੇ ਟੁਕੜੇ ਅਤੇ ਗਰਮ ਮਸਾਲਾ ਪਾ ਕੇ 2 ਮਿੰਟ ਹਲਕੀ ਅੱਗ ਤੇ ਪਕਾਓ। ਗਰਮਾ-ਗਰਮ ਰੋਟੀ ਨਾਲ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>2</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ASC240</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Wash the chicken. Mix it with the curd, turmeric and salt and leave it for 15 minutes.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Chicken dho lo. Dahi, haldi aur namak mila ke 15 minute rakh do.</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>चिकन धो लो। दही, हल्दी और नमक मिलाकर 15 मिनट रख दो।</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>ਚਿਕਨ ਧੋ ਲਓ। ਦਹੀਂ, ਹਲਦੀ ਅਤੇ ਲੂਣ ਮਿਲਾ ਕੇ 15 ਮਿੰਟ ਰੱਖ ਦਿਓ।</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>15</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Wash your hands, knife and board with soap after touching raw chicken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ASC240</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>2</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Heat the ghee or oil and add the bay leaf, cardamom, cloves, cinnamon, peppercorns and cumin. Add the onion and fry until deep golden, about 8 minutes.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Ghee ya tel garam karke tej patta, elaichi, laung, dalchini, kali mirch aur jeera daalo. Pyaaz daal ke gehra sunehra hone tak bhuno, lagbhag 8 minute.</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>घी या तेल गरम करके तेज पत्ता, इलायची, लौंग, दालचीनी, काली मिर्च और जीरा डालो। प्याज़ डालकर गहरा सुनहरा होने तक भूनो, लगभग 8 मिनट।</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>ਘਿਓ ਜਾਂ ਤੇਲ ਗਰਮ ਕਰਕੇ ਤੇਜ ਪੱਤਾ, ਇਲਾਇਚੀ, ਲੌਂਗ, ਦਾਲਚੀਨੀ, ਕਾਲੀ ਮਿਰਚ ਅਤੇ ਜੀਰਾ ਪਾਓ। ਪਿਆਜ਼ ਪਾ ਕੇ ਗੂੜ੍ਹਾ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ, ਲਗਭਗ 8 ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>8</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ASC240</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>3</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Add the ginger and garlic for a minute. Add the tomatoes, coriander powder, red chilli powder and ground poppy seeds, and cook until oil shows at the sides, about 5 minutes.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Adrak lehsun daal ke ek minute chalao. Tamatar, dhaniya powder, laal mirch aur pisi khaskhas daal ke kinaaron pe tel dikhne tak pakao, lagbhag 5 minute.</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>अदरक लहसुन डालकर एक मिनट चलाओ। टमाटर, धनिया पाउडर, लाल मिर्च और पिसी खसखस डालकर किनारों पर तेल दिखने तक पकाओ, लगभग 5 मिनट।</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>ਅਦਰਕ ਲਸਣ ਪਾ ਕੇ ਇੱਕ ਮਿੰਟ ਹਿਲਾਓ। ਟਮਾਟਰ, ਧਨੀਆ ਪਾਊਡਰ, ਲਾਲ ਮਿਰਚ ਅਤੇ ਪੀਸੀ ਖਸਖਸ ਪਾ ਕੇ ਕਿਨਾਰਿਆਂ ਤੇ ਤੇਲ ਦਿਸਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 5 ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>5</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ASC240</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>4</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Add the chicken and fry on high heat for 5 minutes until it changes colour.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Chicken daal ke tez aanch pe 5 minute bhuno, jab tak rang badal jaaye.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>चिकन डालकर तेज़ आँच पर 5 मिनट भूनो, जब तक रंग बदल जाए।</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>ਚਿਕਨ ਪਾ ਕੇ ਤੇਜ਼ ਅੱਗ ਤੇ 5 ਮਿੰਟ ਭੁੰਨੋ, ਜਦੋਂ ਤੱਕ ਰੰਗ ਬਦਲ ਜਾਵੇ।</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>5</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ASC240</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>5</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Add 1 cup water, cover and simmer for 20 minutes, or 3 whistles in a cooker, until the chicken is cooked through.</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>1 cup paani daal ke dhak do aur 20 minute halki aanch pe pakao, ya cooker mein 3 seeti, jab tak chicken andar tak pak jaaye.</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1 कप पानी डालकर ढक दो और 20 मिनट हल्की आँच पर पकाओ, या कुकर में 3 सीटी, जब तक चिकन अंदर तक पक जाए।</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1 ਕੱਪ ਪਾਣੀ ਪਾ ਕੇ ਢੱਕ ਦਿਓ ਅਤੇ 20 ਮਿੰਟ ਹਲਕੀ ਅੱਗ ਤੇ ਪਕਾਓ, ਜਾਂ ਕੁੱਕਰ ਵਿੱਚ 3 ਸੀਟੀਆਂ, ਜਦੋਂ ਤੱਕ ਚਿਕਨ ਅੰਦਰ ਤੱਕ ਪੱਕ ਜਾਵੇ।</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>20</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Cut the thickest piece: it must be white all through, with no pink inside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ASC240</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>6</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Stir in the garam masala, top with coriander and serve with rice or roti.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Garam masala milao, dhaniya daalo aur chawal ya roti ke saath khao.</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>गरम मसाला मिलाओ, हरा धनिया डालो और चावल या रोटी के साथ खाओ।</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>ਗਰਮ ਮਸਾਲਾ ਮਿਲਾਓ, ਹਰਾ ਧਨੀਆ ਪਾਓ ਅਤੇ ਚੌਲਾਂ ਜਾਂ ਰੋਟੀ ਨਾਲ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ASC485</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Boil the potato until soft, about 2 whistles in the cooker. Cool, peel and cut it into small cubes.</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Aloo ko cooker mein 2 seeti tak ubaal lo. Thanda karke chheelo aur chhote tukde karo.</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>आलू को कुकर में 2 सीटी तक उबाल लो। ठंडा करके छीलो और छोटे टुकड़े करो।</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>ਆਲੂ ਨੂੰ ਕੁੱਕਰ ਵਿੱਚ 2 ਸੀਟੀਆਂ ਤੱਕ ਉਬਾਲ ਲਓ। ਠੰਡਾ ਕਰਕੇ ਛਿੱਲੋ ਅਤੇ ਛੋਟੇ ਟੁਕੜੇ ਕਰੋ।</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>8</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Let the pressure go down fully before you open the cooker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ASC485</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>2</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Beat the curd with the salt until smooth.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Dahi mein namak daal ke smooth hone tak phento.</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>दही में नमक डालकर चिकना होने तक फेंटो।</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>ਦਹੀਂ ਵਿੱਚ ਲੂਣ ਪਾ ਕੇ ਮੁਲਾਇਮ ਹੋਣ ਤੱਕ ਫੈਂਟੋ।</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ASC485</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>3</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Mix the potato into the curd. If you like, sprinkle a pinch of roasted cumin or red chilli on top, and serve cool.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Aloo ko dahi mein mila do. Pasand ho to upar chutki bhar bhuna jeera ya laal mirch chhidko aur thanda khao.</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>आलू को दही में मिला दो। पसंद हो तो ऊपर चुटकी भर भुना जीरा या लाल मिर्च छिड़को और ठंडा खाओ।</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>ਆਲੂ ਨੂੰ ਦਹੀਂ ਵਿੱਚ ਮਿਲਾ ਦਿਓ। ਪਸੰਦ ਹੋਵੇ ਤਾਂ ਉੱਤੇ ਚੁਟਕੀ ਭਰ ਭੁੰਨਿਆ ਜੀਰਾ ਜਾਂ ਲਾਲ ਮਿਰਚ ਛਿੜਕੋ ਅਤੇ ਠੰਡਾ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>BFP039</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Dry roast the suji on low heat, stirring, until it smells nutty and turns light golden, about 4 minutes. Take it out.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Suji ko dheemi aanch pe chalaate hue bhuno, jab tak khushboo aaye aur halki sunehri ho jaaye, lagbhag 4 minute. Nikaal lo.</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>सूजी को धीमी आँच पर चलाते हुए भूनो, जब तक खुशबू आए और हल्की सुनहरी हो जाए, लगभग 4 मिनट। निकाल लो।</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>ਸੂਜੀ ਨੂੰ ਹੌਲੀ ਅੱਗ ਤੇ ਹਿਲਾਉਂਦੇ ਹੋਏ ਭੁੰਨੋ, ਜਦੋਂ ਤੱਕ ਖੁਸ਼ਬੂ ਆਵੇ ਅਤੇ ਹਲਕੀ ਸੁਨਹਿਰੀ ਹੋ ਜਾਵੇ, ਲਗਭਗ 4 ਮਿੰਟ। ਕੱਢ ਲਓ।</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>4</v>
+      </c>
+      <c r="H107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>BFP039</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>2</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Heat the oil. Add mustard seeds and urad dal and fry until the dal is golden. Add the dry red chilli, hing and curry leaves.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Tel garam karo. Rai aur urad dal daal ke dal sunehri hone tak bhuno. Sukhi laal mirch, hing aur kadi patta daalo.</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>तेल गरम करो। राई और उड़द दाल डालकर दाल सुनहरी होने तक भूनो। सूखी लाल मिर्च, हींग और कड़ी पत्ता डालो।</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>ਤੇਲ ਗਰਮ ਕਰੋ। ਰਾਈ ਅਤੇ ਮਾਂਹ ਦੀ ਦਾਲ ਪਾ ਕੇ ਦਾਲ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ। ਸੁੱਕੀ ਲਾਲ ਮਿਰਚ, ਹਿੰਗ ਅਤੇ ਕੜੀ ਪੱਤਾ ਪਾਓ।</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>BFP039</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>3</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Add the chopped onion, green chilli and ginger. Cook until the onion is soft.</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Kata pyaaz, hari mirch aur adrak daal ke pyaaz naram hone tak pakao.</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>कटा प्याज़, हरी मिर्च और अदरक डालकर प्याज़ नरम होने तक पकाओ।</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>ਕੱਟਿਆ ਪਿਆਜ਼, ਹਰੀ ਮਿਰਚ ਅਤੇ ਅਦਰਕ ਪਾ ਕੇ ਪਿਆਜ਼ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ।</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>BFP039</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>4</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Pour in 100 ml water, add salt and red chilli powder, and bring it to a boil.</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>100 ml paani daalo, namak aur laal mirch daal ke ubaal aane do.</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>100 ml पानी डालो, नमक और लाल मिर्च डालकर उबाल आने दो।</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>100 ml ਪਾਣੀ ਪਾਓ, ਲੂਣ ਅਤੇ ਲਾਲ ਮਿਰਚ ਪਾ ਕੇ ਉਬਾਲ ਆਉਣ ਦਿਓ।</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>BFP039</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>5</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Turn the heat low. Add the roasted suji slowly while stirring all the time so no lumps form. Cover and cook for 2 minutes.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Aanch dheemi karo. Bhuni suji dheere dheere daalo aur lagaataar chalaate raho taaki gutliyaan na banein. Dhak ke 2 minute pakao.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>आँच धीमी करो। भुनी सूजी धीरे-धीरे डालो और लगातार चलाते रहो ताकि गुठलियाँ न बनें। ढककर 2 मिनट पकाओ।</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>ਅੱਗ ਹੌਲੀ ਕਰੋ। ਭੁੰਨੀ ਸੂਜੀ ਹੌਲੀ-ਹੌਲੀ ਪਾਓ ਅਤੇ ਲਗਾਤਾਰ ਹਿਲਾਉਂਦੇ ਰਹੋ ਤਾਂ ਜੋ ਗੰਢਾਂ ਨਾ ਬਣਨ। ਢੱਕ ਕੇ 2 ਮਿੰਟ ਪਕਾਓ।</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>2</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>It splutters while it cooks. Keep your hand back and stir with a long spoon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>BFP039</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>6</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Squeeze in the lemon, sprinkle coriander and serve hot.</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Nimbu nichodo, dhaniya daalo aur garam garam khao.</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>नींबू निचोड़ो, हरा धनिया डालो और गरमागरम खाओ।</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>ਨਿੰਬੂ ਨਿਚੋੜੋ, ਹਰਾ ਧਨੀਆ ਪਾਓ ਅਤੇ ਗਰਮਾ-ਗਰਮ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>BFP040</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Roast the vermicelli in a dry pan on low heat until golden, about 3 minutes. Take it out.</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Sevaiyan sookhe pan mein dheemi aanch pe sunehri hone tak bhuno, lagbhag 3 minute. Nikaal lo.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>सेवइयाँ सूखे पैन में धीमी आँच पर सुनहरी होने तक भूनो, लगभग 3 मिनट। निकाल लो।</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>ਸੇਵੀਆਂ ਸੁੱਕੇ ਪੈਨ ਵਿੱਚ ਹੌਲੀ ਅੱਗ ਤੇ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ, ਲਗਭਗ 3 ਮਿੰਟ। ਕੱਢ ਲਓ।</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>3</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>BFP040</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>2</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Heat the oil. Add mustard seeds and urad dal, then the dry red chilli, hing, curry leaves, onion, green chilli and ginger. Cook until the onion is soft.</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Tel garam karo. Rai aur urad dal daalo, phir sukhi laal mirch, hing, kadi patta, pyaaz, hari mirch aur adrak. Pyaaz naram hone tak pakao.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>तेल गरम करो। राई और उड़द दाल डालो, फिर सूखी लाल मिर्च, हींग, कड़ी पत्ता, प्याज़, हरी मिर्च और अदरक। प्याज़ नरम होने तक पकाओ।</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>ਤੇਲ ਗਰਮ ਕਰੋ। ਰਾਈ ਅਤੇ ਮਾਂਹ ਦੀ ਦਾਲ ਪਾਓ, ਫਿਰ ਸੁੱਕੀ ਲਾਲ ਮਿਰਚ, ਹਿੰਗ, ਕੜੀ ਪੱਤਾ, ਪਿਆਜ਼, ਹਰੀ ਮਿਰਚ ਅਤੇ ਅਦਰਕ। ਪਿਆਜ਼ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ।</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>BFP040</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>3</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Pour in 100 ml water with salt and red chilli powder and bring it to a boil. Add the vermicelli and stir.</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>100 ml paani, namak aur laal mirch daal ke ubaal aane do. Sevaiyan daal ke milao.</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>100 ml पानी, नमक और लाल मिर्च डालकर उबाल आने दो। सेवइयाँ डालकर मिलाओ।</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>100 ml ਪਾਣੀ, ਲੂਣ ਅਤੇ ਲਾਲ ਮਿਰਚ ਪਾ ਕੇ ਉਬਾਲ ਆਉਣ ਦਿਓ। ਸੇਵੀਆਂ ਪਾ ਕੇ ਮਿਲਾਓ।</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>BFP040</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>4</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Cover and cook on low heat until the water is soaked up, about 4 minutes. Fluff gently with a fork.</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Dhak ke dheemi aanch pe paani sokh jaane tak pakao, lagbhag 4 minute. Kaante se halke se kholo.</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>ढककर धीमी आँच पर पानी सोख जाने तक पकाओ, लगभग 4 मिनट। काँटे से हल्के से खोलो।</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>ਢੱਕ ਕੇ ਹੌਲੀ ਅੱਗ ਤੇ ਪਾਣੀ ਸੋਖ ਜਾਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 4 ਮਿੰਟ। ਕਾਂਟੇ ਨਾਲ ਹੌਲੀ ਜਿਹੇ ਖੋਲ੍ਹੋ।</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>4</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>BFP040</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>5</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Squeeze in the lemon, add coriander and serve hot.</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Nimbu nichodo, dhaniya daalo aur garam garam khao.</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>नींबू निचोड़ो, हरा धनिया डालो और गरमागरम खाओ।</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>ਨਿੰਬੂ ਨਿਚੋੜੋ, ਹਰਾ ਧਨੀਆ ਪਾਓ ਅਤੇ ਗਰਮਾ-ਗਰਮ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>BFP041</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Wash the rice, dry it on a cloth and grind it coarsely, like suji. Roast it on low heat until it smells nutty, about 4 minutes.</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Chawal dho ke kapde pe sukha lo aur suji jaisa mota pees lo. Dheemi aanch pe khushboo aane tak bhuno, lagbhag 4 minute.</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>चावल धोकर कपड़े पर सुखा लो और सूजी जैसा मोटा पीस लो। धीमी आँच पर खुशबू आने तक भूनो, लगभग 4 मिनट।</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>ਚੌਲ ਧੋ ਕੇ ਕੱਪੜੇ ਤੇ ਸੁਕਾ ਲਓ ਅਤੇ ਸੂਜੀ ਵਰਗਾ ਮੋਟਾ ਪੀਸ ਲਓ। ਹੌਲੀ ਅੱਗ ਤੇ ਖੁਸ਼ਬੂ ਆਉਣ ਤੱਕ ਭੁੰਨੋ, ਲਗਭਗ 4 ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>4</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>BFP041</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>2</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Heat the oil. Add mustard seeds and urad dal and fry until the dal is golden. Add the dry red chilli, hing, curry leaves, onion, green chilli and ginger and cook until the onion is soft.</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Tel garam karo. Rai aur urad dal daal ke dal sunehri hone tak bhuno. Sukhi laal mirch, hing, kadi patta, pyaaz, hari mirch aur adrak daal ke pyaaz naram hone tak pakao.</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>तेल गरम करो। राई और उड़द दाल डालकर दाल सुनहरी होने तक भूनो। सूखी लाल मिर्च, हींग, कड़ी पत्ता, प्याज़, हरी मिर्च और अदरक डालकर प्याज़ नरम होने तक पकाओ।</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>ਤੇਲ ਗਰਮ ਕਰੋ। ਰਾਈ ਅਤੇ ਮਾਂਹ ਦੀ ਦਾਲ ਪਾ ਕੇ ਦਾਲ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ। ਸੁੱਕੀ ਲਾਲ ਮਿਰਚ, ਹਿੰਗ, ਕੜੀ ਪੱਤਾ, ਪਿਆਜ਼, ਹਰੀ ਮਿਰਚ ਅਤੇ ਅਦਰਕ ਪਾ ਕੇ ਪਿਆਜ਼ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ।</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>BFP041</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>3</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Pour in 100 ml water with salt and red chilli powder and bring it to a boil. Add the rice rava slowly, stirring.</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>100 ml paani, namak aur laal mirch daal ke ubaal aane do. Chawal ka rava dheere dheere chalaate hue daalo.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>100 ml पानी, नमक और लाल मिर्च डालकर उबाल आने दो। चावल का रवा धीरे-धीरे चलाते हुए डालो।</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>100 ml ਪਾਣੀ, ਲੂਣ ਅਤੇ ਲਾਲ ਮਿਰਚ ਪਾ ਕੇ ਉਬਾਲ ਆਉਣ ਦਿਓ। ਚੌਲਾਂ ਦਾ ਰਵਾ ਹੌਲੀ-ਹੌਲੀ ਹਿਲਾਉਂਦੇ ਹੋਏ ਪਾਓ।</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>It splutters while it cooks. Keep your hand back and stir with a long spoon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>BFP041</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>4</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Cover and cook on low heat until soft, about 10 minutes, stirring once or twice. Add a splash of water if it looks dry.</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Dhak ke dheemi aanch pe naram hone tak pakao, lagbhag 10 minute, beech mein ek do baar chalao. Sukha lage to thoda paani daal do.</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>ढककर धीमी आँच पर नरम होने तक पकाओ, लगभग 10 मिनट, बीच में एक-दो बार चलाओ। सूखा लगे तो थोड़ा पानी डाल दो।</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>ਢੱਕ ਕੇ ਹੌਲੀ ਅੱਗ ਤੇ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 10 ਮਿੰਟ, ਵਿੱਚ ਇੱਕ-ਦੋ ਵਾਰ ਹਿਲਾਓ। ਸੁੱਕਾ ਲੱਗੇ ਤਾਂ ਥੋੜ੍ਹਾ ਪਾਣੀ ਪਾ ਦਿਓ।</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>10</v>
+      </c>
+      <c r="H121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>BFP041</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>5</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Squeeze in the lemon, add coriander and serve hot.</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Nimbu nichodo, dhaniya daalo aur garam garam khao.</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>नींबू निचोड़ो, हरा धनिया डालो और गरमागरम खाओ।</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>ਨਿੰਬੂ ਨਿਚੋੜੋ, ਹਰਾ ਧਨੀਆ ਪਾਓ ਅਤੇ ਗਰਮਾ-ਗਰਮ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>BFP043</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Dry roast the suji on low heat until it smells nutty, about 4 minutes. Take it out.</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Suji ko dheemi aanch pe khushboo aane tak bhuno, lagbhag 4 minute. Nikaal lo.</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>सूजी को धीमी आँच पर खुशबू आने तक भूनो, लगभग 4 मिनट। निकाल लो।</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>ਸੂਜੀ ਨੂੰ ਹੌਲੀ ਅੱਗ ਤੇ ਖੁਸ਼ਬੂ ਆਉਣ ਤੱਕ ਭੁੰਨੋ, ਲਗਭਗ 4 ਮਿੰਟ। ਕੱਢ ਲਓ।</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>4</v>
+      </c>
+      <c r="H123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>BFP043</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>2</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Heat the oil and fry the peanuts until crunchy. Add mustard seeds and urad dal, then dry red chilli, hing and curry leaves.</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Tel garam karke moongphali crunchy hone tak bhuno. Rai aur urad dal daalo, phir sukhi laal mirch, hing aur kadi patta.</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>तेल गरम करके मूंगफली कुरकुरी होने तक भूनो। राई और उड़द दाल डालो, फिर सूखी लाल मिर्च, हींग और कड़ी पत्ता।</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>ਤੇਲ ਗਰਮ ਕਰਕੇ ਮੂੰਗਫਲੀ ਕਰਾਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ। ਰਾਈ ਅਤੇ ਮਾਂਹ ਦੀ ਦਾਲ ਪਾਓ, ਫਿਰ ਸੁੱਕੀ ਲਾਲ ਮਿਰਚ, ਹਿੰਗ ਅਤੇ ਕੜੀ ਪੱਤਾ।</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>BFP043</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>3</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Add the onion, green chilli and ginger and cook until soft. Add the peas and diced carrot and cook for 3 minutes.</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Pyaaz, hari mirch aur adrak daal ke naram hone tak pakao. Matar aur chhoti kati gajar daal ke 3 minute pakao.</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>प्याज़, हरी मिर्च और अदरक डालकर नरम होने तक पकाओ। मटर और छोटी कटी गाजर डालकर 3 मिनट पकाओ।</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>ਪਿਆਜ਼, ਹਰੀ ਮਿਰਚ ਅਤੇ ਅਦਰਕ ਪਾ ਕੇ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ। ਮਟਰ ਅਤੇ ਛੋਟੀ ਕੱਟੀ ਗਾਜਰ ਪਾ ਕੇ 3 ਮਿੰਟ ਪਕਾਓ।</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>3</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>BFP043</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>4</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Pour in 100 ml water with salt and red chilli powder and bring it to a boil. Add the suji slowly while stirring, cover and cook on low heat for 2 minutes.</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>100 ml paani, namak aur laal mirch daal ke ubaal aane do. Suji dheere dheere chalaate hue daalo, dhak ke dheemi aanch pe 2 minute pakao.</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>100 ml पानी, नमक और लाल मिर्च डालकर उबाल आने दो। सूजी धीरे-धीरे चलाते हुए डालो, ढककर धीमी आँच पर 2 मिनट पकाओ।</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>100 ml ਪਾਣੀ, ਲੂਣ ਅਤੇ ਲਾਲ ਮਿਰਚ ਪਾ ਕੇ ਉਬਾਲ ਆਉਣ ਦਿਓ। ਸੂਜੀ ਹੌਲੀ-ਹੌਲੀ ਹਿਲਾਉਂਦੇ ਹੋਏ ਪਾਓ, ਢੱਕ ਕੇ ਹੌਲੀ ਅੱਗ ਤੇ 2 ਮਿੰਟ ਪਕਾਓ।</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>2</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>It splutters while it cooks. Keep your hand back and stir with a long spoon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>BFP043</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>5</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Squeeze in the lemon and serve hot.</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Nimbu nichodo aur garam garam khao.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>नींबू निचोड़ो और गरमागरम खाओ।</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>ਨਿੰਬੂ ਨਿਚੋੜੋ ਅਤੇ ਗਰਮਾ-ਗਰਮ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>BFP044</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Rinse the poha in a strainer under running water and drain. Mix in the turmeric and salt and leave it for 5 minutes to soften.</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Poha ko chhalni mein paani se dho ke paani nikaal do. Haldi aur namak mila ke 5 minute naram hone do.</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>पोहे को छलनी में पानी से धोकर पानी निकाल दो। हल्दी और नमक मिलाकर 5 मिनट नरम होने दो।</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>ਪੋਹੇ ਨੂੰ ਛਾਨਣੀ ਵਿੱਚ ਪਾਣੀ ਨਾਲ ਧੋ ਕੇ ਪਾਣੀ ਕੱਢ ਦਿਓ। ਹਲਦੀ ਅਤੇ ਲੂਣ ਮਿਲਾ ਕੇ 5 ਮਿੰਟ ਨਰਮ ਹੋਣ ਦਿਓ।</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>5</v>
+      </c>
+      <c r="H128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>BFP044</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>2</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Heat the oil in a pan and fry the peanuts until crunchy. Take them out.</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Kadhai mein tel garam karke moongphali crunchy hone tak bhuno aur nikaal lo.</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>कड़ाही में तेल गरम करके मूंगफली कुरकुरी होने तक भूनो और निकाल लो।</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>ਕੜਾਹੀ ਵਿੱਚ ਤੇਲ ਗਰਮ ਕਰਕੇ ਮੂੰਗਫਲੀ ਕਰਾਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ ਅਤੇ ਕੱਢ ਲਓ।</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>BFP044</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>3</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>In the same oil add mustard seeds. When they crackle add hing, curry leaves and green chilli, then the small potato cubes. Cover and cook on low heat until soft, about 5 minutes.</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Usi tel mein rai daalo. Chatakne lage to hing, kadi patta aur hari mirch daalo, phir chhote kate aloo. Dhak ke dheemi aanch pe 5 minute naram hone tak pakao.</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>उसी तेल में राई डालो। चटकने लगे तो हींग, कड़ी पत्ता और हरी मिर्च डालो, फिर छोटे कटे आलू। ढककर धीमी आँच पर 5 मिनट नरम होने तक पकाओ।</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>ਉਸੇ ਤੇਲ ਵਿੱਚ ਰਾਈ ਪਾਓ। ਤਿੜਕਣ ਲੱਗੇ ਤਾਂ ਹਿੰਗ, ਕੜੀ ਪੱਤਾ ਅਤੇ ਹਰੀ ਮਿਰਚ ਪਾਓ, ਫਿਰ ਛੋਟੇ ਕੱਟੇ ਆਲੂ। ਢੱਕ ਕੇ ਹੌਲੀ ਅੱਗ ਤੇ 5 ਮਿੰਟ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ।</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>5</v>
+      </c>
+      <c r="H130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>BFP044</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>4</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Add the poha and red chilli powder. Mix gently so the poha does not break, cover and steam on low heat for 2 minutes.</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Poha aur laal mirch daal ke halke haath se milao taaki poha toote nahi. Dhak ke dheemi aanch pe 2 minute rakho.</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>पोहा और लाल मिर्च डालकर हल्के हाथ से मिलाओ ताकि पोहा टूटे नहीं। ढककर धीमी आँच पर 2 मिनट रखो।</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>ਪੋਹਾ ਅਤੇ ਲਾਲ ਮਿਰਚ ਪਾ ਕੇ ਹੌਲੀ ਹੱਥ ਨਾਲ ਮਿਲਾਓ ਤਾਂ ਜੋ ਪੋਹਾ ਟੁੱਟੇ ਨਾ। ਢੱਕ ਕੇ ਹੌਲੀ ਅੱਗ ਤੇ 2 ਮਿੰਟ ਰੱਖੋ।</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>2</v>
+      </c>
+      <c r="H131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>BFP044</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>5</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Turn off the heat. Squeeze in the lemon, add the peanuts and coriander, and serve hot.</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Gas band karo. Nimbu nichodo, moongphali aur dhaniya daal ke garam garam khao.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>गैस बंद करो। नींबू निचोड़ो, मूंगफली और हरा धनिया डालकर गरमागरम खाओ।</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>ਗੈਸ ਬੰਦ ਕਰੋ। ਨਿੰਬੂ ਨਿਚੋੜੋ, ਮੂੰਗਫਲੀ ਅਤੇ ਹਰਾ ਧਨੀਆ ਪਾ ਕੇ ਗਰਮਾ-ਗਰਮ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>BFP136</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Wash the rice 2 or 3 times and soak it in water for 20 minutes.</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Chawal 2-3 baar dho ke 20 minute paani mein bhigo do.</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>चावल 2-3 बार धोकर 20 मिनट पानी में भिगो दो।</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>ਚੌਲ 2-3 ਵਾਰ ਧੋ ਕੇ 20 ਮਿੰਟ ਪਾਣੀ ਵਿੱਚ ਭਿਓਂ ਦਿਓ।</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>20</v>
+      </c>
+      <c r="H133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>BFP136</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>2</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Heat the oil and add the bay leaf, cumin, cardamom, cloves and cinnamon. When they sizzle, add the sliced onion and cook until light golden.</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Tel garam karke tej patta, jeera, elaichi, laung aur dalchini daalo. Chatakne lagein to kata pyaaz daal ke halka sunehra hone tak bhuno.</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>तेल गरम करके तेज पत्ता, जीरा, इलायची, लौंग और दालचीनी डालो। चटकने लगें तो कटा प्याज़ डालकर हल्का सुनहरा होने तक भूनो।</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>ਤੇਲ ਗਰਮ ਕਰਕੇ ਤੇਜ ਪੱਤਾ, ਜੀਰਾ, ਇਲਾਇਚੀ, ਲੌਂਗ ਅਤੇ ਦਾਲਚੀਨੀ ਪਾਓ। ਤਿੜਕਣ ਲੱਗਣ ਤਾਂ ਕੱਟਿਆ ਪਿਆਜ਼ ਪਾ ਕੇ ਹਲਕਾ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ।</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>BFP136</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>3</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Add the peas, the drained rice and salt. Stir gently for a minute.</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Matar, paani nikaale chawal aur namak daalo. Ek minute halke haath se chalao.</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>मटर, पानी निकाले चावल और नमक डालो। एक मिनट हल्के हाथ से चलाओ।</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>ਮਟਰ, ਪਾਣੀ ਕੱਢੇ ਚੌਲ ਅਤੇ ਲੂਣ ਪਾਓ। ਇੱਕ ਮਿੰਟ ਹੌਲੀ ਹੱਥ ਨਾਲ ਹਿਲਾਓ।</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>BFP136</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>4</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Add 160 ml water and bring it to a boil. Cover and cook on the lowest heat for 12 minutes, or 2 whistles in a cooker.</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>160 ml paani daal ke ubaal aane do. Dhak ke sabse dheemi aanch pe 12 minute pakao, ya cooker mein 2 seeti.</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>160 ml पानी डालकर उबाल आने दो। ढककर सबसे धीमी आँच पर 12 मिनट पकाओ, या कुकर में 2 सीटी।</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>160 ml ਪਾਣੀ ਪਾ ਕੇ ਉਬਾਲ ਆਉਣ ਦਿਓ। ਢੱਕ ਕੇ ਸਭ ਤੋਂ ਹੌਲੀ ਅੱਗ ਤੇ 12 ਮਿੰਟ ਪਕਾਓ, ਜਾਂ ਕੁੱਕਰ ਵਿੱਚ 2 ਸੀਟੀਆਂ।</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>12</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Let the pressure go down fully before you open the cooker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>BFP136</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>5</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Turn off the heat and leave it covered for 5 minutes. Fluff it gently with a fork and serve.</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Gas band karke 5 minute dhaka rehne do. Kaante se halka sa khol ke serve karo.</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>गैस बंद करके 5 मिनट ढका रहने दो। काँटे से हल्का सा खोलकर परोसो।</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>ਗੈਸ ਬੰਦ ਕਰਕੇ 5 ਮਿੰਟ ਢੱਕਿਆ ਰਹਿਣ ਦਿਓ। ਕਾਂਟੇ ਨਾਲ ਹਲਕਾ ਜਿਹਾ ਖੋਲ੍ਹ ਕੇ ਪਰੋਸੋ।</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>5</v>
+      </c>
+      <c r="H137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>BFP147</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Heat the oil, add mustard seeds and urad dal and fry until golden. Add the dry red chilli, hing and curry leaves, then the suji. Roast on low heat for 3 minutes and let it cool.</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Tel garam karke rai aur urad dal sunehri hone tak bhuno. Sukhi laal mirch, hing aur kadi patta daalo, phir suji. Dheemi aanch pe 3 minute bhuno aur thanda hone do.</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>तेल गरम करके राई और उड़द दाल सुनहरी होने तक भूनो। सूखी लाल मिर्च, हींग और कड़ी पत्ता डालो, फिर सूजी। धीमी आँच पर 3 मिनट भूनो और ठंडा होने दो।</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>ਤੇਲ ਗਰਮ ਕਰਕੇ ਰਾਈ ਅਤੇ ਮਾਂਹ ਦੀ ਦਾਲ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ। ਸੁੱਕੀ ਲਾਲ ਮਿਰਚ, ਹਿੰਗ ਅਤੇ ਕੜੀ ਪੱਤਾ ਪਾਓ, ਫਿਰ ਸੂਜੀ। ਹੌਲੀ ਅੱਗ ਤੇ 3 ਮਿੰਟ ਭੁੰਨੋ ਅਤੇ ਠੰਡਾ ਹੋਣ ਦਿਓ।</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>3</v>
+      </c>
+      <c r="H138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>BFP147</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>2</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Mix in the sour curd and salt, add a little water for a thick batter and rest it for 10 minutes.</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Khatta dahi aur namak milao, thoda paani daal ke gaadha ghol banao aur 10 minute rakh do.</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>खट्टा दही और नमक मिलाओ, थोड़ा पानी डालकर गाढ़ा घोल बनाओ और 10 मिनट रख दो।</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>ਖੱਟਾ ਦਹੀਂ ਅਤੇ ਲੂਣ ਮਿਲਾਓ, ਥੋੜ੍ਹਾ ਪਾਣੀ ਪਾ ਕੇ ਗਾੜ੍ਹਾ ਘੋਲ ਬਣਾਓ ਅਤੇ 10 ਮਿੰਟ ਰੱਖ ਦਿਓ।</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>10</v>
+      </c>
+      <c r="H139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>BFP147</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>3</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Just before steaming, stir in the Eno with a spoon of water. The batter will turn frothy.</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Bhaap mein rakhne se theek pehle Eno ek chammach paani ke saath milao. Ghol jhaagdaar ho jaayega.</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>भाप में रखने से ठीक पहले ईनो एक चम्मच पानी के साथ मिलाओ। घोल झागदार हो जाएगा।</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>ਭਾਫ਼ ਵਿੱਚ ਰੱਖਣ ਤੋਂ ਠੀਕ ਪਹਿਲਾਂ ਈਨੋ ਇੱਕ ਚਮਚ ਪਾਣੀ ਨਾਲ ਮਿਲਾਓ। ਘੋਲ ਝੱਗਦਾਰ ਹੋ ਜਾਵੇਗਾ।</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>BFP147</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>4</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Pour into greased idli moulds and steam for 12 minutes. Rest 2 minutes and serve with chutney.</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Tel lage idli saanchon mein daal ke 12 minute bhaap mein pakao. 2 minute rukh ke chutney ke saath khao.</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>तेल लगे इडली साँचों में डालकर 12 मिनट भाप में पकाओ। 2 मिनट रुककर चटनी के साथ खाओ।</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>ਤੇਲ ਲੱਗੇ ਇਡਲੀ ਸਾਂਚਿਆਂ ਵਿੱਚ ਪਾ ਕੇ 12 ਮਿੰਟ ਭਾਫ਼ ਵਿੱਚ ਪਕਾਓ। 2 ਮਿੰਟ ਰੁਕ ਕੇ ਚਟਣੀ ਨਾਲ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>12</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Lower things into boiling water gently with a spoon, so it does not splash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>BFP166</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Wash the moong dal 2 or 3 times. Cook it with 1 and a quarter cups of water, turmeric and salt until soft, about 2 whistles or 15 minutes in a pot.</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Moong dal 2-3 baar dho lo. Sava cup paani, haldi aur namak ke saath naram hone tak pakao, cooker mein 2 seeti ya pateele mein 15 minute.</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>मूंग दाल 2-3 बार धो लो। सवा कप पानी, हल्दी और नमक के साथ नरम होने तक पकाओ, कुकर में 2 सीटी या पतीले में 15 मिनट।</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>ਮੂੰਗੀ ਦੀ ਦਾਲ 2-3 ਵਾਰ ਧੋ ਲਓ। ਸਵਾ ਕੱਪ ਪਾਣੀ, ਹਲਦੀ ਅਤੇ ਲੂਣ ਨਾਲ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ, ਕੁੱਕਰ ਵਿੱਚ 2 ਸੀਟੀਆਂ ਜਾਂ ਪਤੀਲੇ ਵਿੱਚ 15 ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>15</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Let the pressure go down fully before you open the cooker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>BFP166</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>2</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>For the tadka, heat the ghee and add cumin. When it crackles add the garlic, ginger and green chilli for a few seconds.</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Tadke ke liye ghee garam karke jeera daalo. Chatakne lage to lehsun, adrak aur hari mirch kuch second bhuno.</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>तड़के के लिए घी गरम करके जीरा डालो। चटकने लगे तो लहसुन, अदरक और हरी मिर्च कुछ सेकंड भूनो।</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>ਤੜਕੇ ਲਈ ਘਿਓ ਗਰਮ ਕਰਕੇ ਜੀਰਾ ਪਾਓ। ਤਿੜਕਣ ਲੱਗੇ ਤਾਂ ਲਸਣ, ਅਦਰਕ ਅਤੇ ਹਰੀ ਮਿਰਚ ਕੁਝ ਸਕਿੰਟ ਭੁੰਨੋ।</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>BFP166</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>3</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Turn off the heat, add the red chilli powder and pour the tadka over the dal. Stir in the garam masala and serve with rice or roti.</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Gas band karke laal mirch daalo aur tadka dal ke upar daal do. Garam masala milao aur chawal ya roti ke saath khao.</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>गैस बंद करके लाल मिर्च डालो और तड़का दाल के ऊपर डाल दो। गरम मसाला मिलाओ और चावल या रोटी के साथ खाओ।</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>ਗੈਸ ਬੰਦ ਕਰਕੇ ਲਾਲ ਮਿਰਚ ਪਾਓ ਅਤੇ ਤੜਕਾ ਦਾਲ ਉੱਤੇ ਪਾ ਦਿਓ। ਗਰਮ ਮਸਾਲਾ ਮਿਲਾਓ ਅਤੇ ਚੌਲਾਂ ਜਾਂ ਰੋਟੀ ਨਾਲ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>It splutters while it cooks. Keep your hand back and stir with a long spoon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>BFP239</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Peel the potato and cut it into cubes. Chop the onion and tomato, and crush the ginger and garlic.</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Aloo chheel ke tukde karo. Pyaaz aur tamatar kaato, adrak lehsun kooto.</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>आलू छीलकर टुकड़े करो। प्याज़ और टमाटर काटो, अदरक लहसुन कूटो।</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>ਆਲੂ ਛਿੱਲ ਕੇ ਟੁਕੜੇ ਕਰੋ। ਪਿਆਜ਼ ਅਤੇ ਟਮਾਟਰ ਕੱਟੋ, ਅਦਰਕ ਲਸਣ ਕੁੱਟੋ।</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>BFP239</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>2</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Heat the oil, add the bay leaf and cumin. Fry the onion until golden, then the ginger, garlic and green chilli for a minute.</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Tel garam karke tej patta aur jeera daalo. Pyaaz sunehra hone tak bhuno, phir adrak, lehsun aur hari mirch ek minute.</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>तेल गरम करके तेज पत्ता और जीरा डालो। प्याज़ सुनहरा होने तक भूनो, फिर अदरक, लहसुन और हरी मिर्च एक मिनट।</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>ਤੇਲ ਗਰਮ ਕਰਕੇ ਤੇਜ ਪੱਤਾ ਅਤੇ ਜੀਰਾ ਪਾਓ। ਪਿਆਜ਼ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ, ਫਿਰ ਅਦਰਕ, ਲਸਣ ਅਤੇ ਹਰੀ ਮਿਰਚ ਇੱਕ ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>BFP239</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>3</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Add the tomato, turmeric, coriander powder, red chilli powder and salt. Cook until oil shows at the sides, about 5 minutes.</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Tamatar, haldi, dhaniya powder, laal mirch aur namak daalo. Kinaaron pe tel dikhne tak pakao, lagbhag 5 minute.</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>टमाटर, हल्दी, धनिया पाउडर, लाल मिर्च और नमक डालो। किनारों पर तेल दिखने तक पकाओ, लगभग 5 मिनट।</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>ਟਮਾਟਰ, ਹਲਦੀ, ਧਨੀਆ ਪਾਊਡਰ, ਲਾਲ ਮਿਰਚ ਅਤੇ ਲੂਣ ਪਾਓ। ਕਿਨਾਰਿਆਂ ਤੇ ਤੇਲ ਦਿਸਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 5 ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>5</v>
+      </c>
+      <c r="H147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>BFP239</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>4</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Add the potato and 1 cup water. Cover and cook until the potato is soft, about 15 minutes, or 2 whistles in a cooker.</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Aloo aur 1 cup paani daalo. Dhak ke aloo naram hone tak pakao, lagbhag 15 minute, ya cooker mein 2 seeti.</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>आलू और 1 कप पानी डालो। ढककर आलू नरम होने तक पकाओ, लगभग 15 मिनट, या कुकर में 2 सीटी।</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>ਆਲੂ ਅਤੇ 1 ਕੱਪ ਪਾਣੀ ਪਾਓ। ਢੱਕ ਕੇ ਆਲੂ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 15 ਮਿੰਟ, ਜਾਂ ਕੁੱਕਰ ਵਿੱਚ 2 ਸੀਟੀਆਂ।</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>15</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Let the pressure go down fully before you open the cooker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>BFP239</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>5</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Stir in the garam masala, top with coriander and serve with roti or puri.</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Garam masala milao, dhaniya daalo aur roti ya poori ke saath khao.</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>गरम मसाला मिलाओ, हरा धनिया डालो और रोटी या पूरी के साथ खाओ।</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>ਗਰਮ ਮਸਾਲਾ ਮਿਲਾਓ, ਹਰਾ ਧਨੀਆ ਪਾਓ ਅਤੇ ਰੋਟੀ ਜਾਂ ਪੂਰੀ ਨਾਲ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>BFP240</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Lower the egg gently into boiling water and boil for 10 minutes. Cool it in cold water, peel, and make 2 small cuts on it.</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Anda ubalte paani mein dheere se daalo aur 10 minute ubaalo. Thande paani mein thanda karke chheel lo aur do chhote cheere laga do.</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>अंडा उबलते पानी में धीरे से डालो और 10 मिनट उबालो। ठंडे पानी में ठंडा करके छील लो और दो छोटे चीरे लगा दो।</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>ਆਂਡਾ ਉਬਲਦੇ ਪਾਣੀ ਵਿੱਚ ਹੌਲੀ ਜਿਹੇ ਪਾਓ ਅਤੇ 10 ਮਿੰਟ ਉਬਾਲੋ। ਠੰਡੇ ਪਾਣੀ ਵਿੱਚ ਠੰਡਾ ਕਰਕੇ ਛਿੱਲ ਲਓ ਅਤੇ ਦੋ ਛੋਟੇ ਚੀਰੇ ਲਗਾ ਦਿਓ।</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>10</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Lower things into boiling water gently with a spoon, so it does not splash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>BFP240</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>2</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Heat the oil and add the bay leaf and cumin. Add the onion and fry until golden, then the ginger, garlic and green chilli for a minute.</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Tel garam karke tej patta aur jeera daalo. Pyaaz daal ke sunehra hone tak bhuno, phir adrak, lehsun aur hari mirch ek minute.</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>तेल गरम करके तेज पत्ता और जीरा डालो। प्याज़ डालकर सुनहरा होने तक भूनो, फिर अदरक, लहसुन और हरी मिर्च एक मिनट।</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>ਤੇਲ ਗਰਮ ਕਰਕੇ ਤੇਜ ਪੱਤਾ ਅਤੇ ਜੀਰਾ ਪਾਓ। ਪਿਆਜ਼ ਪਾ ਕੇ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ, ਫਿਰ ਅਦਰਕ, ਲਸਣ ਅਤੇ ਹਰੀ ਮਿਰਚ ਇੱਕ ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>BFP240</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>3</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Add the tomato, turmeric, coriander powder, red chilli powder and salt. Cook until oil shows at the sides, about 5 minutes.</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Tamatar, haldi, dhaniya powder, laal mirch aur namak daalo. Kinaaron pe tel dikhe tab tak pakao, lagbhag 5 minute.</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>टमाटर, हल्दी, धनिया पाउडर, लाल मिर्च और नमक डालो। किनारों पर तेल दिखे तब तक पकाओ, लगभग 5 मिनट।</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>ਟਮਾਟਰ, ਹਲਦੀ, ਧਨੀਆ ਪਾਊਡਰ, ਲਾਲ ਮਿਰਚ ਅਤੇ ਲੂਣ ਪਾਓ। ਕਿਨਾਰਿਆਂ ਤੇ ਤੇਲ ਦਿਸੇ ਤਦ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 5 ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>5</v>
+      </c>
+      <c r="H152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>BFP240</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>4</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Add 1 cup water and bring it to a boil. Add the egg and simmer for 5 minutes.</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>1 cup paani daal ke ubaal aane do. Anda daal ke 5 minute halki aanch pe pakao.</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>1 कप पानी डालकर उबाल आने दो। अंडा डालकर 5 मिनट हल्की आँच पर पकाओ।</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>1 ਕੱਪ ਪਾਣੀ ਪਾ ਕੇ ਉਬਾਲ ਆਉਣ ਦਿਓ। ਆਂਡਾ ਪਾ ਕੇ 5 ਮਿੰਟ ਹਲਕੀ ਅੱਗ ਤੇ ਪਕਾਓ।</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>5</v>
+      </c>
+      <c r="H153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>BFP240</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>5</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Stir in the garam masala, top with coriander and serve with rice or roti.</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Garam masala milao, dhaniya daalo aur chawal ya roti ke saath khao.</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>गरम मसाला मिलाओ, हरा धनिया डालो और चावल या रोटी के साथ खाओ।</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>ਗਰਮ ਮਸਾਲਾ ਮਿਲਾਓ, ਹਰਾ ਧਨੀਆ ਪਾਓ ਅਤੇ ਚੌਲਾਂ ਜਾਂ ਰੋਟੀ ਨਾਲ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>BFP556</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Wash the rice and moong dal together and soak for 15 minutes. Wash the spinach and chop it finely.</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Chawal aur moong dal saath dho ke 15 minute bhigo do. Palak dho ke barik kaat lo.</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>चावल और मूंग दाल साथ धोकर 15 मिनट भिगो दो। पालक धोकर बारीक काट लो।</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>ਚੌਲ ਅਤੇ ਮੂੰਗੀ ਦੀ ਦਾਲ ਇਕੱਠੇ ਧੋ ਕੇ 15 ਮਿੰਟ ਭਿਓਂ ਦਿਓ। ਪਾਲਕ ਧੋ ਕੇ ਬਾਰੀਕ ਕੱਟ ਲਓ।</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>15</v>
+      </c>
+      <c r="H155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>BFP556</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>2</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Heat the oil in the cooker, add the spinach and stir for a minute until it wilts.</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Cooker mein tel garam karke palak daalo aur ek minute murjhaane tak chalao.</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>कुकर में तेल गरम करके पालक डालो और एक मिनट मुरझाने तक चलाओ।</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>ਕੁੱਕਰ ਵਿੱਚ ਤੇਲ ਗਰਮ ਕਰਕੇ ਪਾਲਕ ਪਾਓ ਅਤੇ ਇੱਕ ਮਿੰਟ ਮੁਰਝਾਉਣ ਤੱਕ ਹਿਲਾਓ।</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>BFP556</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>3</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Add the drained rice and dal, salt and 200 ml water. Pressure cook for 3 whistles.</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Paani nikaale chawal dal, namak aur 200 ml paani daalo. Cooker mein 3 seeti lagao.</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>पानी निकाले चावल दाल, नमक और 200 ml पानी डालो। कुकर में 3 सीटी लगाओ।</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>ਪਾਣੀ ਕੱਢੇ ਚੌਲ ਦਾਲ, ਲੂਣ ਅਤੇ 200 ml ਪਾਣੀ ਪਾਓ। ਕੁੱਕਰ ਵਿੱਚ 3 ਸੀਟੀਆਂ ਲਗਾਓ।</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>12</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Let the pressure go down fully before you open the cooker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>BFP556</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>4</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Stir well. Add a little hot water if you like it softer, and serve hot with curd or pickle.</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Achhe se milao. Naram pasand ho to thoda garam paani daalo, aur dahi ya achaar ke saath garam garam khao.</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>अच्छे से मिलाओ। नरम पसंद हो तो थोड़ा गरम पानी डालो, और दही या अचार के साथ गरमागरम खाओ।</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>ਚੰਗੀ ਤਰ੍ਹਾਂ ਮਿਲਾਓ। ਨਰਮ ਪਸੰਦ ਹੋਵੇ ਤਾਂ ਥੋੜ੍ਹਾ ਗਰਮ ਪਾਣੀ ਪਾਓ, ਅਤੇ ਦਹੀਂ ਜਾਂ ਅਚਾਰ ਨਾਲ ਗਰਮਾ-ਗਰਮ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>BFP579</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Roast the suji on low heat for 3 minutes. Roast the chana dal and peanuts in a little oil until golden. Chop the spinach finely.</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Suji dheemi aanch pe 3 minute bhuno. Chana dal aur moongphali thode tel mein sunehri hone tak bhuno. Palak barik kaato.</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>सूजी धीमी आँच पर 3 मिनट भूनो। चना दाल और मूंगफली थोड़े तेल में सुनहरी होने तक भूनो। पालक बारीक काटो।</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>ਸੂਜੀ ਹੌਲੀ ਅੱਗ ਤੇ 3 ਮਿੰਟ ਭੁੰਨੋ। ਛੋਲਿਆਂ ਦੀ ਦਾਲ ਅਤੇ ਮੂੰਗਫਲੀ ਥੋੜ੍ਹੇ ਤੇਲ ਵਿੱਚ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ। ਪਾਲਕ ਬਾਰੀਕ ਕੱਟੋ।</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>3</v>
+      </c>
+      <c r="H159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>BFP579</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>2</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Mix the suji, curd, spinach, chana dal, peanuts, red chilli powder and salt with a little water into a thick batter. Rest it for 15 minutes.</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Suji, dahi, palak, chana dal, moongphali, laal mirch aur namak thode paani ke saath mila ke gaadha ghol banao. 15 minute rakh do.</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>सूजी, दही, पालक, चना दाल, मूंगफली, लाल मिर्च और नमक थोड़े पानी के साथ मिलाकर गाढ़ा घोल बनाओ। 15 मिनट रख दो।</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>ਸੂਜੀ, ਦਹੀਂ, ਪਾਲਕ, ਛੋਲਿਆਂ ਦੀ ਦਾਲ, ਮੂੰਗਫਲੀ, ਲਾਲ ਮਿਰਚ ਅਤੇ ਲੂਣ ਥੋੜ੍ਹੇ ਪਾਣੀ ਨਾਲ ਮਿਲਾ ਕੇ ਗਾੜ੍ਹਾ ਘੋਲ ਬਣਾਓ। 15 ਮਿੰਟ ਰੱਖ ਦਿਓ।</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>15</v>
+      </c>
+      <c r="H160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>BFP579</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>3</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Just before steaming, stir in the baking soda.</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Bhaap mein rakhne se theek pehle meetha soda milao.</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>भाप में रखने से ठीक पहले मीठा सोडा मिलाओ।</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>ਭਾਫ਼ ਵਿੱਚ ਰੱਖਣ ਤੋਂ ਠੀਕ ਪਹਿਲਾਂ ਮਿੱਠਾ ਸੋਡਾ ਮਿਲਾਓ।</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>BFP579</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>4</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Pour into greased idli moulds and steam for 12 minutes. Rest 2 minutes and serve with chutney.</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Tel lage idli saanchon mein daal ke 12 minute bhaap mein pakao. 2 minute rukh ke chutney ke saath khao.</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>तेल लगे इडली साँचों में डालकर 12 मिनट भाप में पकाओ। 2 मिनट रुककर चटनी के साथ खाओ।</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>ਤੇਲ ਲੱਗੇ ਇਡਲੀ ਸਾਂਚਿਆਂ ਵਿੱਚ ਪਾ ਕੇ 12 ਮਿੰਟ ਭਾਫ਼ ਵਿੱਚ ਪਕਾਓ। 2 ਮਿੰਟ ਰੁਕ ਕੇ ਚਟਣੀ ਨਾਲ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>12</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Lower things into boiling water gently with a spoon, so it does not splash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
           <t>OSR100</t>
         </is>
       </c>
-      <c r="B63" t="n">
+      <c r="B163" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Chop the onion, tomato, green chilli, ginger and coriander very finely.</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Pyaaz, tamatar, hari mirch, adrak aur dhaniya bahut barik kaat lo.</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>प्याज़, टमाटर, हरी मिर्च, अदरक और हरा धनिया बहुत बारीक काट लो।</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>ਪਿਆਜ਼, ਟਮਾਟਰ, ਹਰੀ ਮਿਰਚ, ਅਦਰਕ ਅਤੇ ਹਰਾ ਧਨੀਆ ਬਹੁਤ ਬਾਰੀਕ ਕੱਟ ਲਓ।</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>OSR100</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>2</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Mix the besan with turmeric, red chilli powder, ajwain and salt. Add about half a cup of water slowly to make a smooth pouring batter, then mix in the chopped vegetables.</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Besan mein haldi, laal mirch, ajwain aur namak milao. Lagbhag aadha cup paani dheere dheere daal ke smooth ghol banao, phir kati sabziyan mila do.</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>बेसन में हल्दी, लाल मिर्च, अजवाइन और नमक मिलाओ। लगभग आधा कप पानी धीरे-धीरे डालकर चिकना घोल बनाओ, फिर कटी सब्ज़ियाँ मिला दो।</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>ਵੇਸਣ ਵਿੱਚ ਹਲਦੀ, ਲਾਲ ਮਿਰਚ, ਅਜਵਾਇਣ ਅਤੇ ਲੂਣ ਮਿਲਾਓ। ਲਗਭਗ ਅੱਧਾ ਕੱਪ ਪਾਣੀ ਹੌਲੀ-ਹੌਲੀ ਪਾ ਕੇ ਮੁਲਾਇਮ ਘੋਲ ਬਣਾਓ, ਫਿਰ ਕੱਟੀਆਂ ਸਬਜ਼ੀਆਂ ਮਿਲਾ ਦਿਓ।</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>OSR100</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>3</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Heat a tawa and grease it with a few drops of oil. Pour a ladle of batter and spread it into a thin circle.</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Tawa garam karke kuch boond tel lagao. Ek kalchhi ghol daal ke patla gol faila do.</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>तवा गरम करके कुछ बूँद तेल लगाओ। एक कलछी घोल डालकर पतला गोल फैला दो।</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>ਤਵਾ ਗਰਮ ਕਰਕੇ ਕੁਝ ਬੂੰਦਾਂ ਤੇਲ ਲਗਾਓ। ਇੱਕ ਕੜਛੀ ਘੋਲ ਪਾ ਕੇ ਪਤਲਾ ਗੋਲ ਫੈਲਾ ਦਿਓ।</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>OSR100</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>4</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Cook on medium heat until the edges lift, about 2 minutes. Drizzle a little oil, flip and cook the other side for a minute.</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Medium aanch pe kinaare uthne tak sekho, lagbhag 2 minute. Thoda tel daal ke palto aur doosri taraf ek minute sekho.</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>मध्यम आँच पर किनारे उठने तक सेको, लगभग 2 मिनट। थोड़ा तेल डालकर पलटो और दूसरी तरफ़ एक मिनट सेको।</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>ਦਰਮਿਆਨੀ ਅੱਗ ਤੇ ਕਿਨਾਰੇ ਉੱਠਣ ਤੱਕ ਸੇਕੋ, ਲਗਭਗ 2 ਮਿੰਟ। ਥੋੜ੍ਹਾ ਤੇਲ ਪਾ ਕੇ ਪਲਟੋ ਅਤੇ ਦੂਜੇ ਪਾਸੇ ਇੱਕ ਮਿੰਟ ਸੇਕੋ।</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>2</v>
+      </c>
+      <c r="H166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>OSR100</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
         <v>5</v>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C167" t="inlineStr">
         <is>
           <t>Make the rest the same way. Serve hot with green chutney or ketchup.</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D167" t="inlineStr">
         <is>
           <t>Baaki chille bhi aise hi banao. Garam garam hari chutney ya ketchup ke saath khao.</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E167" t="inlineStr">
         <is>
           <t>बाकी चीले भी ऐसे ही बनाओ। गरमागरम हरी चटनी या केचप के साथ खाओ।</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F167" t="inlineStr">
         <is>
           <t>ਬਾਕੀ ਚੀਲੇ ਵੀ ਇਸੇ ਤਰ੍ਹਾਂ ਬਣਾਓ। ਗਰਮਾ-ਗਰਮ ਹਰੀ ਚਟਣੀ ਜਾਂ ਕੈਚਪ ਨਾਲ ਖਾਓ।</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>OSR139</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>1</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Wash the whole urad and rajma and soak them in plenty of water for at least 8 hours, or overnight.</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Saabut urad aur rajma dho ke kam se kam 8 ghante, ya raat bhar, khoob paani mein bhigo do.</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>साबुत उड़द और राजमा धोकर कम से कम 8 घंटे, या रात भर, खूब पानी में भिगो दो।</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>ਸਾਬਤ ਮਾਂਹ ਅਤੇ ਰਾਜਮਾਂਹ ਧੋ ਕੇ ਘੱਟੋ-ਘੱਟ 8 ਘੰਟੇ, ਜਾਂ ਰਾਤ ਭਰ, ਬਹੁਤੇ ਪਾਣੀ ਵਿੱਚ ਭਿਓਂ ਦਿਓ।</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>OSR139</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>2</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Drain them and pressure cook with 4 cups of water and salt for about 8 whistles, until the dal mashes easily between your fingers.</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Paani nikaal ke 4 cup paani aur namak ke saath cooker mein lagbhag 8 seeti tak pakao, jab tak dal ungliyon mein aasaani se mas jaaye.</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>पानी निकालकर 4 कप पानी और नमक के साथ कुकर में लगभग 8 सीटी तक पकाओ, जब तक दाल उँगलियों में आसानी से मसल जाए।</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>ਪਾਣੀ ਕੱਢ ਕੇ 4 ਕੱਪ ਪਾਣੀ ਅਤੇ ਲੂਣ ਨਾਲ ਕੁੱਕਰ ਵਿੱਚ ਲਗਭਗ 8 ਸੀਟੀਆਂ ਤੱਕ ਪਕਾਓ, ਜਦੋਂ ਤੱਕ ਦਾਲ ਉਂਗਲਾਂ ਵਿੱਚ ਆਸਾਨੀ ਨਾਲ ਮਸਲੀ ਜਾਵੇ।</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>35</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Let the pressure go down fully before you open the cooker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>OSR139</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>3</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Heat the butter and add cumin, bay leaf, cardamoms, cloves and cinnamon. Fry the onion until golden, then the ginger garlic paste and green chilli.</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Makhan garam karke jeera, tej patta, elaichi, laung aur dalchini daalo. Pyaaz sunehra hone tak bhuno, phir adrak lehsun ka paste aur hari mirch.</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>मक्खन गरम करके जीरा, तेज पत्ता, इलायची, लौंग और दालचीनी डालो। प्याज़ सुनहरा होने तक भूनो, फिर अदरक लहसुन का पेस्ट और हरी मिर्च।</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>ਮੱਖਣ ਗਰਮ ਕਰਕੇ ਜੀਰਾ, ਤੇਜ ਪੱਤਾ, ਇਲਾਇਚੀ, ਲੌਂਗ ਅਤੇ ਦਾਲਚੀਨੀ ਪਾਓ। ਪਿਆਜ਼ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ, ਫਿਰ ਅਦਰਕ ਲਸਣ ਦਾ ਪੇਸਟ ਅਤੇ ਹਰੀ ਮਿਰਚ।</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>OSR139</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>4</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Add the tomato puree and red chilli powder and cook until thick and the butter separates, about 8 minutes.</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Tamatar ki puree aur laal mirch daal ke gaadha hone aur makhan alag dikhne tak pakao, lagbhag 8 minute.</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>टमाटर की प्यूरी और लाल मिर्च डालकर गाढ़ा होने और मक्खन अलग दिखने तक पकाओ, लगभग 8 मिनट।</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>ਟਮਾਟਰ ਦੀ ਪਿਊਰੀ ਅਤੇ ਲਾਲ ਮਿਰਚ ਪਾ ਕੇ ਗਾੜ੍ਹਾ ਹੋਣ ਅਤੇ ਮੱਖਣ ਵੱਖਰਾ ਦਿਸਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 8 ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>8</v>
+      </c>
+      <c r="H171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>OSR139</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>5</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Add the cooked dal and mash it a little. Simmer on low heat for 20 minutes, stirring often, adding hot water if it gets too thick.</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Paki dal daal ke thoda mash karo. Dheemi aanch pe 20 minute pakao, baar baar chalao, zyada gaadhi ho to garam paani daalo.</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>पकी दाल डालकर थोड़ा मैश करो। धीमी आँच पर 20 मिनट पकाओ, बार-बार चलाओ, ज़्यादा गाढ़ी हो तो गरम पानी डालो।</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>ਪੱਕੀ ਦਾਲ ਪਾ ਕੇ ਥੋੜ੍ਹਾ ਮੈਸ਼ ਕਰੋ। ਹੌਲੀ ਅੱਗ ਤੇ 20 ਮਿੰਟ ਪਕਾਓ, ਵਾਰ-ਵਾਰ ਹਿਲਾਓ, ਬਹੁਤੀ ਗਾੜ੍ਹੀ ਹੋਵੇ ਤਾਂ ਗਰਮ ਪਾਣੀ ਪਾਓ।</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>20</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>It splutters while it cooks. Keep your hand back and stir with a long spoon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>OSR139</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>6</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Stir in the kasuri methi, nutmeg and cream. Top with coriander and serve with naan, roti or rice.</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Kasuri methi, jaiphal aur cream milao. Dhaniya daal ke naan, roti ya chawal ke saath khao.</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>कसूरी मेथी, जायफल और क्रीम मिलाओ। हरा धनिया डालकर नान, रोटी या चावल के साथ खाओ।</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>ਕਸੂਰੀ ਮੇਥੀ, ਜਾਇਫਲ ਅਤੇ ਕਰੀਮ ਮਿਲਾਓ। ਹਰਾ ਧਨੀਆ ਪਾ ਕੇ ਨਾਨ, ਰੋਟੀ ਜਾਂ ਚੌਲਾਂ ਨਾਲ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>OSR144</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>1</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Wash all five dals together and soak them in 3 cups of water for 1 hour.</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Paanchon daalein ek saath dho ke 3 cup paani mein 1 ghanta bhigo do.</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>पाँचों दालें एक साथ धोकर 3 कप पानी में 1 घंटा भिगो दो।</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>ਪੰਜੇ ਦਾਲਾਂ ਇਕੱਠੀਆਂ ਧੋ ਕੇ 3 ਕੱਪ ਪਾਣੀ ਵਿੱਚ 1 ਘੰਟਾ ਭਿਓਂ ਦਿਓ।</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>60</v>
+      </c>
+      <c r="H174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>OSR144</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>2</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Pressure cook the dals in the same water with turmeric and salt for about 4 whistles, until soft. Mash lightly.</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Usi paani mein haldi aur namak daal ke cooker mein lagbhag 4 seeti tak naram hone tak pakao. Halka mash karo.</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>उसी पानी में हल्दी और नमक डालकर कुकर में लगभग 4 सीटी तक नरम होने तक पकाओ। हल्का मैश करो।</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>ਉਸੇ ਪਾਣੀ ਵਿੱਚ ਹਲਦੀ ਅਤੇ ਲੂਣ ਪਾ ਕੇ ਕੁੱਕਰ ਵਿੱਚ ਲਗਭਗ 4 ਸੀਟੀਆਂ ਤੱਕ ਨਰਮ ਹੋਣ ਤੱਕ ਪਕਾਓ। ਹਲਕਾ ਮੈਸ਼ ਕਰੋ।</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>15</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Let the pressure go down fully before you open the cooker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>OSR144</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>3</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Heat the ghee and add cumin, bay leaves, cloves, black cardamom and dry red chilli. Fry the onion until golden, then the ginger garlic paste.</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Ghee garam karke jeera, tej patta, laung, badi elaichi aur sukhi laal mirch daalo. Pyaaz sunehra hone tak bhuno, phir adrak lehsun ka paste.</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>घी गरम करके जीरा, तेज पत्ता, लौंग, बड़ी इलायची और सूखी लाल मिर्च डालो। प्याज़ सुनहरा होने तक भूनो, फिर अदरक लहसुन का पेस्ट।</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>ਘਿਓ ਗਰਮ ਕਰਕੇ ਜੀਰਾ, ਤੇਜ ਪੱਤਾ, ਲੌਂਗ, ਵੱਡੀ ਇਲਾਇਚੀ ਅਤੇ ਸੁੱਕੀ ਲਾਲ ਮਿਰਚ ਪਾਓ। ਪਿਆਜ਼ ਸੁਨਹਿਰੀ ਹੋਣ ਤੱਕ ਭੁੰਨੋ, ਫਿਰ ਅਦਰਕ ਲਸਣ ਦਾ ਪੇਸਟ।</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>OSR144</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>4</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Add the tomato, coriander powder, cumin powder and red chilli powder. Cook until oil shows at the sides, about 5 minutes.</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Tamatar, dhaniya powder, jeera powder aur laal mirch daalo. Kinaaron pe tel dikhne tak pakao, lagbhag 5 minute.</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>टमाटर, धनिया पाउडर, जीरा पाउडर और लाल मिर्च डालो। किनारों पर तेल दिखने तक पकाओ, लगभग 5 मिनट।</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>ਟਮਾਟਰ, ਧਨੀਆ ਪਾਊਡਰ, ਜੀਰਾ ਪਾਊਡਰ ਅਤੇ ਲਾਲ ਮਿਰਚ ਪਾਓ। ਕਿਨਾਰਿਆਂ ਤੇ ਤੇਲ ਦਿਸਣ ਤੱਕ ਪਕਾਓ, ਲਗਭਗ 5 ਮਿੰਟ।</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>5</v>
+      </c>
+      <c r="H177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>OSR144</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>5</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Pour in the dal, simmer for 8 minutes, then stir in kasuri methi, garam masala and coriander. Serve with roti, bati or rice.</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Dal daal ke 8 minute halki aanch pe pakao, phir kasuri methi, garam masala aur dhaniya milao. Roti, baati ya chawal ke saath khao.</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>दाल डालकर 8 मिनट हल्की आँच पर पकाओ, फिर कसूरी मेथी, गरम मसाला और हरा धनिया मिलाओ। रोटी, बाटी या चावल के साथ खाओ।</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>ਦਾਲ ਪਾ ਕੇ 8 ਮਿੰਟ ਹਲਕੀ ਅੱਗ ਤੇ ਪਕਾਓ, ਫਿਰ ਕਸੂਰੀ ਮੇਥੀ, ਗਰਮ ਮਸਾਲਾ ਅਤੇ ਹਰਾ ਧਨੀਆ ਮਿਲਾਓ। ਰੋਟੀ, ਬਾਟੀ ਜਾਂ ਚੌਲਾਂ ਨਾਲ ਖਾਓ।</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>8</v>
+      </c>
+      <c r="H178" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -81384,7 +85336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81478,726 +85430,2376 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASC059</t>
+          <t>ASC047</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>egg is rubbery or dry</t>
+          <t>too thick</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>It cooked too long or too hot. Next time cook on low heat and take it off while still soft.</t>
+          <t>Stir in a little warm milk until it is how you like it.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ज़्यादा देर या तेज़ आँच पर पका। अगली बार धीमी आँच पर पकाना और थोड़ा नरम रहते ही उतार लेना।</t>
+          <t>थोड़ा गरम दूध मिलाओ जब तक मनपसंद न हो जाए।</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASC059</t>
+          <t>ASC047</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>egg is watery</t>
+          <t>daliya still hard</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cook it 30 seconds more on low heat, stirring.</t>
+          <t>Add a few spoons of water, cover and cook for 5 more minutes before adding more milk.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>धीमी आँच पर 30 सेकंड और चलाते हुए पकाओ।</t>
+          <t>कुछ चम्मच पानी डालो, ढककर 5 मिनट और पकाओ, फिर दूध डालो।</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASC059</t>
+          <t>ASC047</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>too salty</t>
+          <t>milk stuck at the bottom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Beat one more egg without salt and mix it in.</t>
+          <t>Move it to a clean pan without scraping and keep stirring on low heat.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>एक और अंडा बिना नमक के फेंटकर मिला दो।</t>
+          <t>नीचे से खुरचे बिना साफ़ बर्तन में डालो और धीमी आँच पर चलाते रहो।</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASC098</t>
+          <t>ASC050</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>stuffing comes out or paratha tears</t>
+          <t>too thick or gluey</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Use a little less stuffing, seal the edges well and roll with light hands. Cover a torn patch with a pinch of dry atta.</t>
+          <t>Stir in a little warm milk or water.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>मसाला थोड़ा कम भरो, किनारे अच्छे से बंद करो और हल्के हाथ से बेलो। फटी जगह पर थोड़ा सूखा आटा लगा दो।</t>
+          <t>थोड़ा गरम दूध या पानी मिला दो।</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASC098</t>
+          <t>ASC050</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>paratha is hard</t>
+          <t>too runny</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The dough was stiff or the heat too low. Knead a softer dough and cook on medium heat with a little more ghee.</t>
+          <t>Simmer for 2 more minutes; it thickens more as it cools.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>आटा सख़्त था या आँच धीमी थी। नरम आटा गूँधो और मध्यम आँच पर थोड़ा ज़्यादा घी लगाकर सेको।</t>
+          <t>2 मिनट और पकाओ; ठंडा होने पर और गाढ़ा होता है।</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ASC098</t>
+          <t>ASC050</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>stuffing is wet and sticky</t>
+          <t>milk boiled over</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>The potatoes were too wet. Let them cool fully before mashing, and mix a spoon of dry atta into the stuffing.</t>
+          <t>Lower the heat and keep stirring. Use a bigger pan next time.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>आलू गीले थे। मैश करने से पहले पूरा ठंडा होने दो और मसाले में एक चम्मच सूखा आटा मिला दो।</t>
+          <t>आँच धीमी करो और चलाते रहो। अगली बार बड़ा बर्तन लेना।</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASC190</t>
+          <t>ASC059</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>too watery</t>
+          <t>egg is rubbery or dry</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cook uncovered on high heat for 5 minutes, and mash a few potato pieces into the gravy.</t>
+          <t>It cooked too long or too hot. Next time cook on low heat and take it off while still soft.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>बिना ढके तेज़ आँच पर 5 मिनट पकाओ और आलू के कुछ टुकड़े ग्रेवी में मैश कर दो।</t>
+          <t>ज़्यादा देर या तेज़ आँच पर पका। अगली बार धीमी आँच पर पकाना और थोड़ा नरम रहते ही उतार लेना।</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASC190</t>
+          <t>ASC059</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>too salty</t>
+          <t>egg is watery</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Add half a cup of water and a boiled potato, and cook for 5 minutes.</t>
+          <t>Cook it 30 seconds more on low heat, stirring.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>आधा कप पानी और एक उबला आलू डालकर 5 मिनट पकाओ।</t>
+          <t>धीमी आँच पर 30 सेकंड और चलाते हुए पकाओ।</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ASC190</t>
+          <t>ASC059</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>masala stuck and burnt</t>
+          <t>too salty</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Move it to a clean pan without scraping the bottom, and add a little water.</t>
+          <t>Beat one more egg without salt and mix it in.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>नीचे से खुरचे बिना इसे साफ़ पैन में डाल दो और थोड़ा पानी मिला दो।</t>
+          <t>एक और अंडा बिना नमक के फेंटकर मिला दो।</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASC191</t>
+          <t>ASC098</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>paneer is hard or rubbery</t>
+          <t>stuffing comes out or paratha tears</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>It cooked too long. Soak the pieces in warm water for 10 minutes, and add them only at the end next time.</t>
+          <t>Use a little less stuffing, seal the edges well and roll with light hands. Cover a torn patch with a pinch of dry atta.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>पनीर ज़्यादा पक गया। टुकड़ों को 10 मिनट गुनगुने पानी में रखो, और अगली बार आखिर में डालना।</t>
+          <t>मसाला थोड़ा कम भरो, किनारे अच्छे से बंद करो और हल्के हाथ से बेलो। फटी जगह पर थोड़ा सूखा आटा लगा दो।</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ASC191</t>
+          <t>ASC098</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>too spicy</t>
+          <t>paratha is hard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turn off the heat and stir in a spoon of cream or beaten curd.</t>
+          <t>The dough was stiff or the heat too low. Knead a softer dough and cook on medium heat with a little more ghee.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>गैस बंद करके एक चम्मच मलाई या फेंटा हुआ दही मिला दो।</t>
+          <t>आटा सख़्त था या आँच धीमी थी। नरम आटा गूँधो और मध्यम आँच पर थोड़ा ज़्यादा घी लगाकर सेको।</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ASC191</t>
+          <t>ASC098</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>too watery</t>
+          <t>stuffing is wet and sticky</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cook uncovered on high heat for 4 to 5 minutes, stirring.</t>
+          <t>The potatoes were too wet. Let them cool fully before mashing, and mix a spoon of dry atta into the stuffing.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>बिना ढके तेज़ आँच पर 4-5 मिनट चलाते हुए पकाओ।</t>
+          <t>आलू गीले थे। मैश करने से पहले पूरा ठंडा होने दो और मसाले में एक चम्मच सूखा आटा मिला दो।</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ASC215</t>
+          <t>ASC115</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>palak turned dark or brown</t>
+          <t>rice is mushy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>The spinach cooked too long. It is still fine to eat. Next time boil it for only 2 minutes and cook the puree briefly.</t>
+          <t>Too much water. Open the lid on low heat for 2 minutes to let steam out. Use a little less water next time.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>पालक ज़्यादा पक गया। खाने में ठीक है। अगली बार सिर्फ़ 2 मिनट उबालना और प्यूरी कम पकाना।</t>
+          <t>पानी ज़्यादा था। धीमी आँच पर ढक्कन खोलकर 2 मिनट भाप निकलने दो। अगली बार पानी थोड़ा कम।</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ASC215</t>
+          <t>ASC115</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>tastes bitter</t>
+          <t>rice is still hard</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Stir in a spoon of cream or a pinch of sugar.</t>
+          <t>Sprinkle 3 tablespoons of hot water, cover and cook on low heat for 5 minutes.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>एक चम्मच मलाई या चुटकी भर चीनी मिला दो।</t>
+          <t>3 चम्मच गरम पानी छिड़को, ढककर धीमी आँच पर 5 मिनट पकाओ।</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ASC215</t>
+          <t>ASC115</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>too thick</t>
+          <t>bottom got burnt</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Add 2 to 3 tablespoons of hot water and stir.</t>
+          <t>Do not stir. Spoon the top rice into another pan and leave the burnt layer.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2-3 चम्मच गरम पानी डालकर मिलाओ।</t>
+          <t>चलाओ मत। ऊपर के चावल दूसरे बर्तन में निकाल लो, जली परत छोड़ दो।</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ASC240</t>
+          <t>ASC117</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>chicken is hard or chewy</t>
+          <t>sprouts still crunchy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Add half a cup of water, cover and simmer on low heat for 10 more minutes.</t>
+          <t>That is fine and healthy. For softer sprouts, steam them for 5 minutes before adding next time.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>आधा कप पानी डालो, ढककर धीमी आँच पर 10 मिनट और पकाओ।</t>
+          <t>यह ठीक और सेहतमंद है। नरम चाहिए तो अगली बार डालने से पहले 5 मिनट भाप में पका लेना।</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ASC240</t>
+          <t>ASC117</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>too spicy</t>
+          <t>rice is mushy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turn off the heat and stir in 2 spoons of beaten curd or cream.</t>
+          <t>Open the lid on low heat for 2 minutes to let steam out.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>गैस बंद करके 2 चम्मच फेंटा हुआ दही या मलाई मिला दो।</t>
+          <t>धीमी आँच पर 2 मिनट ढक्कन खोलकर भाप निकलने दो।</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASC240</t>
+          <t>ASC117</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>gravy too thin</t>
+          <t>tastes plain</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cook uncovered on high heat for 5 minutes, stirring.</t>
+          <t>Squeeze in some lemon and add a pinch more salt and garam masala.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>बिना ढके तेज़ आँच पर 5 मिनट चलाते हुए पकाओ।</t>
+          <t>थोड़ा नींबू निचोड़ो और चुटकी भर नमक और गरम मसाला डालो।</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BFP039</t>
+          <t>ASC118</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>lumps in upma</t>
+          <t>rice is mushy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Break them with the back of the spoon while stirring. Next time add the suji slowly into the boiling water.</t>
+          <t>Too much water. Open the lid on low heat for 2 minutes. Use a little less water next time.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>चलाते हुए चम्मच के पिछले हिस्से से गुठलियाँ तोड़ दो। अगली बार सूजी धीरे-धीरे डालना।</t>
+          <t>पानी ज़्यादा था। धीमी आँच पर 2 मिनट ढक्कन खोल दो। अगली बार पानी थोड़ा कम।</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BFP039</t>
+          <t>ASC118</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>upma too thick or dry</t>
+          <t>paneer is hard</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Add 2 to 3 tablespoons of hot water, stir and cover for a minute.</t>
+          <t>Soak the pieces in warm water for 10 minutes before mixing them in.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2-3 चम्मच गरम पानी डालो, मिलाओ और एक मिनट ढक दो।</t>
+          <t>मिलाने से पहले पनीर के टुकड़े 10 मिनट गुनगुने पानी में रखो।</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BFP039</t>
+          <t>ASC118</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>upma is sticky</t>
+          <t>rice is still hard</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>The suji was not roasted enough. Next time roast it until it smells nutty.</t>
+          <t>Sprinkle 3 tablespoons of hot water, cover and cook on low heat for 5 minutes.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>सूजी कम भुनी थी। अगली बार खुशबू आने तक अच्छे से भूनना।</t>
+          <t>3 चम्मच गरम पानी छिड़को, ढककर धीमी आँच पर 5 मिनट पकाओ।</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BFP044</t>
+          <t>ASC123</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>poha is mushy</t>
+          <t>rice broke and turned mushy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>It soaked too long. Spread it in the pan on high heat for a minute to dry a little. Next time just rinse and drain.</t>
+          <t>It boiled too long before layering. Stop at three-quarters done next time; it finishes on dum.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>पोहा ज़्यादा देर भीगा। तेज़ आँच पर एक मिनट फैलाकर थोड़ा सुखा लो। अगली बार बस धोकर पानी निकाल देना।</t>
+          <t>परत लगाने से पहले चावल ज़्यादा उबल गए। अगली बार तीन-चौथाई पर रोकना, बाकी दम पर पकते हैं।</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BFP044</t>
+          <t>ASC123</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>poha is dry and hard</t>
+          <t>bottom is burning</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sprinkle 2 tablespoons of water, cover and steam on low heat for 2 minutes.</t>
+          <t>Put a flat tawa under the pot and keep the heat at the lowest for the dum.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2 चम्मच पानी छिड़को, ढककर धीमी आँच पर 2 मिनट भाप में पकाओ।</t>
+          <t>बर्तन के नीचे चपटा तवा रख दो और दम के लिए आँच सबसे धीमी रखो।</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BFP044</t>
+          <t>ASC123</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>too salty</t>
+          <t>rice on top is hard</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mix in a little more rinsed poha, or squeeze in more lemon.</t>
+          <t>Sprinkle 3 tablespoons of hot water or milk, cover tightly and cook on low heat for 5 more minutes.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>थोड़ा और धुला पोहा मिला दो, या थोड़ा और नींबू निचोड़ दो।</t>
+          <t>3 चम्मच गरम पानी या दूध छिड़को, कसकर ढककर धीमी आँच पर 5 मिनट और पकाओ।</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BFP136</t>
+          <t>ASC144</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>rice is mushy</t>
+          <t>idlis are hard and flat</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>There was too much water. Open the lid and let the steam escape on low heat for 2 minutes. Use a little less water next time.</t>
+          <t>The batter did not ferment enough. Leave it longer in a warm spot, or add a pinch of baking soda just before steaming.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>पानी ज़्यादा हो गया। ढक्कन हटाकर धीमी आँच पर 2 मिनट भाप निकलने दो। अगली बार पानी थोड़ा कम डालना।</t>
+          <t>घोल ठीक से नहीं उठा। गरम जगह और देर रखो, या भाप से ठीक पहले चुटकी भर मीठा सोडा मिला दो।</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BFP136</t>
+          <t>ASC144</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>rice is still hard</t>
+          <t>idlis stick to the mould</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sprinkle 2 to 3 tablespoons of hot water, cover and cook on low heat for 5 more minutes.</t>
+          <t>Grease the moulds well and let the idlis rest for 2 minutes before taking them out.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2-3 चम्मच गरम पानी छिड़को, ढककर धीमी आँच पर 5 मिनट और पकाओ।</t>
+          <t>साँचों में अच्छे से तेल लगाओ और निकालने से पहले 2 मिनट रुको।</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BFP136</t>
+          <t>ASC144</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>bottom got burnt</t>
+          <t>sticky inside</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Do not stir. Spoon the top rice into another pan and leave the burnt layer behind.</t>
+          <t>Steam for 3 to 4 more minutes, until a knife comes out clean.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>चलाओ मत। ऊपर के चावल चम्मच से दूसरे बर्तन में निकाल लो, जली परत वहीं छोड़ दो।</t>
+          <t>3-4 मिनट और भाप में पकाओ, जब तक चाकू साफ़ न निकले।</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BFP240</t>
+          <t>ASC146</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yolk turned green</t>
+          <t>dosa sticks and tears</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>The egg boiled too long. It is safe to eat. Next time boil it for 10 minutes and cool it in cold water straight away.</t>
+          <t>The tawa was not hot or seasoned. Heat it well, rub it with a cut onion dipped in oil, and try again.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>अंडा ज़्यादा उबल गया। खाने में ठीक है। अगली बार 10 मिनट उबालकर तुरंत ठंडे पानी में डालना।</t>
+          <t>तवा कम गरम या चिकना नहीं था। अच्छे से गरम करो, तेल में डुबोया कटा प्याज़ रगड़ो और फिर कोशिश करो।</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BFP240</t>
+          <t>ASC146</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gravy too thin</t>
+          <t>dosa is thick and soft</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cook uncovered on high heat for 4 to 5 minutes until it thickens.</t>
+          <t>Thin the batter with a little water and spread it faster in wide circles.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>बिना ढके तेज़ आँच पर 4-5 मिनट पकाओ जब तक गाढ़ी न हो जाए।</t>
+          <t>घोल में थोड़ा पानी मिलाओ और बड़े गोल घेरे में जल्दी फैलाओ।</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BFP240</t>
+          <t>ASC146</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>egg tastes plain</t>
+          <t>batter did not ferment</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Make the cuts a little deeper and simmer it in the gravy for 3 more minutes.</t>
+          <t>Keep it in a warm place, like inside the oven with the light on, for a few more hours.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>चीरे थोड़े गहरे करो और ग्रेवी में 3 मिनट और पकाओ।</t>
+          <t>कुछ घंटे और गरम जगह रखो, जैसे ओवन के अंदर बत्ती जलाकर।</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OSR100</t>
+          <t>ASC147</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>chilla sticks to the tawa</t>
+          <t>dosa breaks when lifting</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>The tawa was not hot or greased enough. Heat it well and wipe it with a little oil before each chilla.</t>
+          <t>Cook it a minute longer until fully crisp, and lift from the edges with a thin spatula.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>तवा कम गरम था या चिकना नहीं था। अच्छे से गरम करो और हर चीले से पहले थोड़ा तेल पोंछ दो।</t>
+          <t>एक मिनट और पूरा कुरकुरा होने तक सेको, और पतली पलटनी से किनारों से उठाओ।</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OSR100</t>
+          <t>ASC147</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>chilla breaks when flipping</t>
+          <t>dosa is thick, not lacy</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>The batter is too thin. Mix in a tablespoon of besan, and wait until the edges lift before flipping.</t>
+          <t>The batter is too thick. Add water until it is like buttermilk and pour from higher up.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>घोल पतला है। एक चम्मच बेसन मिलाओ, और किनारे उठने के बाद ही पलटो।</t>
+          <t>घोल गाढ़ा है। छाछ जैसा पतला होने तक पानी मिलाओ और ऊपर से डालो।</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>ASC147</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>sticks to the tawa</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>The tawa was not hot enough. Heat it well and grease it before each dosa.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>तवा कम गरम था। अच्छे से गरम करो और हर डोसे से पहले चिकना करो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ASC155</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>chana dal still hard</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Chana dal takes longest. Add half a cup of water and give it 2 more whistles.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>चना दाल सबसे देर में पकती है। आधा कप पानी डालकर 2 सीटी और लगाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ASC155</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>too much water</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Boil it uncovered on high heat for 5 minutes.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>बिना ढके तेज़ आँच पर 5 मिनट उबालो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ASC155</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>too salty</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Add hot water and a squeeze of lemon, and boil for 2 minutes.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>गरम पानी और थोड़ा नींबू डालकर 2 मिनट उबालो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ASC175</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>tastes bitter</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Methi is a little bitter by nature. Add a pinch of sugar or a squeeze of lemon and mix.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>मेथी थोड़ी कड़वी होती है। चुटकी भर चीनी या नींबू निचोड़कर मिला दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ASC175</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>potato sticking to the pan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Sprinkle 2 tablespoons of water, scrape gently and cover for 2 minutes.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2 चम्मच पानी छिड़को, हल्का खुरचो और 2 मिनट ढक दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ASC175</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>methi is gritty</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>It was not washed well. Wash methi in a big bowl of water 2 or 3 times next time.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>मेथी अच्छे से नहीं धुली। अगली बार बड़े बर्तन में 2-3 बार पानी बदलकर धोना।</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ASC190</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>too watery</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Cook uncovered on high heat for 5 minutes, and mash a few potato pieces into the gravy.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>बिना ढके तेज़ आँच पर 5 मिनट पकाओ और आलू के कुछ टुकड़े ग्रेवी में मैश कर दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ASC190</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>too salty</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Add half a cup of water and a boiled potato, and cook for 5 minutes.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>आधा कप पानी और एक उबला आलू डालकर 5 मिनट पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ASC190</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>masala stuck and burnt</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Move it to a clean pan without scraping the bottom, and add a little water.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>नीचे से खुरचे बिना इसे साफ़ पैन में डाल दो और थोड़ा पानी मिला दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ASC191</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>paneer is hard or rubbery</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>It cooked too long. Soak the pieces in warm water for 10 minutes, and add them only at the end next time.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>पनीर ज़्यादा पक गया। टुकड़ों को 10 मिनट गुनगुने पानी में रखो, और अगली बार आखिर में डालना।</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ASC191</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>too spicy</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Turn off the heat and stir in a spoon of cream or beaten curd.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>गैस बंद करके एक चम्मच मलाई या फेंटा हुआ दही मिला दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ASC191</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>too watery</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Cook uncovered on high heat for 4 to 5 minutes, stirring.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>बिना ढके तेज़ आँच पर 4-5 मिनट चलाते हुए पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ASC192</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>too watery</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Mushrooms let out water. Cook uncovered on high heat for 3 to 4 minutes.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>मशरूम पानी छोड़ते हैं। बिना ढके तेज़ आँच पर 3-4 मिनट पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ASC192</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>mushrooms are rubbery</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>They cooked too long. Add them only in the last 5 minutes next time.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>मशरूम ज़्यादा पक गए। अगली बार आखिरी 5 मिनट में डालना।</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ASC192</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>too spicy</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Stir in a spoon of cream or curd off the heat.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>गैस बंद करके एक चम्मच मलाई या दही मिला दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ASC193</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>peas are wrinkly and hard</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>They cooked uncovered too long. Add a little water, cover and cook for 3 minutes.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>मटर बिना ढके ज़्यादा पके। थोड़ा पानी डालो, ढककर 3 मिनट पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ASC193</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>too watery</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Cook uncovered on high heat for 3 to 4 minutes.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>बिना ढके तेज़ आँच पर 3-4 मिनट पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ASC193</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>too salty</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Add half a cup of water and a boiled potato and simmer for 5 minutes.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>आधा कप पानी और एक उबला आलू डालकर 5 मिनट पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ASC214</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>curd split in the gravy</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Turn the heat off, beat a spoon of fresh curd with a pinch of besan and stir it in. Next time add curd on low heat.</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>गैस बंद करो, एक चम्मच ताज़ा दही में चुटकी भर बेसन फेंटकर मिला दो। अगली बार दही धीमी आँच पर डालना।</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ASC214</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>potatoes taste plain inside</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Prick them more and leave them in the gravy, covered, for 10 more minutes.</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>आलू में और छेद करो और ढककर 10 मिनट और ग्रेवी में रहने दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ASC214</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>too spicy</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Stir in another spoon of curd or a spoon of cream on low heat.</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>धीमी आँच पर एक चम्मच और दही या मलाई मिला दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ASC215</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>palak turned dark or brown</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>The spinach cooked too long. It is still fine to eat. Next time boil it for only 2 minutes and cook the puree briefly.</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>पालक ज़्यादा पक गया। खाने में ठीक है। अगली बार सिर्फ़ 2 मिनट उबालना और प्यूरी कम पकाना।</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ASC215</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>tastes bitter</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Stir in a spoon of cream or a pinch of sugar.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>एक चम्मच मलाई या चुटकी भर चीनी मिला दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ASC215</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>too thick</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Add 2 to 3 tablespoons of hot water and stir.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2-3 चम्मच गरम पानी डालकर मिलाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ASC240</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>chicken is hard or chewy</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Add half a cup of water, cover and simmer on low heat for 10 more minutes.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>आधा कप पानी डालो, ढककर धीमी आँच पर 10 मिनट और पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ASC240</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>too spicy</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Turn off the heat and stir in 2 spoons of beaten curd or cream.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>गैस बंद करके 2 चम्मच फेंटा हुआ दही या मलाई मिला दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ASC240</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>gravy too thin</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Cook uncovered on high heat for 5 minutes, stirring.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>बिना ढके तेज़ आँच पर 5 मिनट चलाते हुए पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ASC485</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>curd is too sour</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Mix in a spoon of milk or a pinch of sugar.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>एक चम्मच दूध या चुटकी भर चीनी मिला दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ASC485</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>too thick</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Beat in 2 tablespoons of cold water.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2 चम्मच ठंडा पानी मिलाकर फेंटो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ASC485</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>potato breaks into mush</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>It was overboiled. It still tastes good; next time stop at 2 whistles.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>आलू ज़्यादा उबल गया। स्वाद फिर भी अच्छा है; अगली बार 2 सीटी पर रुकना।</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BFP039</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>lumps in upma</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Break them with the back of the spoon while stirring. Next time add the suji slowly into the boiling water.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>चलाते हुए चम्मच के पिछले हिस्से से गुठलियाँ तोड़ दो। अगली बार सूजी धीरे-धीरे डालना।</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BFP039</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>upma too thick or dry</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Add 2 to 3 tablespoons of hot water, stir and cover for a minute.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2-3 चम्मच गरम पानी डालो, मिलाओ और एक मिनट ढक दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BFP039</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>upma is sticky</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>The suji was not roasted enough. Next time roast it until it smells nutty.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>सूजी कम भुनी थी। अगली बार खुशबू आने तक अच्छे से भूनना।</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BFP040</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>semiya turned sticky and mushy</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Too much water or it was not roasted. Spread it in the pan on medium heat for 2 minutes to dry a little.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>पानी ज़्यादा था या सेवइयाँ कम भुनी थीं। मध्यम आँच पर 2 मिनट फैलाकर थोड़ा सुखा लो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BFP040</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>semiya still hard</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Sprinkle 2 tablespoons of hot water, cover and cook for 2 minutes.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2 चम्मच गरम पानी छिड़को, ढककर 2 मिनट पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>BFP040</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>too salty</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Squeeze in more lemon and mix in a handful of roasted peanuts or vegetables.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>थोड़ा और नींबू निचोड़ो और मुट्ठी भर भुनी मूंगफली या सब्ज़ी मिला दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BFP041</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>still grainy and hard</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Add 3 tablespoons of hot water, cover and cook for 4 more minutes.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3 चम्मच गरम पानी डालो, ढककर 4 मिनट और पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>BFP041</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>lumps formed</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Break them with the back of the spoon while stirring.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>चलाते हुए चम्मच के पिछले हिस्से से गुठलियाँ तोड़ दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BFP041</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>stuck to the pan</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Add a teaspoon of oil around the edges and scrape gently.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>किनारों पर एक चम्मच तेल डालो और हल्का खुरचो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BFP043</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>lumps in upma</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Break them with the back of the spoon. Next time add the suji slowly into the boiling water.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>चम्मच के पिछले हिस्से से गुठलियाँ तोड़ दो। अगली बार सूजी धीरे-धीरे डालना।</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BFP043</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>too dry</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Add 2 to 3 tablespoons of hot water, stir and cover for a minute.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2-3 चम्मच गरम पानी डालो, मिलाओ और एक मिनट ढक दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BFP043</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>vegetables still hard</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Cut them smaller next time. For now, cover and cook on low heat for 3 more minutes.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>अगली बार सब्ज़ियाँ छोटी काटना। अभी ढककर धीमी आँच पर 3 मिनट और पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BFP044</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>poha is mushy</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>It soaked too long. Spread it in the pan on high heat for a minute to dry a little. Next time just rinse and drain.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>पोहा ज़्यादा देर भीगा। तेज़ आँच पर एक मिनट फैलाकर थोड़ा सुखा लो। अगली बार बस धोकर पानी निकाल देना।</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BFP044</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>poha is dry and hard</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Sprinkle 2 tablespoons of water, cover and steam on low heat for 2 minutes.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2 चम्मच पानी छिड़को, ढककर धीमी आँच पर 2 मिनट भाप में पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BFP044</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>too salty</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Mix in a little more rinsed poha, or squeeze in more lemon.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>थोड़ा और धुला पोहा मिला दो, या थोड़ा और नींबू निचोड़ दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>BFP136</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>rice is mushy</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>There was too much water. Open the lid and let the steam escape on low heat for 2 minutes. Use a little less water next time.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>पानी ज़्यादा हो गया। ढक्कन हटाकर धीमी आँच पर 2 मिनट भाप निकलने दो। अगली बार पानी थोड़ा कम डालना।</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BFP136</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>rice is still hard</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Sprinkle 2 to 3 tablespoons of hot water, cover and cook on low heat for 5 more minutes.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2-3 चम्मच गरम पानी छिड़को, ढककर धीमी आँच पर 5 मिनट और पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>BFP136</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>bottom got burnt</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Do not stir. Spoon the top rice into another pan and leave the burnt layer behind.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>चलाओ मत। ऊपर के चावल चम्मच से दूसरे बर्तन में निकाल लो, जली परत वहीं छोड़ दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>BFP147</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>idlis did not rise</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>The Eno went in too early or was old. Add Eno only right before steaming, and steam straight away.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ईनो बहुत पहले डाला या पुराना था। ईनो भाप से ठीक पहले डालो और तुरंत भाप में रखो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>BFP147</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>idlis are dry</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>The batter was too thick. Add 2 tablespoons of curd or water next time.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>घोल बहुत गाढ़ा था। अगली बार 2 चम्मच दही या पानी और डालना।</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>BFP147</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>sticky inside</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Steam for 3 more minutes, until a knife comes out clean.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3 मिनट और भाप में पकाओ, जब तक चाकू साफ़ न निकले।</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>BFP166</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>too much water</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Boil it uncovered on high heat for 5 minutes and the extra water will dry up.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>बिना ढके तेज़ आँच पर 5 मिनट उबालो, ज़्यादा पानी सूख जाएगा।</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>BFP166</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>too thick</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Add half a cup of hot water and boil for 2 minutes.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>आधा कप गरम पानी डालकर 2 मिनट उबालो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>BFP166</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>tadka burnt</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Throw it away and make a fresh one. Burnt garlic or cumin makes the dal bitter.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>जला तड़का फेंक दो और नया बनाओ। जला लहसुन या जीरा दाल को कड़वा कर देता है।</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>BFP239</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>too watery</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Mash 3 or 4 potato pieces into the gravy and cook uncovered for 3 minutes.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>आलू के 3-4 टुकड़े ग्रेवी में मैश करो और बिना ढके 3 मिनट पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>BFP239</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>potato still hard</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Add a little water, cover and cook for 5 more minutes.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>थोड़ा पानी डालो, ढककर 5 मिनट और पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>BFP239</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>too salty</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Add half a cup of water and one more boiled potato.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>आधा कप पानी और एक उबला आलू और डाल दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>BFP240</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>yolk turned green</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>The egg boiled too long. It is safe to eat. Next time boil it for 10 minutes and cool it in cold water straight away.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>अंडा ज़्यादा उबल गया। खाने में ठीक है। अगली बार 10 मिनट उबालकर तुरंत ठंडे पानी में डालना।</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>BFP240</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>gravy too thin</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Cook uncovered on high heat for 4 to 5 minutes until it thickens.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>बिना ढके तेज़ आँच पर 4-5 मिनट पकाओ जब तक गाढ़ी न हो जाए।</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>BFP240</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>egg tastes plain</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Make the cuts a little deeper and simmer it in the gravy for 3 more minutes.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>चीरे थोड़े गहरे करो और ग्रेवी में 3 मिनट और पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>BFP556</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>too dry</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Stir in half a cup of hot water and simmer for 2 minutes.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>आधा कप गरम पानी मिलाकर 2 मिनट पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>BFP556</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>too mushy</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>That is how khichdi often is. If you want it looser, it is fine; if too wet, cook uncovered for 3 minutes.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>खिचड़ी अक्सर ऐसी ही होती है। ज़्यादा गीली लगे तो बिना ढके 3 मिनट पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>BFP556</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>tastes plain</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Make a quick tadka of ghee, cumin and a pinch of hing and pour it on top.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>घी, जीरा और चुटकी भर हींग का झटपट तड़का बनाकर ऊपर डाल दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>BFP579</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>idlis are dense</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Add the soda only right before steaming, and do not overmix after adding it.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>सोडा भाप से ठीक पहले डालो, और उसके बाद ज़्यादा मत चलाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>BFP579</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>idlis are dry</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Add 2 tablespoons more curd to the batter.</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>घोल में 2 चम्मच और दही मिला दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>BFP579</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>sticky inside</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Steam for 3 more minutes, until a knife comes out clean.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3 मिनट और भाप में पकाओ, जब तक चाकू साफ़ न निकले।</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>OSR100</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>chilla sticks to the tawa</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>The tawa was not hot or greased enough. Heat it well and wipe it with a little oil before each chilla.</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>तवा कम गरम था या चिकना नहीं था। अच्छे से गरम करो और हर चीले से पहले थोड़ा तेल पोंछ दो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>OSR100</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>chilla breaks when flipping</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>The batter is too thin. Mix in a tablespoon of besan, and wait until the edges lift before flipping.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>घोल पतला है। एक चम्मच बेसन मिलाओ, और किनारे उठने के बाद ही पलटो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>OSR100</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
         <is>
           <t>raw inside</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>Spread it thinner and cook on lower heat, covered, for a minute.</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>पतला फैलाओ और धीमी आँच पर ढककर एक मिनट पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>OSR139</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>dal still hard</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Add a cup of hot water and pressure cook for 3 to 4 more whistles. Soak overnight next time.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>एक कप गरम पानी डालकर कुकर में 3-4 सीटी और लगाओ। अगली बार रात भर भिगोना।</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>OSR139</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>too thick</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Add hot water, half a cup at a time, and simmer for 2 minutes.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>आधा-आधा कप गरम पानी डालो और 2 मिनट पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>OSR139</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>sticking at the bottom</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Move it to a clean pot without scraping, add water and keep stirring.</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>नीचे से खुरचे बिना साफ़ बर्तन में डालो, पानी मिलाओ और चलाते रहो।</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>OSR144</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>some dal still hard</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Chana and urad cook slowest. Add half a cup of water and 2 more whistles.</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>चना और उड़द सबसे देर में पकते हैं। आधा कप पानी डालकर 2 सीटी और लगाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>OSR144</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>too thick</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Add hot water a little at a time and simmer for 2 minutes.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>थोड़ा-थोड़ा गरम पानी डालो और 2 मिनट पकाओ।</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>OSR144</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>too spicy</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Add a spoon of ghee and some more hot water, and serve with curd.</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>एक चम्मच घी और थोड़ा गरम पानी मिलाओ, और दही के साथ खाओ।</t>
         </is>
       </c>
     </row>

--- a/data/amma_ji_recipes.xlsx
+++ b/data/amma_ji_recipes.xlsx
@@ -77297,7 +77297,7 @@
       </c>
       <c r="B1904" t="inlineStr">
         <is>
-          <t>cheese</t>
+          <t>cream</t>
         </is>
       </c>
       <c r="C1904" t="inlineStr">
@@ -77318,7 +77318,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="G1904" t="inlineStr"/>
+      <c r="G1904" t="inlineStr">
+        <is>
+          <t>milk, skip</t>
+        </is>
+      </c>
     </row>
     <row r="1905">
       <c r="A1905" t="inlineStr">
